--- a/PRECOS.xlsx
+++ b/PRECOS.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G989"/>
+  <dimension ref="A1:G1041"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -22488,17 +22488,17 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -22507,26 +22507,29 @@
         </is>
       </c>
       <c r="E717">
-        <v>3.45</v>
+        <v>4.2</v>
+      </c>
+      <c r="F717">
+        <v>62.16</v>
       </c>
       <c r="G717" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -22535,26 +22538,29 @@
         </is>
       </c>
       <c r="E718">
-        <v>3.89</v>
+        <v>4.02</v>
+      </c>
+      <c r="F718">
+        <v>-6.94</v>
       </c>
       <c r="G718" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -22563,26 +22569,29 @@
         </is>
       </c>
       <c r="E719">
-        <v>6.78</v>
+        <v>5.986666666666667</v>
+      </c>
+      <c r="F719">
+        <v>-50.07</v>
       </c>
       <c r="G719" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -22591,26 +22600,29 @@
         </is>
       </c>
       <c r="E720">
-        <v>2.89</v>
+        <v>5.31</v>
+      </c>
+      <c r="F720">
+        <v>-29.11</v>
       </c>
       <c r="G720" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -22619,26 +22631,29 @@
         </is>
       </c>
       <c r="E721">
-        <v>29.78</v>
+        <v>25.99</v>
+      </c>
+      <c r="F721">
+        <v>-1.25</v>
       </c>
       <c r="G721" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -22647,26 +22662,29 @@
         </is>
       </c>
       <c r="E722">
-        <v>48.9</v>
+        <v>39.49</v>
+      </c>
+      <c r="F722">
+        <v>2.6</v>
       </c>
       <c r="G722" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -22675,26 +22693,29 @@
         </is>
       </c>
       <c r="E723">
-        <v>3.47</v>
+        <v>3.873333333333333</v>
+      </c>
+      <c r="F723">
+        <v>-7.56</v>
       </c>
       <c r="G723" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -22703,26 +22724,29 @@
         </is>
       </c>
       <c r="E724">
-        <v>4.82</v>
+        <v>6.316666666666666</v>
+      </c>
+      <c r="F724">
+        <v>46.22</v>
       </c>
       <c r="G724" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -22731,26 +22755,29 @@
         </is>
       </c>
       <c r="E725">
-        <v>4.42</v>
+        <v>5.12</v>
+      </c>
+      <c r="F725">
+        <v>1.19</v>
       </c>
       <c r="G725" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -22759,26 +22786,29 @@
         </is>
       </c>
       <c r="E726">
-        <v>27.29</v>
+        <v>27.65666666666667</v>
+      </c>
+      <c r="F726">
+        <v>-7.5</v>
       </c>
       <c r="G726" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -22787,26 +22817,29 @@
         </is>
       </c>
       <c r="E727">
-        <v>17.9</v>
+        <v>13.56666666666667</v>
+      </c>
+      <c r="F727">
+        <v>-8.949999999999999</v>
       </c>
       <c r="G727" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -22815,26 +22848,29 @@
         </is>
       </c>
       <c r="E728">
-        <v>7.29</v>
+        <v>8.143333333333333</v>
+      </c>
+      <c r="F728">
+        <v>-37.31</v>
       </c>
       <c r="G728" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -22843,10 +22879,13 @@
         </is>
       </c>
       <c r="E729">
-        <v>7.72</v>
+        <v>7.48</v>
+      </c>
+      <c r="F729">
+        <v>4.76</v>
       </c>
       <c r="G729" s="2">
-        <v>45901</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="730">
@@ -22862,7 +22901,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -22871,13 +22910,10 @@
         </is>
       </c>
       <c r="E730">
-        <v>3.18</v>
-      </c>
-      <c r="F730">
-        <v>-7.83</v>
+        <v>3.45</v>
       </c>
       <c r="G730" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="731">
@@ -22893,7 +22929,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -22902,13 +22938,10 @@
         </is>
       </c>
       <c r="E731">
-        <v>3.925</v>
-      </c>
-      <c r="F731">
-        <v>0.9</v>
+        <v>3.89</v>
       </c>
       <c r="G731" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="732">
@@ -22924,7 +22957,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -22933,13 +22966,10 @@
         </is>
       </c>
       <c r="E732">
-        <v>7.515</v>
-      </c>
-      <c r="F732">
-        <v>10.84</v>
+        <v>6.78</v>
       </c>
       <c r="G732" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="733">
@@ -22955,7 +22985,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -22964,13 +22994,10 @@
         </is>
       </c>
       <c r="E733">
-        <v>3.005</v>
-      </c>
-      <c r="F733">
-        <v>3.98</v>
+        <v>2.89</v>
       </c>
       <c r="G733" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="734">
@@ -22986,7 +23013,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -22995,13 +23022,10 @@
         </is>
       </c>
       <c r="E734">
-        <v>30.065</v>
-      </c>
-      <c r="F734">
-        <v>0.96</v>
+        <v>29.78</v>
       </c>
       <c r="G734" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="735">
@@ -23017,7 +23041,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -23026,13 +23050,10 @@
         </is>
       </c>
       <c r="E735">
-        <v>47.545</v>
-      </c>
-      <c r="F735">
-        <v>-2.77</v>
+        <v>48.9</v>
       </c>
       <c r="G735" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="736">
@@ -23048,7 +23069,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -23057,13 +23078,10 @@
         </is>
       </c>
       <c r="E736">
-        <v>3.655</v>
-      </c>
-      <c r="F736">
-        <v>5.33</v>
+        <v>3.47</v>
       </c>
       <c r="G736" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="737">
@@ -23079,7 +23097,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -23088,13 +23106,10 @@
         </is>
       </c>
       <c r="E737">
-        <v>4.905</v>
-      </c>
-      <c r="F737">
-        <v>1.76</v>
+        <v>4.82</v>
       </c>
       <c r="G737" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="738">
@@ -23110,7 +23125,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -23119,13 +23134,10 @@
         </is>
       </c>
       <c r="E738">
-        <v>4.45</v>
-      </c>
-      <c r="F738">
-        <v>0.68</v>
+        <v>4.42</v>
       </c>
       <c r="G738" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="739">
@@ -23141,7 +23153,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -23150,13 +23162,10 @@
         </is>
       </c>
       <c r="E739">
-        <v>27.435</v>
-      </c>
-      <c r="F739">
-        <v>0.53</v>
+        <v>27.29</v>
       </c>
       <c r="G739" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="740">
@@ -23172,7 +23181,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -23181,13 +23190,10 @@
         </is>
       </c>
       <c r="E740">
-        <v>17.425</v>
-      </c>
-      <c r="F740">
-        <v>-2.65</v>
+        <v>17.9</v>
       </c>
       <c r="G740" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="741">
@@ -23203,7 +23209,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -23212,13 +23218,10 @@
         </is>
       </c>
       <c r="E741">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F741">
-        <v>14.95</v>
+        <v>7.29</v>
       </c>
       <c r="G741" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="742">
@@ -23234,7 +23237,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -23243,13 +23246,10 @@
         </is>
       </c>
       <c r="E742">
-        <v>7.775</v>
-      </c>
-      <c r="F742">
-        <v>0.71</v>
+        <v>7.72</v>
       </c>
       <c r="G742" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="743">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -23274,13 +23274,13 @@
         </is>
       </c>
       <c r="E743">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="F743">
-        <v>-0.63</v>
+        <v>-7.83</v>
       </c>
       <c r="G743" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="744">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -23305,13 +23305,13 @@
         </is>
       </c>
       <c r="E744">
-        <v>3.73</v>
+        <v>3.925</v>
       </c>
       <c r="F744">
-        <v>-4.97</v>
+        <v>0.9</v>
       </c>
       <c r="G744" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="745">
@@ -23327,7 +23327,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -23336,13 +23336,13 @@
         </is>
       </c>
       <c r="E745">
-        <v>7.11</v>
+        <v>7.515</v>
       </c>
       <c r="F745">
-        <v>-5.39</v>
+        <v>10.84</v>
       </c>
       <c r="G745" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="746">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -23367,13 +23367,13 @@
         </is>
       </c>
       <c r="E746">
-        <v>2.79</v>
+        <v>3.005</v>
       </c>
       <c r="F746">
-        <v>-7.15</v>
+        <v>3.98</v>
       </c>
       <c r="G746" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="747">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -23398,13 +23398,13 @@
         </is>
       </c>
       <c r="E747">
-        <v>29.79</v>
+        <v>30.065</v>
       </c>
       <c r="F747">
-        <v>-0.91</v>
+        <v>0.96</v>
       </c>
       <c r="G747" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="748">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -23429,13 +23429,13 @@
         </is>
       </c>
       <c r="E748">
-        <v>47.23</v>
+        <v>47.545</v>
       </c>
       <c r="F748">
-        <v>-0.66</v>
+        <v>-2.77</v>
       </c>
       <c r="G748" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="749">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -23460,13 +23460,13 @@
         </is>
       </c>
       <c r="E749">
-        <v>3.45</v>
+        <v>3.655</v>
       </c>
       <c r="F749">
-        <v>-5.61</v>
+        <v>5.33</v>
       </c>
       <c r="G749" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="750">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -23491,13 +23491,13 @@
         </is>
       </c>
       <c r="E750">
-        <v>4.56</v>
+        <v>4.905</v>
       </c>
       <c r="F750">
-        <v>-7.03</v>
+        <v>1.76</v>
       </c>
       <c r="G750" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="751">
@@ -23513,7 +23513,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -23522,13 +23522,13 @@
         </is>
       </c>
       <c r="E751">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="F751">
-        <v>-11.91</v>
+        <v>0.68</v>
       </c>
       <c r="G751" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="752">
@@ -23544,7 +23544,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -23553,13 +23553,13 @@
         </is>
       </c>
       <c r="E752">
-        <v>25.37</v>
+        <v>27.435</v>
       </c>
       <c r="F752">
-        <v>-7.53</v>
+        <v>0.53</v>
       </c>
       <c r="G752" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="753">
@@ -23575,7 +23575,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -23584,13 +23584,13 @@
         </is>
       </c>
       <c r="E753">
-        <v>17.9</v>
+        <v>17.425</v>
       </c>
       <c r="F753">
-        <v>2.73</v>
+        <v>-2.65</v>
       </c>
       <c r="G753" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="754">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -23615,13 +23615,13 @@
         </is>
       </c>
       <c r="E754">
-        <v>6.79</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F754">
-        <v>-18.97</v>
+        <v>14.95</v>
       </c>
       <c r="G754" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="755">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -23646,13 +23646,13 @@
         </is>
       </c>
       <c r="E755">
-        <v>7.96</v>
+        <v>7.775</v>
       </c>
       <c r="F755">
-        <v>2.38</v>
+        <v>0.71</v>
       </c>
       <c r="G755" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="756">
@@ -23666,16 +23666,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D756" t="inlineStr">
         <is>
           <t>Arroz tipo 1</t>
         </is>
       </c>
       <c r="E756">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="F756">
-        <v>7.59</v>
+        <v>-0.63</v>
+      </c>
+      <c r="G756" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="757">
@@ -23689,16 +23697,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D757" t="inlineStr">
         <is>
           <t>Açúcar Refinado</t>
         </is>
       </c>
       <c r="E757">
-        <v>4.08</v>
+        <v>3.73</v>
       </c>
       <c r="F757">
-        <v>9.380000000000001</v>
+        <v>-4.97</v>
+      </c>
+      <c r="G757" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="758">
@@ -23712,16 +23728,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D758" t="inlineStr">
         <is>
           <t>Banana</t>
         </is>
       </c>
       <c r="E758">
-        <v>7.91</v>
+        <v>7.11</v>
       </c>
       <c r="F758">
-        <v>11.25</v>
+        <v>-5.39</v>
+      </c>
+      <c r="G758" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="759">
@@ -23735,16 +23759,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D759" t="inlineStr">
         <is>
           <t>Batata</t>
         </is>
       </c>
       <c r="E759">
-        <v>3.47</v>
+        <v>2.79</v>
       </c>
       <c r="F759">
-        <v>24.37</v>
+        <v>-7.15</v>
+      </c>
+      <c r="G759" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="760">
@@ -23758,16 +23790,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D760" t="inlineStr">
         <is>
           <t>Café em pó</t>
         </is>
       </c>
       <c r="E760">
-        <v>30.56</v>
+        <v>29.79</v>
       </c>
       <c r="F760">
-        <v>2.58</v>
+        <v>-0.91</v>
+      </c>
+      <c r="G760" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="761">
@@ -23781,16 +23821,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D761" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
       <c r="E761">
-        <v>46.2</v>
+        <v>47.23</v>
       </c>
       <c r="F761">
-        <v>-2.18</v>
+        <v>-0.66</v>
+      </c>
+      <c r="G761" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="762">
@@ -23804,16 +23852,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D762" t="inlineStr">
         <is>
           <t>Farinha de Trigo</t>
         </is>
       </c>
       <c r="E762">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="F762">
-        <v>6.67</v>
+        <v>-5.61</v>
+      </c>
+      <c r="G762" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="763">
@@ -23827,16 +23883,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D763" t="inlineStr">
         <is>
           <t>Feijão Preto</t>
         </is>
       </c>
       <c r="E763">
-        <v>4.74</v>
+        <v>4.56</v>
       </c>
       <c r="F763">
-        <v>3.95</v>
+        <v>-7.03</v>
+      </c>
+      <c r="G763" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="764">
@@ -23850,16 +23914,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D764" t="inlineStr">
         <is>
           <t>Leite</t>
         </is>
       </c>
       <c r="E764">
-        <v>4.64</v>
+        <v>3.92</v>
       </c>
       <c r="F764">
-        <v>18.37</v>
+        <v>-11.91</v>
+      </c>
+      <c r="G764" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="765">
@@ -23873,16 +23945,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D765" t="inlineStr">
         <is>
           <t>Manteiga</t>
         </is>
       </c>
       <c r="E765">
-        <v>28.75</v>
+        <v>25.37</v>
       </c>
       <c r="F765">
-        <v>13.32</v>
+        <v>-7.53</v>
+      </c>
+      <c r="G765" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="766">
@@ -23896,16 +23976,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D766" t="inlineStr">
         <is>
           <t>Pão Francês</t>
         </is>
       </c>
       <c r="E766">
-        <v>16.95</v>
+        <v>17.9</v>
       </c>
       <c r="F766">
-        <v>-5.31</v>
+        <v>2.73</v>
+      </c>
+      <c r="G766" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="767">
@@ -23919,16 +24007,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D767" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
       <c r="E767">
-        <v>5.43</v>
+        <v>6.79</v>
       </c>
       <c r="F767">
-        <v>-20.03</v>
+        <v>-18.97</v>
+      </c>
+      <c r="G767" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="768">
@@ -23942,16 +24038,24 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
       <c r="D768" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
       <c r="E768">
-        <v>7.42</v>
+        <v>7.96</v>
       </c>
       <c r="F768">
-        <v>-6.78</v>
+        <v>2.38</v>
+      </c>
+      <c r="G768" s="2">
+        <v>45962</v>
       </c>
     </row>
     <row r="769">
@@ -23962,12 +24066,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C769" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -23976,13 +24075,10 @@
         </is>
       </c>
       <c r="E769">
-        <v>3.753333333333333</v>
+        <v>3.4</v>
       </c>
       <c r="F769">
-        <v>10.39</v>
-      </c>
-      <c r="G769" s="2">
-        <v>46235</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="770">
@@ -23993,12 +24089,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C770" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -24007,13 +24098,10 @@
         </is>
       </c>
       <c r="E770">
-        <v>3.4875</v>
+        <v>4.08</v>
       </c>
       <c r="F770">
-        <v>-14.52</v>
-      </c>
-      <c r="G770" s="2">
-        <v>46235</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="771">
@@ -24024,12 +24112,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C771" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -24038,13 +24121,10 @@
         </is>
       </c>
       <c r="E771">
-        <v>5.918333333333333</v>
+        <v>7.91</v>
       </c>
       <c r="F771">
-        <v>-25.18</v>
-      </c>
-      <c r="G771" s="2">
-        <v>46235</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="772">
@@ -24055,12 +24135,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C772" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -24069,13 +24144,10 @@
         </is>
       </c>
       <c r="E772">
-        <v>5.4375</v>
+        <v>3.47</v>
       </c>
       <c r="F772">
-        <v>56.7</v>
-      </c>
-      <c r="G772" s="2">
-        <v>46235</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="773">
@@ -24086,12 +24158,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C773" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -24100,13 +24167,10 @@
         </is>
       </c>
       <c r="E773">
-        <v>23.59166666666667</v>
+        <v>30.56</v>
       </c>
       <c r="F773">
-        <v>-22.8</v>
-      </c>
-      <c r="G773" s="2">
-        <v>46235</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="774">
@@ -24117,12 +24181,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C774" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -24131,13 +24190,10 @@
         </is>
       </c>
       <c r="E774">
-        <v>54.75333333333333</v>
+        <v>46.2</v>
       </c>
       <c r="F774">
-        <v>18.51</v>
-      </c>
-      <c r="G774" s="2">
-        <v>46235</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="775">
@@ -24148,12 +24204,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C775" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -24162,13 +24213,10 @@
         </is>
       </c>
       <c r="E775">
-        <v>3.5875</v>
+        <v>3.68</v>
       </c>
       <c r="F775">
-        <v>-2.51</v>
-      </c>
-      <c r="G775" s="2">
-        <v>46235</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="776">
@@ -24179,12 +24227,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C776" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -24193,13 +24236,10 @@
         </is>
       </c>
       <c r="E776">
-        <v>6.6125</v>
+        <v>4.74</v>
       </c>
       <c r="F776">
-        <v>39.5</v>
-      </c>
-      <c r="G776" s="2">
-        <v>46235</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="777">
@@ -24210,12 +24250,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C777" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -24224,13 +24259,10 @@
         </is>
       </c>
       <c r="E777">
-        <v>5.126666666666667</v>
+        <v>4.64</v>
       </c>
       <c r="F777">
-        <v>10.49</v>
-      </c>
-      <c r="G777" s="2">
-        <v>46235</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="778">
@@ -24241,12 +24273,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C778" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -24255,13 +24282,10 @@
         </is>
       </c>
       <c r="E778">
-        <v>29.4425</v>
+        <v>28.75</v>
       </c>
       <c r="F778">
-        <v>2.41</v>
-      </c>
-      <c r="G778" s="2">
-        <v>46235</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="779">
@@ -24272,12 +24296,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C779" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -24286,13 +24305,10 @@
         </is>
       </c>
       <c r="E779">
-        <v>15.70666666666667</v>
+        <v>16.95</v>
       </c>
       <c r="F779">
-        <v>-7.34</v>
-      </c>
-      <c r="G779" s="2">
-        <v>46235</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="780">
@@ -24303,12 +24319,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C780" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -24317,13 +24328,10 @@
         </is>
       </c>
       <c r="E780">
-        <v>7.433333333333334</v>
+        <v>5.43</v>
       </c>
       <c r="F780">
-        <v>36.89</v>
-      </c>
-      <c r="G780" s="2">
-        <v>46235</v>
+        <v>-20.03</v>
       </c>
     </row>
     <row r="781">
@@ -24334,12 +24342,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C781" t="inlineStr">
-        <is>
-          <t>Agosto</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -24348,13 +24351,10 @@
         </is>
       </c>
       <c r="E781">
-        <v>7.036666666666667</v>
+        <v>7.42</v>
       </c>
       <c r="F781">
-        <v>-5.17</v>
-      </c>
-      <c r="G781" s="2">
-        <v>46235</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="782">
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -24379,13 +24379,13 @@
         </is>
       </c>
       <c r="E782">
-        <v>3.4975</v>
+        <v>3.753333333333333</v>
       </c>
       <c r="F782">
-        <v>-6.82</v>
+        <v>10.39</v>
       </c>
       <c r="G782" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="783">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -24410,13 +24410,13 @@
         </is>
       </c>
       <c r="E783">
-        <v>3.425</v>
+        <v>3.4875</v>
       </c>
       <c r="F783">
-        <v>-1.79</v>
+        <v>-14.52</v>
       </c>
       <c r="G783" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="784">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="E784">
-        <v>5.362500000000001</v>
+        <v>5.918333333333333</v>
       </c>
       <c r="F784">
-        <v>-9.390000000000001</v>
+        <v>-25.18</v>
       </c>
       <c r="G784" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="785">
@@ -24463,7 +24463,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -24472,13 +24472,13 @@
         </is>
       </c>
       <c r="E785">
-        <v>5.9625</v>
+        <v>5.4375</v>
       </c>
       <c r="F785">
-        <v>9.66</v>
+        <v>56.7</v>
       </c>
       <c r="G785" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="786">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -24503,13 +24503,13 @@
         </is>
       </c>
       <c r="E786">
-        <v>22.15666666666667</v>
+        <v>23.59166666666667</v>
       </c>
       <c r="F786">
-        <v>-6.08</v>
+        <v>-22.8</v>
       </c>
       <c r="G786" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="787">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="E787">
-        <v>49.65833333333333</v>
+        <v>54.75333333333333</v>
       </c>
       <c r="F787">
-        <v>-9.31</v>
+        <v>18.51</v>
       </c>
       <c r="G787" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="788">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -24565,13 +24565,13 @@
         </is>
       </c>
       <c r="E788">
-        <v>3.69</v>
+        <v>3.5875</v>
       </c>
       <c r="F788">
-        <v>2.86</v>
+        <v>-2.51</v>
       </c>
       <c r="G788" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="789">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="E789">
-        <v>5.9575</v>
+        <v>6.6125</v>
       </c>
       <c r="F789">
-        <v>-9.91</v>
+        <v>39.5</v>
       </c>
       <c r="G789" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="790">
@@ -24618,7 +24618,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -24627,13 +24627,13 @@
         </is>
       </c>
       <c r="E790">
-        <v>5.065</v>
+        <v>5.126666666666667</v>
       </c>
       <c r="F790">
-        <v>-1.2</v>
+        <v>10.49</v>
       </c>
       <c r="G790" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="791">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -24658,13 +24658,13 @@
         </is>
       </c>
       <c r="E791">
-        <v>27.06833333333334</v>
+        <v>29.4425</v>
       </c>
       <c r="F791">
-        <v>-8.06</v>
+        <v>2.41</v>
       </c>
       <c r="G791" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="792">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -24689,13 +24689,13 @@
         </is>
       </c>
       <c r="E792">
-        <v>15.60833333333333</v>
+        <v>15.70666666666667</v>
       </c>
       <c r="F792">
-        <v>-0.63</v>
+        <v>-7.34</v>
       </c>
       <c r="G792" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="793">
@@ -24711,7 +24711,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -24720,13 +24720,13 @@
         </is>
       </c>
       <c r="E793">
-        <v>11.41833333333333</v>
+        <v>7.433333333333334</v>
       </c>
       <c r="F793">
-        <v>53.61</v>
+        <v>36.89</v>
       </c>
       <c r="G793" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="794">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -24751,19 +24751,19 @@
         </is>
       </c>
       <c r="E794">
-        <v>7.003333333333334</v>
+        <v>7.036666666666667</v>
       </c>
       <c r="F794">
-        <v>-0.47</v>
+        <v>-5.17</v>
       </c>
       <c r="G794" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -24773,7 +24773,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
@@ -24782,16 +24782,19 @@
         </is>
       </c>
       <c r="E795">
-        <v>3.46</v>
+        <v>3.4975</v>
+      </c>
+      <c r="F795">
+        <v>-6.82</v>
       </c>
       <c r="G795" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -24801,7 +24804,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -24810,16 +24813,19 @@
         </is>
       </c>
       <c r="E796">
-        <v>4.446666666666667</v>
+        <v>3.425</v>
+      </c>
+      <c r="F796">
+        <v>-1.79</v>
       </c>
       <c r="G796" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -24829,7 +24835,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -24838,16 +24844,19 @@
         </is>
       </c>
       <c r="E797">
-        <v>5.82</v>
+        <v>5.362500000000001</v>
+      </c>
+      <c r="F797">
+        <v>-9.390000000000001</v>
       </c>
       <c r="G797" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -24857,7 +24866,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -24866,16 +24875,19 @@
         </is>
       </c>
       <c r="E798">
-        <v>4.49</v>
+        <v>5.9625</v>
+      </c>
+      <c r="F798">
+        <v>9.66</v>
       </c>
       <c r="G798" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -24885,7 +24897,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -24894,16 +24906,19 @@
         </is>
       </c>
       <c r="E799">
-        <v>32.35</v>
+        <v>22.15666666666667</v>
+      </c>
+      <c r="F799">
+        <v>-6.08</v>
       </c>
       <c r="G799" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -24913,7 +24928,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -24922,16 +24937,19 @@
         </is>
       </c>
       <c r="E800">
-        <v>48.44333333333334</v>
+        <v>49.65833333333333</v>
+      </c>
+      <c r="F800">
+        <v>-9.31</v>
       </c>
       <c r="G800" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -24941,7 +24959,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -24950,16 +24968,19 @@
         </is>
       </c>
       <c r="E801">
-        <v>3.813333333333333</v>
+        <v>3.69</v>
+      </c>
+      <c r="F801">
+        <v>2.86</v>
       </c>
       <c r="G801" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -24969,7 +24990,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -24978,16 +24999,19 @@
         </is>
       </c>
       <c r="E802">
-        <v>5.46</v>
+        <v>5.9575</v>
+      </c>
+      <c r="F802">
+        <v>-9.91</v>
       </c>
       <c r="G802" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -24997,7 +25021,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -25006,16 +25030,19 @@
         </is>
       </c>
       <c r="E803">
-        <v>4.48</v>
+        <v>5.065</v>
+      </c>
+      <c r="F803">
+        <v>-1.2</v>
       </c>
       <c r="G803" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -25025,7 +25052,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -25034,16 +25061,19 @@
         </is>
       </c>
       <c r="E804">
-        <v>28.26666666666667</v>
+        <v>27.06833333333334</v>
+      </c>
+      <c r="F804">
+        <v>-8.06</v>
       </c>
       <c r="G804" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -25053,7 +25083,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -25062,16 +25092,19 @@
         </is>
       </c>
       <c r="E805">
-        <v>16.94666666666667</v>
+        <v>15.60833333333333</v>
+      </c>
+      <c r="F805">
+        <v>-0.63</v>
       </c>
       <c r="G805" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -25081,7 +25114,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -25090,16 +25123,19 @@
         </is>
       </c>
       <c r="E806">
-        <v>8.99</v>
+        <v>11.41833333333333</v>
+      </c>
+      <c r="F806">
+        <v>53.61</v>
       </c>
       <c r="G806" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -25109,7 +25145,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -25118,10 +25154,13 @@
         </is>
       </c>
       <c r="E807">
-        <v>7.763333333333333</v>
+        <v>7.003333333333334</v>
+      </c>
+      <c r="F807">
+        <v>-0.47</v>
       </c>
       <c r="G807" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="808">
@@ -25137,7 +25176,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -25146,13 +25185,10 @@
         </is>
       </c>
       <c r="E808">
-        <v>3.69</v>
-      </c>
-      <c r="F808">
-        <v>6.65</v>
+        <v>3.46</v>
       </c>
       <c r="G808" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="809">
@@ -25168,7 +25204,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -25177,13 +25213,10 @@
         </is>
       </c>
       <c r="E809">
-        <v>4.15</v>
-      </c>
-      <c r="F809">
-        <v>-6.67</v>
+        <v>4.446666666666667</v>
       </c>
       <c r="G809" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="810">
@@ -25199,7 +25232,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -25208,13 +25241,10 @@
         </is>
       </c>
       <c r="E810">
-        <v>5.29</v>
-      </c>
-      <c r="F810">
-        <v>-9.109999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="G810" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="811">
@@ -25230,7 +25260,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -25239,13 +25269,10 @@
         </is>
       </c>
       <c r="E811">
-        <v>7.456666666666667</v>
-      </c>
-      <c r="F811">
-        <v>66.06999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="G811" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="812">
@@ -25261,7 +25288,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -25270,13 +25297,10 @@
         </is>
       </c>
       <c r="E812">
-        <v>31.37333333333333</v>
-      </c>
-      <c r="F812">
-        <v>-3.02</v>
+        <v>32.35</v>
       </c>
       <c r="G812" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="813">
@@ -25292,7 +25316,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -25301,13 +25325,10 @@
         </is>
       </c>
       <c r="E813">
-        <v>48.68</v>
-      </c>
-      <c r="F813">
-        <v>0.49</v>
+        <v>48.44333333333334</v>
       </c>
       <c r="G813" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="814">
@@ -25323,7 +25344,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -25332,13 +25353,10 @@
         </is>
       </c>
       <c r="E814">
-        <v>3.76</v>
-      </c>
-      <c r="F814">
-        <v>-1.4</v>
+        <v>3.813333333333333</v>
       </c>
       <c r="G814" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="815">
@@ -25354,7 +25372,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -25363,13 +25381,10 @@
         </is>
       </c>
       <c r="E815">
-        <v>5.89</v>
-      </c>
-      <c r="F815">
-        <v>7.88</v>
+        <v>5.46</v>
       </c>
       <c r="G815" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="816">
@@ -25385,7 +25400,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -25394,13 +25409,10 @@
         </is>
       </c>
       <c r="E816">
-        <v>5.756666666666667</v>
-      </c>
-      <c r="F816">
-        <v>28.5</v>
+        <v>4.48</v>
       </c>
       <c r="G816" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="817">
@@ -25416,7 +25428,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -25425,13 +25437,10 @@
         </is>
       </c>
       <c r="E817">
-        <v>28.72</v>
-      </c>
-      <c r="F817">
-        <v>1.6</v>
+        <v>28.26666666666667</v>
       </c>
       <c r="G817" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="818">
@@ -25447,7 +25456,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -25456,13 +25465,10 @@
         </is>
       </c>
       <c r="E818">
-        <v>17.21333333333333</v>
-      </c>
-      <c r="F818">
-        <v>1.57</v>
+        <v>16.94666666666667</v>
       </c>
       <c r="G818" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="819">
@@ -25478,7 +25484,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -25489,11 +25495,8 @@
       <c r="E819">
         <v>8.99</v>
       </c>
-      <c r="F819">
-        <v>0</v>
-      </c>
       <c r="G819" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="820">
@@ -25509,7 +25512,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -25518,13 +25521,10 @@
         </is>
       </c>
       <c r="E820">
-        <v>7.706666666666666</v>
-      </c>
-      <c r="F820">
-        <v>-0.73</v>
+        <v>7.763333333333333</v>
       </c>
       <c r="G820" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="821">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -25549,13 +25549,13 @@
         </is>
       </c>
       <c r="E821">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="F821">
-        <v>-2.44</v>
+        <v>6.65</v>
       </c>
       <c r="G821" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="822">
@@ -25571,7 +25571,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -25580,13 +25580,13 @@
         </is>
       </c>
       <c r="E822">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="F822">
-        <v>0.48</v>
+        <v>-6.67</v>
       </c>
       <c r="G822" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="823">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -25611,13 +25611,13 @@
         </is>
       </c>
       <c r="E823">
-        <v>4.99</v>
+        <v>5.29</v>
       </c>
       <c r="F823">
-        <v>-5.67</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="G823" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="824">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -25642,13 +25642,13 @@
         </is>
       </c>
       <c r="E824">
-        <v>8.99</v>
+        <v>7.456666666666667</v>
       </c>
       <c r="F824">
-        <v>20.56</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G824" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="825">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -25673,13 +25673,13 @@
         </is>
       </c>
       <c r="E825">
-        <v>28.76666666666667</v>
+        <v>31.37333333333333</v>
       </c>
       <c r="F825">
-        <v>-8.31</v>
+        <v>-3.02</v>
       </c>
       <c r="G825" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="826">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -25704,13 +25704,13 @@
         </is>
       </c>
       <c r="E826">
-        <v>50.02666666666666</v>
+        <v>48.68</v>
       </c>
       <c r="F826">
-        <v>2.77</v>
+        <v>0.49</v>
       </c>
       <c r="G826" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="827">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -25735,13 +25735,13 @@
         </is>
       </c>
       <c r="E827">
-        <v>3.506666666666666</v>
+        <v>3.76</v>
       </c>
       <c r="F827">
-        <v>-6.74</v>
+        <v>-1.4</v>
       </c>
       <c r="G827" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="828">
@@ -25757,7 +25757,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -25766,13 +25766,13 @@
         </is>
       </c>
       <c r="E828">
-        <v>5.896666666666667</v>
+        <v>5.89</v>
       </c>
       <c r="F828">
-        <v>0.11</v>
+        <v>7.88</v>
       </c>
       <c r="G828" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="829">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -25797,13 +25797,13 @@
         </is>
       </c>
       <c r="E829">
-        <v>5.656666666666667</v>
+        <v>5.756666666666667</v>
       </c>
       <c r="F829">
-        <v>-1.74</v>
+        <v>28.5</v>
       </c>
       <c r="G829" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="830">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -25828,13 +25828,13 @@
         </is>
       </c>
       <c r="E830">
-        <v>28.66666666666667</v>
+        <v>28.72</v>
       </c>
       <c r="F830">
-        <v>-0.19</v>
+        <v>1.6</v>
       </c>
       <c r="G830" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="831">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -25859,13 +25859,13 @@
         </is>
       </c>
       <c r="E831">
-        <v>17.56333333333333</v>
+        <v>17.21333333333333</v>
       </c>
       <c r="F831">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="G831" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="832">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -25890,13 +25890,13 @@
         </is>
       </c>
       <c r="E832">
-        <v>13.59333333333333</v>
+        <v>8.99</v>
       </c>
       <c r="F832">
-        <v>51.21</v>
+        <v>0</v>
       </c>
       <c r="G832" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="833">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -25921,19 +25921,19 @@
         </is>
       </c>
       <c r="E833">
-        <v>7.443333333333333</v>
+        <v>7.706666666666666</v>
       </c>
       <c r="F833">
-        <v>-3.42</v>
+        <v>-0.73</v>
       </c>
       <c r="G833" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -25952,16 +25952,19 @@
         </is>
       </c>
       <c r="E834">
-        <v>3.716666666666666</v>
+        <v>3.6</v>
+      </c>
+      <c r="F834">
+        <v>-2.44</v>
       </c>
       <c r="G834" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -25971,7 +25974,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -25980,16 +25983,19 @@
         </is>
       </c>
       <c r="E835">
-        <v>3.753333333333333</v>
+        <v>4.17</v>
+      </c>
+      <c r="F835">
+        <v>0.48</v>
       </c>
       <c r="G835" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -25999,7 +26005,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -26008,16 +26014,19 @@
         </is>
       </c>
       <c r="E836">
-        <v>6.183333333333334</v>
+        <v>4.99</v>
+      </c>
+      <c r="F836">
+        <v>-5.67</v>
       </c>
       <c r="G836" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -26027,7 +26036,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -26036,16 +26045,19 @@
         </is>
       </c>
       <c r="E837">
-        <v>4.26</v>
+        <v>8.99</v>
+      </c>
+      <c r="F837">
+        <v>20.56</v>
       </c>
       <c r="G837" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -26055,7 +26067,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -26064,16 +26076,19 @@
         </is>
       </c>
       <c r="E838">
-        <v>28.61</v>
+        <v>28.76666666666667</v>
+      </c>
+      <c r="F838">
+        <v>-8.31</v>
       </c>
       <c r="G838" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -26083,7 +26098,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -26092,16 +26107,19 @@
         </is>
       </c>
       <c r="E839">
-        <v>52.79333333333334</v>
+        <v>50.02666666666666</v>
+      </c>
+      <c r="F839">
+        <v>2.77</v>
       </c>
       <c r="G839" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -26111,7 +26129,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -26120,16 +26138,19 @@
         </is>
       </c>
       <c r="E840">
-        <v>3.406666666666667</v>
+        <v>3.506666666666666</v>
+      </c>
+      <c r="F840">
+        <v>-6.74</v>
       </c>
       <c r="G840" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -26139,7 +26160,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -26148,16 +26169,19 @@
         </is>
       </c>
       <c r="E841">
-        <v>5.123333333333333</v>
+        <v>5.896666666666667</v>
+      </c>
+      <c r="F841">
+        <v>0.11</v>
       </c>
       <c r="G841" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -26167,7 +26191,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -26176,16 +26200,19 @@
         </is>
       </c>
       <c r="E842">
-        <v>3.8</v>
+        <v>5.656666666666667</v>
+      </c>
+      <c r="F842">
+        <v>-1.74</v>
       </c>
       <c r="G842" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -26195,7 +26222,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -26204,16 +26231,19 @@
         </is>
       </c>
       <c r="E843">
-        <v>26.67333333333333</v>
+        <v>28.66666666666667</v>
+      </c>
+      <c r="F843">
+        <v>-0.19</v>
       </c>
       <c r="G843" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -26223,7 +26253,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -26232,16 +26262,19 @@
         </is>
       </c>
       <c r="E844">
-        <v>13.35333333333333</v>
+        <v>17.56333333333333</v>
+      </c>
+      <c r="F844">
+        <v>2.03</v>
       </c>
       <c r="G844" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -26251,7 +26284,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -26260,16 +26293,19 @@
         </is>
       </c>
       <c r="E845">
-        <v>12.98</v>
+        <v>13.59333333333333</v>
+      </c>
+      <c r="F845">
+        <v>51.21</v>
       </c>
       <c r="G845" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -26279,7 +26315,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -26288,10 +26324,13 @@
         </is>
       </c>
       <c r="E846">
-        <v>9.199999999999999</v>
+        <v>7.443333333333333</v>
+      </c>
+      <c r="F846">
+        <v>-3.42</v>
       </c>
       <c r="G846" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="847">
@@ -26307,7 +26346,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -26316,13 +26355,10 @@
         </is>
       </c>
       <c r="E847">
-        <v>3.44</v>
-      </c>
-      <c r="F847">
-        <v>-7.44</v>
+        <v>3.716666666666666</v>
       </c>
       <c r="G847" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="848">
@@ -26338,7 +26374,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -26347,13 +26383,10 @@
         </is>
       </c>
       <c r="E848">
-        <v>4.21</v>
-      </c>
-      <c r="F848">
-        <v>12.17</v>
+        <v>3.753333333333333</v>
       </c>
       <c r="G848" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="849">
@@ -26369,7 +26402,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -26378,13 +26411,10 @@
         </is>
       </c>
       <c r="E849">
-        <v>5.24</v>
-      </c>
-      <c r="F849">
-        <v>-15.26</v>
+        <v>6.183333333333334</v>
       </c>
       <c r="G849" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="850">
@@ -26400,7 +26430,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -26409,13 +26439,10 @@
         </is>
       </c>
       <c r="E850">
-        <v>4.79</v>
-      </c>
-      <c r="F850">
-        <v>12.44</v>
+        <v>4.26</v>
       </c>
       <c r="G850" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="851">
@@ -26431,7 +26458,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -26440,13 +26467,10 @@
         </is>
       </c>
       <c r="E851">
-        <v>27.24</v>
-      </c>
-      <c r="F851">
-        <v>-4.79</v>
+        <v>28.61</v>
       </c>
       <c r="G851" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="852">
@@ -26462,7 +26486,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -26471,13 +26495,10 @@
         </is>
       </c>
       <c r="E852">
-        <v>47.93</v>
-      </c>
-      <c r="F852">
-        <v>-9.210000000000001</v>
+        <v>52.79333333333334</v>
       </c>
       <c r="G852" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="853">
@@ -26493,7 +26514,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -26502,13 +26523,10 @@
         </is>
       </c>
       <c r="E853">
-        <v>3.59</v>
-      </c>
-      <c r="F853">
-        <v>5.38</v>
+        <v>3.406666666666667</v>
       </c>
       <c r="G853" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="854">
@@ -26524,7 +26542,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -26533,13 +26551,10 @@
         </is>
       </c>
       <c r="E854">
-        <v>4.890000000000001</v>
-      </c>
-      <c r="F854">
-        <v>-4.55</v>
+        <v>5.123333333333333</v>
       </c>
       <c r="G854" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="855">
@@ -26555,7 +26570,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -26564,13 +26579,10 @@
         </is>
       </c>
       <c r="E855">
-        <v>4.75</v>
-      </c>
-      <c r="F855">
-        <v>25</v>
+        <v>3.8</v>
       </c>
       <c r="G855" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="856">
@@ -26586,7 +26598,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -26595,13 +26607,10 @@
         </is>
       </c>
       <c r="E856">
-        <v>20.54</v>
-      </c>
-      <c r="F856">
-        <v>-22.99</v>
+        <v>26.67333333333333</v>
       </c>
       <c r="G856" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="857">
@@ -26617,7 +26626,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -26626,13 +26635,10 @@
         </is>
       </c>
       <c r="E857">
-        <v>13.4</v>
-      </c>
-      <c r="F857">
-        <v>0.35</v>
+        <v>13.35333333333333</v>
       </c>
       <c r="G857" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="858">
@@ -26648,7 +26654,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -26657,13 +26663,10 @@
         </is>
       </c>
       <c r="E858">
-        <v>5.985</v>
-      </c>
-      <c r="F858">
-        <v>-53.89</v>
+        <v>12.98</v>
       </c>
       <c r="G858" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="859">
@@ -26679,7 +26682,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -26688,19 +26691,16 @@
         </is>
       </c>
       <c r="E859">
-        <v>7.725</v>
-      </c>
-      <c r="F859">
-        <v>-16.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G859" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -26710,7 +26710,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -26719,16 +26719,19 @@
         </is>
       </c>
       <c r="E860">
-        <v>3.3</v>
+        <v>3.44</v>
+      </c>
+      <c r="F860">
+        <v>-7.44</v>
       </c>
       <c r="G860" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -26738,7 +26741,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -26747,16 +26750,19 @@
         </is>
       </c>
       <c r="E861">
-        <v>4.353333333333333</v>
+        <v>4.21</v>
+      </c>
+      <c r="F861">
+        <v>12.17</v>
       </c>
       <c r="G861" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -26766,7 +26772,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -26775,16 +26781,19 @@
         </is>
       </c>
       <c r="E862">
-        <v>5.976666666666667</v>
+        <v>5.24</v>
+      </c>
+      <c r="F862">
+        <v>-15.26</v>
       </c>
       <c r="G862" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -26794,7 +26803,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -26803,16 +26812,19 @@
         </is>
       </c>
       <c r="E863">
-        <v>4.78</v>
+        <v>4.79</v>
+      </c>
+      <c r="F863">
+        <v>12.44</v>
       </c>
       <c r="G863" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -26822,7 +26834,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -26831,16 +26843,19 @@
         </is>
       </c>
       <c r="E864">
-        <v>27.43</v>
+        <v>27.24</v>
+      </c>
+      <c r="F864">
+        <v>-4.79</v>
       </c>
       <c r="G864" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -26850,7 +26865,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -26859,16 +26874,19 @@
         </is>
       </c>
       <c r="E865">
-        <v>44.9</v>
+        <v>47.93</v>
+      </c>
+      <c r="F865">
+        <v>-9.210000000000001</v>
       </c>
       <c r="G865" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -26878,7 +26896,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -26887,16 +26905,19 @@
         </is>
       </c>
       <c r="E866">
-        <v>3.326666666666667</v>
+        <v>3.59</v>
+      </c>
+      <c r="F866">
+        <v>5.38</v>
       </c>
       <c r="G866" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -26906,7 +26927,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -26915,16 +26936,19 @@
         </is>
       </c>
       <c r="E867">
-        <v>5.3</v>
+        <v>4.890000000000001</v>
+      </c>
+      <c r="F867">
+        <v>-4.55</v>
       </c>
       <c r="G867" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -26934,7 +26958,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -26943,16 +26967,19 @@
         </is>
       </c>
       <c r="E868">
-        <v>3.806666666666667</v>
+        <v>4.75</v>
+      </c>
+      <c r="F868">
+        <v>25</v>
       </c>
       <c r="G868" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -26962,7 +26989,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -26971,16 +26998,19 @@
         </is>
       </c>
       <c r="E869">
-        <v>27.32333333333333</v>
+        <v>20.54</v>
+      </c>
+      <c r="F869">
+        <v>-22.99</v>
       </c>
       <c r="G869" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -26990,7 +27020,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -26999,16 +27029,19 @@
         </is>
       </c>
       <c r="E870">
-        <v>15.56666666666667</v>
+        <v>13.4</v>
+      </c>
+      <c r="F870">
+        <v>0.35</v>
       </c>
       <c r="G870" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -27018,7 +27051,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -27027,16 +27060,19 @@
         </is>
       </c>
       <c r="E871">
-        <v>10.32</v>
+        <v>5.985</v>
+      </c>
+      <c r="F871">
+        <v>-53.89</v>
       </c>
       <c r="G871" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -27046,7 +27082,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -27055,10 +27091,13 @@
         </is>
       </c>
       <c r="E872">
-        <v>7.836666666666667</v>
+        <v>7.725</v>
+      </c>
+      <c r="F872">
+        <v>-16.03</v>
       </c>
       <c r="G872" s="2">
-        <v>46082</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="873">
@@ -27074,7 +27113,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -27083,13 +27122,10 @@
         </is>
       </c>
       <c r="E873">
-        <v>3.39</v>
-      </c>
-      <c r="F873">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="G873" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="874">
@@ -27105,7 +27141,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -27114,13 +27150,10 @@
         </is>
       </c>
       <c r="E874">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F874">
-        <v>2.07</v>
+        <v>4.353333333333333</v>
       </c>
       <c r="G874" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="875">
@@ -27136,7 +27169,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -27145,13 +27178,10 @@
         </is>
       </c>
       <c r="E875">
-        <v>6.56</v>
-      </c>
-      <c r="F875">
-        <v>9.76</v>
+        <v>5.976666666666667</v>
       </c>
       <c r="G875" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="876">
@@ -27167,7 +27197,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -27176,13 +27206,10 @@
         </is>
       </c>
       <c r="E876">
-        <v>4.98</v>
-      </c>
-      <c r="F876">
-        <v>4.18</v>
+        <v>4.78</v>
       </c>
       <c r="G876" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="877">
@@ -27198,7 +27225,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -27207,13 +27234,10 @@
         </is>
       </c>
       <c r="E877">
-        <v>27.95333333333333</v>
-      </c>
-      <c r="F877">
-        <v>1.91</v>
+        <v>27.43</v>
       </c>
       <c r="G877" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="878">
@@ -27229,7 +27253,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -27238,13 +27262,10 @@
         </is>
       </c>
       <c r="E878">
-        <v>55.32666666666667</v>
-      </c>
-      <c r="F878">
-        <v>23.22</v>
+        <v>44.9</v>
       </c>
       <c r="G878" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="879">
@@ -27260,7 +27281,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -27269,13 +27290,10 @@
         </is>
       </c>
       <c r="E879">
-        <v>3.45</v>
-      </c>
-      <c r="F879">
-        <v>3.71</v>
+        <v>3.326666666666667</v>
       </c>
       <c r="G879" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="880">
@@ -27291,7 +27309,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -27300,13 +27318,10 @@
         </is>
       </c>
       <c r="E880">
-        <v>5.376666666666667</v>
-      </c>
-      <c r="F880">
-        <v>1.45</v>
+        <v>5.3</v>
       </c>
       <c r="G880" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="881">
@@ -27322,7 +27337,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -27331,13 +27346,10 @@
         </is>
       </c>
       <c r="E881">
-        <v>4.22</v>
-      </c>
-      <c r="F881">
-        <v>10.86</v>
+        <v>3.806666666666667</v>
       </c>
       <c r="G881" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="882">
@@ -27353,7 +27365,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -27362,13 +27374,10 @@
         </is>
       </c>
       <c r="E882">
-        <v>28.10333333333333</v>
-      </c>
-      <c r="F882">
-        <v>2.85</v>
+        <v>27.32333333333333</v>
       </c>
       <c r="G882" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="883">
@@ -27384,7 +27393,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -27393,13 +27402,10 @@
         </is>
       </c>
       <c r="E883">
-        <v>15.9</v>
-      </c>
-      <c r="F883">
-        <v>2.14</v>
+        <v>15.56666666666667</v>
       </c>
       <c r="G883" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="884">
@@ -27415,7 +27421,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -27424,13 +27430,10 @@
         </is>
       </c>
       <c r="E884">
-        <v>10.65333333333333</v>
-      </c>
-      <c r="F884">
-        <v>3.23</v>
+        <v>10.32</v>
       </c>
       <c r="G884" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="885">
@@ -27446,7 +27449,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -27455,13 +27458,10 @@
         </is>
       </c>
       <c r="E885">
-        <v>7.993333333333333</v>
-      </c>
-      <c r="F885">
-        <v>2</v>
+        <v>7.836666666666667</v>
       </c>
       <c r="G885" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="886">
@@ -27477,7 +27477,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -27486,13 +27486,13 @@
         </is>
       </c>
       <c r="E886">
-        <v>3.206666666666667</v>
+        <v>3.39</v>
       </c>
       <c r="F886">
-        <v>-5.41</v>
+        <v>2.73</v>
       </c>
       <c r="G886" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="887">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -27517,13 +27517,13 @@
         </is>
       </c>
       <c r="E887">
-        <v>3.663333333333334</v>
+        <v>4.443333333333333</v>
       </c>
       <c r="F887">
-        <v>-17.55</v>
+        <v>2.07</v>
       </c>
       <c r="G887" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="888">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="E888">
-        <v>5.49</v>
+        <v>6.56</v>
       </c>
       <c r="F888">
-        <v>-16.31</v>
+        <v>9.76</v>
       </c>
       <c r="G888" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="889">
@@ -27570,7 +27570,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -27579,13 +27579,13 @@
         </is>
       </c>
       <c r="E889">
-        <v>4.853333333333333</v>
+        <v>4.98</v>
       </c>
       <c r="F889">
-        <v>-2.54</v>
+        <v>4.18</v>
       </c>
       <c r="G889" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="890">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -27610,13 +27610,13 @@
         </is>
       </c>
       <c r="E890">
-        <v>23.21</v>
+        <v>27.95333333333333</v>
       </c>
       <c r="F890">
-        <v>-16.97</v>
+        <v>1.91</v>
       </c>
       <c r="G890" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="891">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -27641,13 +27641,13 @@
         </is>
       </c>
       <c r="E891">
-        <v>49.02666666666666</v>
+        <v>55.32666666666667</v>
       </c>
       <c r="F891">
-        <v>-11.39</v>
+        <v>23.22</v>
       </c>
       <c r="G891" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="892">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="E892">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="F892">
-        <v>4.64</v>
+        <v>3.71</v>
       </c>
       <c r="G892" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="893">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -27703,13 +27703,13 @@
         </is>
       </c>
       <c r="E893">
-        <v>5.846666666666667</v>
+        <v>5.376666666666667</v>
       </c>
       <c r="F893">
-        <v>8.74</v>
+        <v>1.45</v>
       </c>
       <c r="G893" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="894">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="E894">
-        <v>4.916666666666667</v>
+        <v>4.22</v>
       </c>
       <c r="F894">
-        <v>16.51</v>
+        <v>10.86</v>
       </c>
       <c r="G894" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="895">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -27765,13 +27765,13 @@
         </is>
       </c>
       <c r="E895">
-        <v>24.68666666666667</v>
+        <v>28.10333333333333</v>
       </c>
       <c r="F895">
-        <v>-12.16</v>
+        <v>2.85</v>
       </c>
       <c r="G895" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="896">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -27796,13 +27796,13 @@
         </is>
       </c>
       <c r="E896">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="F896">
-        <v>-12.58</v>
+        <v>2.14</v>
       </c>
       <c r="G896" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="897">
@@ -27818,7 +27818,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -27827,13 +27827,13 @@
         </is>
       </c>
       <c r="E897">
-        <v>5.816666666666667</v>
+        <v>10.65333333333333</v>
       </c>
       <c r="F897">
-        <v>-45.4</v>
+        <v>3.23</v>
       </c>
       <c r="G897" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="898">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -27858,19 +27858,19 @@
         </is>
       </c>
       <c r="E898">
-        <v>7.043333333333333</v>
+        <v>7.993333333333333</v>
       </c>
       <c r="F898">
-        <v>-11.88</v>
+        <v>2</v>
       </c>
       <c r="G898" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -27889,16 +27889,19 @@
         </is>
       </c>
       <c r="E899">
-        <v>3.393333333333334</v>
+        <v>3.206666666666667</v>
+      </c>
+      <c r="F899">
+        <v>-5.41</v>
       </c>
       <c r="G899" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -27908,7 +27911,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -27917,16 +27920,19 @@
         </is>
       </c>
       <c r="E900">
-        <v>3.69</v>
+        <v>3.663333333333334</v>
+      </c>
+      <c r="F900">
+        <v>-17.55</v>
       </c>
       <c r="G900" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -27936,7 +27942,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -27945,16 +27951,19 @@
         </is>
       </c>
       <c r="E901">
-        <v>6.066666666666666</v>
+        <v>5.49</v>
+      </c>
+      <c r="F901">
+        <v>-16.31</v>
       </c>
       <c r="G901" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -27964,7 +27973,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -27973,16 +27982,19 @@
         </is>
       </c>
       <c r="E902">
-        <v>3.826666666666667</v>
+        <v>4.853333333333333</v>
+      </c>
+      <c r="F902">
+        <v>-2.54</v>
       </c>
       <c r="G902" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -27992,7 +28004,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -28001,16 +28013,19 @@
         </is>
       </c>
       <c r="E903">
-        <v>28.97</v>
+        <v>23.21</v>
+      </c>
+      <c r="F903">
+        <v>-16.97</v>
       </c>
       <c r="G903" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -28020,7 +28035,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -28029,16 +28044,19 @@
         </is>
       </c>
       <c r="E904">
-        <v>43.38</v>
+        <v>49.02666666666666</v>
+      </c>
+      <c r="F904">
+        <v>-11.39</v>
       </c>
       <c r="G904" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -28048,7 +28066,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -28057,16 +28075,19 @@
         </is>
       </c>
       <c r="E905">
-        <v>3.7</v>
+        <v>3.61</v>
+      </c>
+      <c r="F905">
+        <v>4.64</v>
       </c>
       <c r="G905" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -28076,7 +28097,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -28085,16 +28106,19 @@
         </is>
       </c>
       <c r="E906">
-        <v>4.903333333333333</v>
+        <v>5.846666666666667</v>
+      </c>
+      <c r="F906">
+        <v>8.74</v>
       </c>
       <c r="G906" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -28104,7 +28128,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -28113,16 +28137,19 @@
         </is>
       </c>
       <c r="E907">
-        <v>3.783333333333333</v>
+        <v>4.916666666666667</v>
+      </c>
+      <c r="F907">
+        <v>16.51</v>
       </c>
       <c r="G907" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -28132,7 +28159,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -28141,16 +28168,19 @@
         </is>
       </c>
       <c r="E908">
-        <v>23.95333333333333</v>
+        <v>24.68666666666667</v>
+      </c>
+      <c r="F908">
+        <v>-12.16</v>
       </c>
       <c r="G908" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -28160,7 +28190,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -28169,16 +28199,19 @@
         </is>
       </c>
       <c r="E909">
-        <v>14.2</v>
+        <v>13.9</v>
+      </c>
+      <c r="F909">
+        <v>-12.58</v>
       </c>
       <c r="G909" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -28188,7 +28221,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -28197,16 +28230,19 @@
         </is>
       </c>
       <c r="E910">
-        <v>8.130000000000001</v>
+        <v>5.816666666666667</v>
+      </c>
+      <c r="F910">
+        <v>-45.4</v>
       </c>
       <c r="G910" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -28216,7 +28252,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -28225,16 +28261,19 @@
         </is>
       </c>
       <c r="E911">
-        <v>6.693333333333333</v>
+        <v>7.043333333333333</v>
+      </c>
+      <c r="F911">
+        <v>-11.88</v>
       </c>
       <c r="G911" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -28244,7 +28283,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -28253,16 +28292,19 @@
         </is>
       </c>
       <c r="E912">
-        <v>2.705</v>
+        <v>3.406666666666667</v>
+      </c>
+      <c r="F912">
+        <v>6.24</v>
       </c>
       <c r="G912" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -28272,7 +28314,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -28281,16 +28323,19 @@
         </is>
       </c>
       <c r="E913">
-        <v>3.72</v>
+        <v>3.643333333333333</v>
+      </c>
+      <c r="F913">
+        <v>-0.55</v>
       </c>
       <c r="G913" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -28300,7 +28345,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -28309,16 +28354,19 @@
         </is>
       </c>
       <c r="E914">
-        <v>5.140000000000001</v>
+        <v>5.49</v>
+      </c>
+      <c r="F914">
+        <v>0</v>
       </c>
       <c r="G914" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -28328,7 +28376,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -28337,16 +28385,19 @@
         </is>
       </c>
       <c r="E915">
-        <v>4.390000000000001</v>
+        <v>4.98</v>
+      </c>
+      <c r="F915">
+        <v>2.61</v>
       </c>
       <c r="G915" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -28356,7 +28407,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -28365,16 +28416,19 @@
         </is>
       </c>
       <c r="E916">
-        <v>48.94</v>
+        <v>22.64333333333333</v>
+      </c>
+      <c r="F916">
+        <v>-2.44</v>
       </c>
       <c r="G916" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -28384,7 +28438,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -28393,16 +28447,19 @@
         </is>
       </c>
       <c r="E917">
-        <v>55.07</v>
+        <v>47.77333333333333</v>
+      </c>
+      <c r="F917">
+        <v>-2.56</v>
       </c>
       <c r="G917" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -28412,7 +28469,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -28421,16 +28478,19 @@
         </is>
       </c>
       <c r="E918">
-        <v>3.12</v>
+        <v>3.583333333333333</v>
+      </c>
+      <c r="F918">
+        <v>-0.74</v>
       </c>
       <c r="G918" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -28440,7 +28500,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -28449,16 +28509,19 @@
         </is>
       </c>
       <c r="E919">
-        <v>4.84</v>
+        <v>6.086666666666667</v>
+      </c>
+      <c r="F919">
+        <v>4.1</v>
       </c>
       <c r="G919" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -28468,7 +28531,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -28477,16 +28540,19 @@
         </is>
       </c>
       <c r="E920">
-        <v>4.234999999999999</v>
+        <v>4.833333333333333</v>
+      </c>
+      <c r="F920">
+        <v>-1.69</v>
       </c>
       <c r="G920" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -28496,7 +28562,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -28505,16 +28571,19 @@
         </is>
       </c>
       <c r="E921">
-        <v>13.96</v>
+        <v>25.47</v>
+      </c>
+      <c r="F921">
+        <v>3.17</v>
       </c>
       <c r="G921" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -28524,7 +28593,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -28533,16 +28602,19 @@
         </is>
       </c>
       <c r="E922">
-        <v>14.94</v>
+        <v>14.23333333333333</v>
+      </c>
+      <c r="F922">
+        <v>2.4</v>
       </c>
       <c r="G922" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -28552,7 +28624,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -28561,16 +28633,19 @@
         </is>
       </c>
       <c r="E923">
-        <v>8.24</v>
+        <v>11.98</v>
+      </c>
+      <c r="F923">
+        <v>105.96</v>
       </c>
       <c r="G923" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -28580,7 +28655,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -28589,16 +28664,19 @@
         </is>
       </c>
       <c r="E924">
-        <v>8.460000000000001</v>
+        <v>7.123333333333333</v>
+      </c>
+      <c r="F924">
+        <v>1.14</v>
       </c>
       <c r="G924" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -28617,7 +28695,7 @@
         </is>
       </c>
       <c r="E925">
-        <v>2.633333333333333</v>
+        <v>3.393333333333334</v>
       </c>
       <c r="G925" s="2">
         <v>46113</v>
@@ -28626,7 +28704,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -28645,7 +28723,7 @@
         </is>
       </c>
       <c r="E926">
-        <v>4.17</v>
+        <v>3.69</v>
       </c>
       <c r="G926" s="2">
         <v>46113</v>
@@ -28654,7 +28732,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -28673,7 +28751,7 @@
         </is>
       </c>
       <c r="E927">
-        <v>5.29</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="G927" s="2">
         <v>46113</v>
@@ -28682,7 +28760,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -28701,7 +28779,7 @@
         </is>
       </c>
       <c r="E928">
-        <v>5.09</v>
+        <v>3.826666666666667</v>
       </c>
       <c r="G928" s="2">
         <v>46113</v>
@@ -28710,7 +28788,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -28729,7 +28807,7 @@
         </is>
       </c>
       <c r="E929">
-        <v>52.37</v>
+        <v>28.97</v>
       </c>
       <c r="G929" s="2">
         <v>46113</v>
@@ -28738,7 +28816,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -28757,7 +28835,7 @@
         </is>
       </c>
       <c r="E930">
-        <v>60.96666666666667</v>
+        <v>43.38</v>
       </c>
       <c r="G930" s="2">
         <v>46113</v>
@@ -28766,7 +28844,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -28785,7 +28863,7 @@
         </is>
       </c>
       <c r="E931">
-        <v>3.836666666666666</v>
+        <v>3.7</v>
       </c>
       <c r="G931" s="2">
         <v>46113</v>
@@ -28794,7 +28872,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -28813,7 +28891,7 @@
         </is>
       </c>
       <c r="E932">
-        <v>4.89</v>
+        <v>4.903333333333333</v>
       </c>
       <c r="G932" s="2">
         <v>46113</v>
@@ -28822,7 +28900,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -28841,7 +28919,7 @@
         </is>
       </c>
       <c r="E933">
-        <v>4.426666666666667</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="G933" s="2">
         <v>46113</v>
@@ -28850,7 +28928,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -28869,7 +28947,7 @@
         </is>
       </c>
       <c r="E934">
-        <v>16.92333333333333</v>
+        <v>23.95333333333333</v>
       </c>
       <c r="G934" s="2">
         <v>46113</v>
@@ -28878,7 +28956,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -28897,7 +28975,7 @@
         </is>
       </c>
       <c r="E935">
-        <v>17.86</v>
+        <v>14.2</v>
       </c>
       <c r="G935" s="2">
         <v>46113</v>
@@ -28906,7 +28984,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -28925,7 +29003,7 @@
         </is>
       </c>
       <c r="E936">
-        <v>8.933333333333334</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G936" s="2">
         <v>46113</v>
@@ -28934,7 +29012,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -28953,7 +29031,7 @@
         </is>
       </c>
       <c r="E937">
-        <v>8.673333333333334</v>
+        <v>6.693333333333333</v>
       </c>
       <c r="G937" s="2">
         <v>46113</v>
@@ -28962,7 +29040,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -28972,7 +29050,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -28981,19 +29059,16 @@
         </is>
       </c>
       <c r="E938">
-        <v>3.256666666666667</v>
-      </c>
-      <c r="F938">
-        <v>23.67</v>
+        <v>2.705</v>
       </c>
       <c r="G938" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -29003,7 +29078,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -29012,19 +29087,16 @@
         </is>
       </c>
       <c r="E939">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F939">
-        <v>6.55</v>
+        <v>3.72</v>
       </c>
       <c r="G939" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -29034,7 +29106,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -29043,19 +29115,16 @@
         </is>
       </c>
       <c r="E940">
-        <v>4.99</v>
-      </c>
-      <c r="F940">
-        <v>-5.67</v>
+        <v>5.140000000000001</v>
       </c>
       <c r="G940" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -29065,7 +29134,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -29074,19 +29143,16 @@
         </is>
       </c>
       <c r="E941">
-        <v>6.293333333333334</v>
-      </c>
-      <c r="F941">
-        <v>23.64</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="G941" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -29096,7 +29162,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -29105,19 +29171,16 @@
         </is>
       </c>
       <c r="E942">
-        <v>23.41333333333333</v>
-      </c>
-      <c r="F942">
-        <v>-55.29</v>
+        <v>48.94</v>
       </c>
       <c r="G942" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -29127,7 +29190,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -29136,19 +29199,16 @@
         </is>
       </c>
       <c r="E943">
-        <v>48.88</v>
-      </c>
-      <c r="F943">
-        <v>-19.83</v>
+        <v>55.07</v>
       </c>
       <c r="G943" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -29158,7 +29218,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -29167,19 +29227,16 @@
         </is>
       </c>
       <c r="E944">
-        <v>3.996666666666667</v>
-      </c>
-      <c r="F944">
-        <v>4.17</v>
+        <v>3.12</v>
       </c>
       <c r="G944" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -29189,7 +29246,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -29198,19 +29255,16 @@
         </is>
       </c>
       <c r="E945">
-        <v>6.433333333333334</v>
-      </c>
-      <c r="F945">
-        <v>31.56</v>
+        <v>4.84</v>
       </c>
       <c r="G945" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -29220,7 +29274,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -29229,19 +29283,16 @@
         </is>
       </c>
       <c r="E946">
-        <v>5.12</v>
-      </c>
-      <c r="F946">
-        <v>15.66</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="G946" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -29251,7 +29302,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -29260,19 +29311,16 @@
         </is>
       </c>
       <c r="E947">
-        <v>31.21666666666667</v>
-      </c>
-      <c r="F947">
-        <v>84.45999999999999</v>
+        <v>13.96</v>
       </c>
       <c r="G947" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -29282,7 +29330,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -29291,19 +29339,16 @@
         </is>
       </c>
       <c r="E948">
-        <v>15.26</v>
-      </c>
-      <c r="F948">
-        <v>-14.56</v>
+        <v>14.94</v>
       </c>
       <c r="G948" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -29313,7 +29358,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -29322,19 +29367,16 @@
         </is>
       </c>
       <c r="E949">
-        <v>5.76</v>
-      </c>
-      <c r="F949">
-        <v>-35.52</v>
+        <v>8.24</v>
       </c>
       <c r="G949" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
@@ -29344,7 +29386,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -29353,13 +29395,10 @@
         </is>
       </c>
       <c r="E950">
-        <v>7.956666666666667</v>
-      </c>
-      <c r="F950">
-        <v>-8.26</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G950" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="951">
@@ -29375,7 +29414,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -29384,13 +29423,10 @@
         </is>
       </c>
       <c r="E951">
-        <v>3.256666666666667</v>
-      </c>
-      <c r="F951">
-        <v>0</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="G951" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="952">
@@ -29406,7 +29442,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -29415,13 +29451,10 @@
         </is>
       </c>
       <c r="E952">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F952">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="G952" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="953">
@@ -29437,7 +29470,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -29446,13 +29479,10 @@
         </is>
       </c>
       <c r="E953">
-        <v>4.99</v>
-      </c>
-      <c r="F953">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="G953" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="954">
@@ -29468,7 +29498,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -29477,13 +29507,10 @@
         </is>
       </c>
       <c r="E954">
-        <v>5.96</v>
-      </c>
-      <c r="F954">
-        <v>-5.3</v>
+        <v>5.09</v>
       </c>
       <c r="G954" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="955">
@@ -29499,7 +29526,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -29508,13 +29535,10 @@
         </is>
       </c>
       <c r="E955">
-        <v>22.8</v>
-      </c>
-      <c r="F955">
-        <v>-2.62</v>
+        <v>52.37</v>
       </c>
       <c r="G955" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="956">
@@ -29530,7 +29554,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -29539,13 +29563,10 @@
         </is>
       </c>
       <c r="E956">
-        <v>48.27333333333333</v>
-      </c>
-      <c r="F956">
-        <v>-1.24</v>
+        <v>60.96666666666667</v>
       </c>
       <c r="G956" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="957">
@@ -29561,7 +29582,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -29570,13 +29591,10 @@
         </is>
       </c>
       <c r="E957">
-        <v>3.996666666666667</v>
-      </c>
-      <c r="F957">
-        <v>0</v>
+        <v>3.836666666666666</v>
       </c>
       <c r="G957" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="958">
@@ -29592,7 +29610,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -29601,13 +29619,10 @@
         </is>
       </c>
       <c r="E958">
-        <v>6.433333333333334</v>
-      </c>
-      <c r="F958">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="G958" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="959">
@@ -29623,7 +29638,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -29632,13 +29647,10 @@
         </is>
       </c>
       <c r="E959">
-        <v>5.07</v>
-      </c>
-      <c r="F959">
-        <v>-0.98</v>
+        <v>4.426666666666667</v>
       </c>
       <c r="G959" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="960">
@@ -29654,7 +29666,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -29663,13 +29675,10 @@
         </is>
       </c>
       <c r="E960">
-        <v>30.76333333333333</v>
-      </c>
-      <c r="F960">
-        <v>-1.45</v>
+        <v>16.92333333333333</v>
       </c>
       <c r="G960" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="961">
@@ -29685,7 +29694,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -29694,13 +29703,10 @@
         </is>
       </c>
       <c r="E961">
-        <v>15.26</v>
-      </c>
-      <c r="F961">
-        <v>0</v>
+        <v>17.86</v>
       </c>
       <c r="G961" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="962">
@@ -29716,7 +29722,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -29725,13 +29731,10 @@
         </is>
       </c>
       <c r="E962">
-        <v>5.49</v>
-      </c>
-      <c r="F962">
-        <v>-4.69</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="G962" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="963">
@@ -29747,7 +29750,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -29756,19 +29759,16 @@
         </is>
       </c>
       <c r="E963">
-        <v>7.906666666666667</v>
-      </c>
-      <c r="F963">
-        <v>-0.63</v>
+        <v>8.673333333333334</v>
       </c>
       <c r="G963" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -29787,7 +29787,10 @@
         </is>
       </c>
       <c r="E964">
-        <v>3.49</v>
+        <v>3.256666666666667</v>
+      </c>
+      <c r="F964">
+        <v>23.67</v>
       </c>
       <c r="G964" s="2">
         <v>46235</v>
@@ -29796,7 +29799,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -29815,7 +29818,10 @@
         </is>
       </c>
       <c r="E965">
-        <v>3.75</v>
+        <v>4.443333333333333</v>
+      </c>
+      <c r="F965">
+        <v>6.55</v>
       </c>
       <c r="G965" s="2">
         <v>46235</v>
@@ -29824,7 +29830,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -29843,7 +29849,10 @@
         </is>
       </c>
       <c r="E966">
-        <v>6.806666666666667</v>
+        <v>4.99</v>
+      </c>
+      <c r="F966">
+        <v>-5.67</v>
       </c>
       <c r="G966" s="2">
         <v>46235</v>
@@ -29852,7 +29861,7 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -29871,7 +29880,10 @@
         </is>
       </c>
       <c r="E967">
-        <v>6.46</v>
+        <v>6.293333333333334</v>
+      </c>
+      <c r="F967">
+        <v>23.64</v>
       </c>
       <c r="G967" s="2">
         <v>46235</v>
@@ -29880,7 +29892,7 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -29899,7 +29911,10 @@
         </is>
       </c>
       <c r="E968">
-        <v>23.12333333333333</v>
+        <v>23.41333333333333</v>
+      </c>
+      <c r="F968">
+        <v>-55.29</v>
       </c>
       <c r="G968" s="2">
         <v>46235</v>
@@ -29908,7 +29923,7 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -29927,7 +29942,10 @@
         </is>
       </c>
       <c r="E969">
-        <v>52.01666666666667</v>
+        <v>48.88</v>
+      </c>
+      <c r="F969">
+        <v>-19.83</v>
       </c>
       <c r="G969" s="2">
         <v>46235</v>
@@ -29936,7 +29954,7 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -29955,7 +29973,10 @@
         </is>
       </c>
       <c r="E970">
-        <v>3.386666666666667</v>
+        <v>3.996666666666667</v>
+      </c>
+      <c r="F970">
+        <v>4.17</v>
       </c>
       <c r="G970" s="2">
         <v>46235</v>
@@ -29964,7 +29985,7 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -29983,7 +30004,10 @@
         </is>
       </c>
       <c r="E971">
-        <v>5.926666666666667</v>
+        <v>6.433333333333334</v>
+      </c>
+      <c r="F971">
+        <v>31.56</v>
       </c>
       <c r="G971" s="2">
         <v>46235</v>
@@ -29992,7 +30016,7 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -30011,7 +30035,10 @@
         </is>
       </c>
       <c r="E972">
-        <v>4.91</v>
+        <v>5.12</v>
+      </c>
+      <c r="F972">
+        <v>15.66</v>
       </c>
       <c r="G972" s="2">
         <v>46235</v>
@@ -30020,7 +30047,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -30039,7 +30066,10 @@
         </is>
       </c>
       <c r="E973">
-        <v>26.97</v>
+        <v>31.21666666666667</v>
+      </c>
+      <c r="F973">
+        <v>84.45999999999999</v>
       </c>
       <c r="G973" s="2">
         <v>46235</v>
@@ -30048,7 +30078,7 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -30067,7 +30097,10 @@
         </is>
       </c>
       <c r="E974">
-        <v>15.68666666666667</v>
+        <v>15.26</v>
+      </c>
+      <c r="F974">
+        <v>-14.56</v>
       </c>
       <c r="G974" s="2">
         <v>46235</v>
@@ -30076,7 +30109,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -30095,7 +30128,10 @@
         </is>
       </c>
       <c r="E975">
-        <v>8.286666666666667</v>
+        <v>5.76</v>
+      </c>
+      <c r="F975">
+        <v>-35.52</v>
       </c>
       <c r="G975" s="2">
         <v>46235</v>
@@ -30104,7 +30140,7 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -30123,7 +30159,10 @@
         </is>
       </c>
       <c r="E976">
-        <v>7.036666666666667</v>
+        <v>7.956666666666667</v>
+      </c>
+      <c r="F976">
+        <v>-8.26</v>
       </c>
       <c r="G976" s="2">
         <v>46235</v>
@@ -30132,7 +30171,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -30151,10 +30190,10 @@
         </is>
       </c>
       <c r="E977">
-        <v>3.866666666666667</v>
+        <v>3.256666666666667</v>
       </c>
       <c r="F977">
-        <v>10.79</v>
+        <v>0</v>
       </c>
       <c r="G977" s="2">
         <v>46266</v>
@@ -30163,7 +30202,7 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -30182,10 +30221,10 @@
         </is>
       </c>
       <c r="E978">
-        <v>3.733333333333333</v>
+        <v>4.443333333333333</v>
       </c>
       <c r="F978">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="G978" s="2">
         <v>46266</v>
@@ -30194,7 +30233,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -30213,10 +30252,10 @@
         </is>
       </c>
       <c r="E979">
-        <v>6.6</v>
+        <v>4.99</v>
       </c>
       <c r="F979">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="G979" s="2">
         <v>46266</v>
@@ -30225,7 +30264,7 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -30244,10 +30283,10 @@
         </is>
       </c>
       <c r="E980">
-        <v>6.75</v>
+        <v>5.96</v>
       </c>
       <c r="F980">
-        <v>4.49</v>
+        <v>-5.3</v>
       </c>
       <c r="G980" s="2">
         <v>46266</v>
@@ -30256,7 +30295,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -30275,10 +30314,10 @@
         </is>
       </c>
       <c r="E981">
-        <v>23.51</v>
+        <v>22.8</v>
       </c>
       <c r="F981">
-        <v>1.67</v>
+        <v>-2.62</v>
       </c>
       <c r="G981" s="2">
         <v>46266</v>
@@ -30287,7 +30326,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -30306,10 +30345,10 @@
         </is>
       </c>
       <c r="E982">
-        <v>51.06</v>
+        <v>48.27333333333333</v>
       </c>
       <c r="F982">
-        <v>-1.84</v>
+        <v>-1.24</v>
       </c>
       <c r="G982" s="2">
         <v>46266</v>
@@ -30318,7 +30357,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -30337,10 +30376,10 @@
         </is>
       </c>
       <c r="E983">
-        <v>3.673333333333333</v>
+        <v>3.996666666666667</v>
       </c>
       <c r="F983">
-        <v>8.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="G983" s="2">
         <v>46266</v>
@@ -30349,7 +30388,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -30368,10 +30407,10 @@
         </is>
       </c>
       <c r="E984">
-        <v>6.32</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="F984">
-        <v>6.64</v>
+        <v>0</v>
       </c>
       <c r="G984" s="2">
         <v>46266</v>
@@ -30380,7 +30419,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -30399,10 +30438,10 @@
         </is>
       </c>
       <c r="E985">
-        <v>4.853333333333333</v>
+        <v>5.07</v>
       </c>
       <c r="F985">
-        <v>-1.15</v>
+        <v>-0.98</v>
       </c>
       <c r="G985" s="2">
         <v>46266</v>
@@ -30411,7 +30450,7 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -30430,10 +30469,10 @@
         </is>
       </c>
       <c r="E986">
-        <v>26.59333333333333</v>
+        <v>30.76333333333333</v>
       </c>
       <c r="F986">
-        <v>-1.4</v>
+        <v>-1.45</v>
       </c>
       <c r="G986" s="2">
         <v>46266</v>
@@ -30442,7 +30481,7 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -30461,10 +30500,10 @@
         </is>
       </c>
       <c r="E987">
-        <v>16.85</v>
+        <v>15.26</v>
       </c>
       <c r="F987">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="G987" s="2">
         <v>46266</v>
@@ -30473,7 +30512,7 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -30492,10 +30531,10 @@
         </is>
       </c>
       <c r="E988">
-        <v>13.12</v>
+        <v>5.49</v>
       </c>
       <c r="F988">
-        <v>58.33</v>
+        <v>-4.69</v>
       </c>
       <c r="G988" s="2">
         <v>46266</v>
@@ -30504,31 +30543,1565 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
+          <t>Timbó</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E989">
+        <v>7.906666666666667</v>
+      </c>
+      <c r="F989">
+        <v>-0.63</v>
+      </c>
+      <c r="G989" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
           <t>Balneário Camboriú</t>
         </is>
       </c>
-      <c r="B989" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C989" t="inlineStr">
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E990">
+        <v>3.49</v>
+      </c>
+      <c r="G990" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E991">
+        <v>3.75</v>
+      </c>
+      <c r="G991" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E992">
+        <v>6.806666666666667</v>
+      </c>
+      <c r="G992" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E993">
+        <v>6.46</v>
+      </c>
+      <c r="G993" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E994">
+        <v>23.12333333333333</v>
+      </c>
+      <c r="G994" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E995">
+        <v>52.01666666666667</v>
+      </c>
+      <c r="G995" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E996">
+        <v>3.386666666666667</v>
+      </c>
+      <c r="G996" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E997">
+        <v>5.926666666666667</v>
+      </c>
+      <c r="G997" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E998">
+        <v>4.91</v>
+      </c>
+      <c r="G998" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E999">
+        <v>26.97</v>
+      </c>
+      <c r="G999" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1000">
+        <v>15.68666666666667</v>
+      </c>
+      <c r="G1000" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1001">
+        <v>8.286666666666667</v>
+      </c>
+      <c r="G1001" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1002">
+        <v>7.036666666666667</v>
+      </c>
+      <c r="G1002" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
         <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="D989" t="inlineStr">
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1003">
+        <v>3.866666666666667</v>
+      </c>
+      <c r="F1003">
+        <v>10.79</v>
+      </c>
+      <c r="G1003" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1004">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="F1004">
+        <v>-0.44</v>
+      </c>
+      <c r="G1004" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1005">
+        <v>6.6</v>
+      </c>
+      <c r="F1005">
+        <v>-3.04</v>
+      </c>
+      <c r="G1005" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1006">
+        <v>6.75</v>
+      </c>
+      <c r="F1006">
+        <v>4.49</v>
+      </c>
+      <c r="G1006" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1007">
+        <v>23.51</v>
+      </c>
+      <c r="F1007">
+        <v>1.67</v>
+      </c>
+      <c r="G1007" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1008">
+        <v>51.06</v>
+      </c>
+      <c r="F1008">
+        <v>-1.84</v>
+      </c>
+      <c r="G1008" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1009">
+        <v>3.673333333333333</v>
+      </c>
+      <c r="F1009">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="G1009" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1010">
+        <v>6.32</v>
+      </c>
+      <c r="F1010">
+        <v>6.64</v>
+      </c>
+      <c r="G1010" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1011">
+        <v>4.853333333333333</v>
+      </c>
+      <c r="F1011">
+        <v>-1.15</v>
+      </c>
+      <c r="G1011" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1012">
+        <v>26.59333333333333</v>
+      </c>
+      <c r="F1012">
+        <v>-1.4</v>
+      </c>
+      <c r="G1012" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1013">
+        <v>16.85</v>
+      </c>
+      <c r="F1013">
+        <v>7.42</v>
+      </c>
+      <c r="G1013" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1014">
+        <v>13.12</v>
+      </c>
+      <c r="F1014">
+        <v>58.33</v>
+      </c>
+      <c r="G1014" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E989">
+      <c r="E1015">
         <v>7.166666666666667</v>
       </c>
-      <c r="F989">
+      <c r="F1015">
         <v>1.85</v>
       </c>
-      <c r="G989" s="2">
+      <c r="G1015" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1016">
+        <v>3.096666666666667</v>
+      </c>
+      <c r="G1016" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1017">
+        <v>3.763333333333333</v>
+      </c>
+      <c r="G1017" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1018">
+        <v>5.626666666666667</v>
+      </c>
+      <c r="G1018" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1019">
+        <v>5.49</v>
+      </c>
+      <c r="G1019" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1020">
+        <v>23.57333333333333</v>
+      </c>
+      <c r="G1020" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1021">
+        <v>53.28666666666666</v>
+      </c>
+      <c r="G1021" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1022">
+        <v>4.1</v>
+      </c>
+      <c r="G1022" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1023">
+        <v>6.54</v>
+      </c>
+      <c r="G1023" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1024">
+        <v>5.776666666666666</v>
+      </c>
+      <c r="G1024" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1025">
+        <v>28.01666666666667</v>
+      </c>
+      <c r="G1025" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1026">
+        <v>14.9</v>
+      </c>
+      <c r="G1026" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1027">
+        <v>9.120000000000001</v>
+      </c>
+      <c r="G1027" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1028">
+        <v>8.6</v>
+      </c>
+      <c r="G1028" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1029">
+        <v>3.596666666666667</v>
+      </c>
+      <c r="F1029">
+        <v>16.15</v>
+      </c>
+      <c r="G1029" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1030">
+        <v>3.693333333333333</v>
+      </c>
+      <c r="F1030">
+        <v>-1.86</v>
+      </c>
+      <c r="G1030" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1031">
+        <v>5.626666666666667</v>
+      </c>
+      <c r="F1031">
+        <v>0</v>
+      </c>
+      <c r="G1031" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1032">
+        <v>7.926666666666667</v>
+      </c>
+      <c r="F1032">
+        <v>44.38</v>
+      </c>
+      <c r="G1032" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1033">
+        <v>26.01333333333333</v>
+      </c>
+      <c r="F1033">
+        <v>10.35</v>
+      </c>
+      <c r="G1033" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1034">
+        <v>52.74</v>
+      </c>
+      <c r="F1034">
+        <v>-1.03</v>
+      </c>
+      <c r="G1034" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1035">
+        <v>3.88</v>
+      </c>
+      <c r="F1035">
+        <v>-5.37</v>
+      </c>
+      <c r="G1035" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1036">
+        <v>7.143333333333334</v>
+      </c>
+      <c r="F1036">
+        <v>9.23</v>
+      </c>
+      <c r="G1036" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1037">
+        <v>5.826666666666667</v>
+      </c>
+      <c r="F1037">
+        <v>0.87</v>
+      </c>
+      <c r="G1037" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1038">
+        <v>29.14666666666666</v>
+      </c>
+      <c r="F1038">
+        <v>4.03</v>
+      </c>
+      <c r="G1038" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1039">
+        <v>14.9</v>
+      </c>
+      <c r="F1039">
+        <v>0</v>
+      </c>
+      <c r="G1039" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1040">
+        <v>12.32</v>
+      </c>
+      <c r="F1040">
+        <v>35.09</v>
+      </c>
+      <c r="G1040" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1041">
+        <v>8.91</v>
+      </c>
+      <c r="F1041">
+        <v>3.6</v>
+      </c>
+      <c r="G1041" s="2">
         <v>46266</v>
       </c>
     </row>

--- a/PRECOS.xlsx
+++ b/PRECOS.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1041"/>
+  <dimension ref="A1:G1054"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="E730">
-        <v>3.45</v>
+        <v>3.425</v>
       </c>
       <c r="G730" s="2">
         <v>45901</v>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="E731">
-        <v>3.89</v>
+        <v>3.985</v>
       </c>
       <c r="G731" s="2">
         <v>45901</v>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="E732">
-        <v>6.78</v>
+        <v>7.345000000000001</v>
       </c>
       <c r="G732" s="2">
         <v>45901</v>
@@ -22994,7 +22994,7 @@
         </is>
       </c>
       <c r="E733">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="G733" s="2">
         <v>45901</v>
@@ -23022,7 +23022,7 @@
         </is>
       </c>
       <c r="E734">
-        <v>29.78</v>
+        <v>30.17</v>
       </c>
       <c r="G734" s="2">
         <v>45901</v>
@@ -23050,7 +23050,7 @@
         </is>
       </c>
       <c r="E735">
-        <v>48.9</v>
+        <v>47.55</v>
       </c>
       <c r="G735" s="2">
         <v>45901</v>
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="E736">
-        <v>3.47</v>
+        <v>3.575</v>
       </c>
       <c r="G736" s="2">
         <v>45901</v>
@@ -23106,7 +23106,7 @@
         </is>
       </c>
       <c r="E737">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="G737" s="2">
         <v>45901</v>
@@ -23134,7 +23134,7 @@
         </is>
       </c>
       <c r="E738">
-        <v>4.42</v>
+        <v>4.529999999999999</v>
       </c>
       <c r="G738" s="2">
         <v>45901</v>
@@ -23162,7 +23162,7 @@
         </is>
       </c>
       <c r="E739">
-        <v>27.29</v>
+        <v>28.02</v>
       </c>
       <c r="G739" s="2">
         <v>45901</v>
@@ -23190,7 +23190,7 @@
         </is>
       </c>
       <c r="E740">
-        <v>17.9</v>
+        <v>17.425</v>
       </c>
       <c r="G740" s="2">
         <v>45901</v>
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="E741">
-        <v>7.29</v>
+        <v>6.359999999999999</v>
       </c>
       <c r="G741" s="2">
         <v>45901</v>
@@ -23246,7 +23246,7 @@
         </is>
       </c>
       <c r="E742">
-        <v>7.72</v>
+        <v>7.57</v>
       </c>
       <c r="G742" s="2">
         <v>45901</v>
@@ -23277,7 +23277,7 @@
         <v>3.18</v>
       </c>
       <c r="F743">
-        <v>-7.83</v>
+        <v>-7.15</v>
       </c>
       <c r="G743" s="2">
         <v>45931</v>
@@ -23308,7 +23308,7 @@
         <v>3.925</v>
       </c>
       <c r="F744">
-        <v>0.9</v>
+        <v>-1.51</v>
       </c>
       <c r="G744" s="2">
         <v>45931</v>
@@ -23339,7 +23339,7 @@
         <v>7.515</v>
       </c>
       <c r="F745">
-        <v>10.84</v>
+        <v>2.31</v>
       </c>
       <c r="G745" s="2">
         <v>45931</v>
@@ -23370,7 +23370,7 @@
         <v>3.005</v>
       </c>
       <c r="F746">
-        <v>3.98</v>
+        <v>-5.5</v>
       </c>
       <c r="G746" s="2">
         <v>45931</v>
@@ -23401,7 +23401,7 @@
         <v>30.065</v>
       </c>
       <c r="F747">
-        <v>0.96</v>
+        <v>-0.35</v>
       </c>
       <c r="G747" s="2">
         <v>45931</v>
@@ -23432,7 +23432,7 @@
         <v>47.545</v>
       </c>
       <c r="F748">
-        <v>-2.77</v>
+        <v>-0.01</v>
       </c>
       <c r="G748" s="2">
         <v>45931</v>
@@ -23463,7 +23463,7 @@
         <v>3.655</v>
       </c>
       <c r="F749">
-        <v>5.33</v>
+        <v>2.24</v>
       </c>
       <c r="G749" s="2">
         <v>45931</v>
@@ -23494,7 +23494,7 @@
         <v>4.905</v>
       </c>
       <c r="F750">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="G750" s="2">
         <v>45931</v>
@@ -23525,7 +23525,7 @@
         <v>4.45</v>
       </c>
       <c r="F751">
-        <v>0.68</v>
+        <v>-1.77</v>
       </c>
       <c r="G751" s="2">
         <v>45931</v>
@@ -23556,7 +23556,7 @@
         <v>27.435</v>
       </c>
       <c r="F752">
-        <v>0.53</v>
+        <v>-2.09</v>
       </c>
       <c r="G752" s="2">
         <v>45931</v>
@@ -23587,7 +23587,7 @@
         <v>17.425</v>
       </c>
       <c r="F753">
-        <v>-2.65</v>
+        <v>0</v>
       </c>
       <c r="G753" s="2">
         <v>45931</v>
@@ -23618,7 +23618,7 @@
         <v>8.380000000000001</v>
       </c>
       <c r="F754">
-        <v>14.95</v>
+        <v>31.76</v>
       </c>
       <c r="G754" s="2">
         <v>45931</v>
@@ -23649,7 +23649,7 @@
         <v>7.775</v>
       </c>
       <c r="F755">
-        <v>0.71</v>
+        <v>2.71</v>
       </c>
       <c r="G755" s="2">
         <v>45931</v>
@@ -24066,7 +24066,12 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -24075,10 +24080,13 @@
         </is>
       </c>
       <c r="E769">
-        <v>3.4</v>
+        <v>3.753333333333333</v>
       </c>
       <c r="F769">
-        <v>7.59</v>
+        <v>18.78</v>
+      </c>
+      <c r="G769" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="770">
@@ -24089,7 +24097,12 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -24098,10 +24111,13 @@
         </is>
       </c>
       <c r="E770">
-        <v>4.08</v>
+        <v>3.4875</v>
       </c>
       <c r="F770">
-        <v>9.380000000000001</v>
+        <v>-6.5</v>
+      </c>
+      <c r="G770" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="771">
@@ -24112,7 +24128,12 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -24121,10 +24142,13 @@
         </is>
       </c>
       <c r="E771">
-        <v>7.91</v>
+        <v>5.918333333333333</v>
       </c>
       <c r="F771">
-        <v>11.25</v>
+        <v>-16.76</v>
+      </c>
+      <c r="G771" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="772">
@@ -24135,7 +24159,12 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -24144,10 +24173,13 @@
         </is>
       </c>
       <c r="E772">
-        <v>3.47</v>
+        <v>5.4375</v>
       </c>
       <c r="F772">
-        <v>24.37</v>
+        <v>94.89</v>
+      </c>
+      <c r="G772" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="773">
@@ -24158,7 +24190,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -24167,10 +24204,13 @@
         </is>
       </c>
       <c r="E773">
-        <v>30.56</v>
+        <v>23.59166666666667</v>
       </c>
       <c r="F773">
-        <v>2.58</v>
+        <v>-20.81</v>
+      </c>
+      <c r="G773" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="774">
@@ -24181,7 +24221,12 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -24190,10 +24235,13 @@
         </is>
       </c>
       <c r="E774">
-        <v>46.2</v>
+        <v>54.75333333333333</v>
       </c>
       <c r="F774">
-        <v>-2.18</v>
+        <v>15.93</v>
+      </c>
+      <c r="G774" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="775">
@@ -24204,7 +24252,12 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -24213,10 +24266,13 @@
         </is>
       </c>
       <c r="E775">
-        <v>3.68</v>
+        <v>3.5875</v>
       </c>
       <c r="F775">
-        <v>6.67</v>
+        <v>3.99</v>
+      </c>
+      <c r="G775" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="776">
@@ -24227,7 +24283,12 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -24236,10 +24297,13 @@
         </is>
       </c>
       <c r="E776">
-        <v>4.74</v>
+        <v>6.6125</v>
       </c>
       <c r="F776">
-        <v>3.95</v>
+        <v>45.01</v>
+      </c>
+      <c r="G776" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="777">
@@ -24250,7 +24314,12 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -24259,10 +24328,13 @@
         </is>
       </c>
       <c r="E777">
-        <v>4.64</v>
+        <v>5.126666666666667</v>
       </c>
       <c r="F777">
-        <v>18.37</v>
+        <v>30.78</v>
+      </c>
+      <c r="G777" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="778">
@@ -24273,7 +24345,12 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -24282,10 +24359,13 @@
         </is>
       </c>
       <c r="E778">
-        <v>28.75</v>
+        <v>29.4425</v>
       </c>
       <c r="F778">
-        <v>13.32</v>
+        <v>16.05</v>
+      </c>
+      <c r="G778" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="779">
@@ -24296,7 +24376,12 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -24305,10 +24390,13 @@
         </is>
       </c>
       <c r="E779">
-        <v>16.95</v>
+        <v>15.70666666666667</v>
       </c>
       <c r="F779">
-        <v>-5.31</v>
+        <v>-12.25</v>
+      </c>
+      <c r="G779" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="780">
@@ -24319,7 +24407,12 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -24328,10 +24421,13 @@
         </is>
       </c>
       <c r="E780">
-        <v>5.43</v>
+        <v>7.433333333333334</v>
       </c>
       <c r="F780">
-        <v>-20.03</v>
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G780" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="781">
@@ -24342,7 +24438,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -24351,10 +24452,13 @@
         </is>
       </c>
       <c r="E781">
-        <v>7.42</v>
+        <v>7.036666666666667</v>
       </c>
       <c r="F781">
-        <v>-6.78</v>
+        <v>-11.6</v>
+      </c>
+      <c r="G781" s="2">
+        <v>46235</v>
       </c>
     </row>
     <row r="782">
@@ -24370,7 +24474,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -24379,13 +24483,13 @@
         </is>
       </c>
       <c r="E782">
-        <v>3.753333333333333</v>
+        <v>3.4975</v>
       </c>
       <c r="F782">
-        <v>10.39</v>
+        <v>-6.82</v>
       </c>
       <c r="G782" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="783">
@@ -24401,7 +24505,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -24410,13 +24514,13 @@
         </is>
       </c>
       <c r="E783">
-        <v>3.4875</v>
+        <v>3.425</v>
       </c>
       <c r="F783">
-        <v>-14.52</v>
+        <v>-1.79</v>
       </c>
       <c r="G783" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="784">
@@ -24432,7 +24536,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -24441,13 +24545,13 @@
         </is>
       </c>
       <c r="E784">
-        <v>5.918333333333333</v>
+        <v>5.362500000000001</v>
       </c>
       <c r="F784">
-        <v>-25.18</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="G784" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="785">
@@ -24463,7 +24567,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -24472,13 +24576,13 @@
         </is>
       </c>
       <c r="E785">
-        <v>5.4375</v>
+        <v>5.9625</v>
       </c>
       <c r="F785">
-        <v>56.7</v>
+        <v>9.66</v>
       </c>
       <c r="G785" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="786">
@@ -24494,7 +24598,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -24503,13 +24607,13 @@
         </is>
       </c>
       <c r="E786">
-        <v>23.59166666666667</v>
+        <v>22.15666666666667</v>
       </c>
       <c r="F786">
-        <v>-22.8</v>
+        <v>-6.08</v>
       </c>
       <c r="G786" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="787">
@@ -24525,7 +24629,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -24534,13 +24638,13 @@
         </is>
       </c>
       <c r="E787">
-        <v>54.75333333333333</v>
+        <v>49.65833333333333</v>
       </c>
       <c r="F787">
-        <v>18.51</v>
+        <v>-9.31</v>
       </c>
       <c r="G787" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="788">
@@ -24556,7 +24660,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -24565,13 +24669,13 @@
         </is>
       </c>
       <c r="E788">
-        <v>3.5875</v>
+        <v>3.69</v>
       </c>
       <c r="F788">
-        <v>-2.51</v>
+        <v>2.86</v>
       </c>
       <c r="G788" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="789">
@@ -24587,7 +24691,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -24596,13 +24700,13 @@
         </is>
       </c>
       <c r="E789">
-        <v>6.6125</v>
+        <v>5.9575</v>
       </c>
       <c r="F789">
-        <v>39.5</v>
+        <v>-9.91</v>
       </c>
       <c r="G789" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="790">
@@ -24618,7 +24722,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -24627,13 +24731,13 @@
         </is>
       </c>
       <c r="E790">
-        <v>5.126666666666667</v>
+        <v>5.065</v>
       </c>
       <c r="F790">
-        <v>10.49</v>
+        <v>-1.2</v>
       </c>
       <c r="G790" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="791">
@@ -24649,7 +24753,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -24658,13 +24762,13 @@
         </is>
       </c>
       <c r="E791">
-        <v>29.4425</v>
+        <v>27.06833333333334</v>
       </c>
       <c r="F791">
-        <v>2.41</v>
+        <v>-8.06</v>
       </c>
       <c r="G791" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="792">
@@ -24680,7 +24784,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -24689,13 +24793,13 @@
         </is>
       </c>
       <c r="E792">
-        <v>15.70666666666667</v>
+        <v>15.60833333333333</v>
       </c>
       <c r="F792">
-        <v>-7.34</v>
+        <v>-0.63</v>
       </c>
       <c r="G792" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="793">
@@ -24711,7 +24815,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -24720,13 +24824,13 @@
         </is>
       </c>
       <c r="E793">
-        <v>7.433333333333334</v>
+        <v>11.41833333333333</v>
       </c>
       <c r="F793">
-        <v>36.89</v>
+        <v>53.61</v>
       </c>
       <c r="G793" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="794">
@@ -24742,7 +24846,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -24751,19 +24855,19 @@
         </is>
       </c>
       <c r="E794">
-        <v>7.036666666666667</v>
+        <v>7.003333333333334</v>
       </c>
       <c r="F794">
-        <v>-5.17</v>
+        <v>-0.47</v>
       </c>
       <c r="G794" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -24773,7 +24877,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
@@ -24782,19 +24886,16 @@
         </is>
       </c>
       <c r="E795">
-        <v>3.4975</v>
-      </c>
-      <c r="F795">
-        <v>-6.82</v>
+        <v>3.46</v>
       </c>
       <c r="G795" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -24804,7 +24905,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -24813,19 +24914,16 @@
         </is>
       </c>
       <c r="E796">
-        <v>3.425</v>
-      </c>
-      <c r="F796">
-        <v>-1.79</v>
+        <v>4.446666666666667</v>
       </c>
       <c r="G796" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -24835,7 +24933,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -24844,19 +24942,16 @@
         </is>
       </c>
       <c r="E797">
-        <v>5.362500000000001</v>
-      </c>
-      <c r="F797">
-        <v>-9.390000000000001</v>
+        <v>5.82</v>
       </c>
       <c r="G797" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -24866,7 +24961,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -24875,19 +24970,16 @@
         </is>
       </c>
       <c r="E798">
-        <v>5.9625</v>
-      </c>
-      <c r="F798">
-        <v>9.66</v>
+        <v>4.49</v>
       </c>
       <c r="G798" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -24897,7 +24989,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -24906,19 +24998,16 @@
         </is>
       </c>
       <c r="E799">
-        <v>22.15666666666667</v>
-      </c>
-      <c r="F799">
-        <v>-6.08</v>
+        <v>32.35</v>
       </c>
       <c r="G799" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -24928,7 +25017,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -24937,19 +25026,16 @@
         </is>
       </c>
       <c r="E800">
-        <v>49.65833333333333</v>
-      </c>
-      <c r="F800">
-        <v>-9.31</v>
+        <v>48.44333333333334</v>
       </c>
       <c r="G800" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -24959,7 +25045,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -24968,19 +25054,16 @@
         </is>
       </c>
       <c r="E801">
-        <v>3.69</v>
-      </c>
-      <c r="F801">
-        <v>2.86</v>
+        <v>3.813333333333333</v>
       </c>
       <c r="G801" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -24990,7 +25073,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -24999,19 +25082,16 @@
         </is>
       </c>
       <c r="E802">
-        <v>5.9575</v>
-      </c>
-      <c r="F802">
-        <v>-9.91</v>
+        <v>5.46</v>
       </c>
       <c r="G802" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -25021,7 +25101,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -25030,19 +25110,16 @@
         </is>
       </c>
       <c r="E803">
-        <v>5.065</v>
-      </c>
-      <c r="F803">
-        <v>-1.2</v>
+        <v>4.48</v>
       </c>
       <c r="G803" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -25052,7 +25129,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -25061,19 +25138,16 @@
         </is>
       </c>
       <c r="E804">
-        <v>27.06833333333334</v>
-      </c>
-      <c r="F804">
-        <v>-8.06</v>
+        <v>28.26666666666667</v>
       </c>
       <c r="G804" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -25083,7 +25157,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -25092,19 +25166,16 @@
         </is>
       </c>
       <c r="E805">
-        <v>15.60833333333333</v>
-      </c>
-      <c r="F805">
-        <v>-0.63</v>
+        <v>16.94666666666667</v>
       </c>
       <c r="G805" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -25114,7 +25185,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -25123,19 +25194,16 @@
         </is>
       </c>
       <c r="E806">
-        <v>11.41833333333333</v>
-      </c>
-      <c r="F806">
-        <v>53.61</v>
+        <v>8.99</v>
       </c>
       <c r="G806" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -25145,7 +25213,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -25154,13 +25222,10 @@
         </is>
       </c>
       <c r="E807">
-        <v>7.003333333333334</v>
-      </c>
-      <c r="F807">
-        <v>-0.47</v>
+        <v>7.763333333333333</v>
       </c>
       <c r="G807" s="2">
-        <v>46266</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="808">
@@ -25176,7 +25241,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -25185,10 +25250,13 @@
         </is>
       </c>
       <c r="E808">
-        <v>3.46</v>
+        <v>3.69</v>
+      </c>
+      <c r="F808">
+        <v>6.65</v>
       </c>
       <c r="G808" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="809">
@@ -25204,7 +25272,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -25213,10 +25281,13 @@
         </is>
       </c>
       <c r="E809">
-        <v>4.446666666666667</v>
+        <v>4.15</v>
+      </c>
+      <c r="F809">
+        <v>-6.67</v>
       </c>
       <c r="G809" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="810">
@@ -25232,7 +25303,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -25241,10 +25312,13 @@
         </is>
       </c>
       <c r="E810">
-        <v>5.82</v>
+        <v>5.29</v>
+      </c>
+      <c r="F810">
+        <v>-9.109999999999999</v>
       </c>
       <c r="G810" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="811">
@@ -25260,7 +25334,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -25269,10 +25343,13 @@
         </is>
       </c>
       <c r="E811">
-        <v>4.49</v>
+        <v>7.456666666666667</v>
+      </c>
+      <c r="F811">
+        <v>66.06999999999999</v>
       </c>
       <c r="G811" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="812">
@@ -25288,7 +25365,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -25297,10 +25374,13 @@
         </is>
       </c>
       <c r="E812">
-        <v>32.35</v>
+        <v>31.37333333333333</v>
+      </c>
+      <c r="F812">
+        <v>-3.02</v>
       </c>
       <c r="G812" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="813">
@@ -25316,7 +25396,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -25325,10 +25405,13 @@
         </is>
       </c>
       <c r="E813">
-        <v>48.44333333333334</v>
+        <v>48.68</v>
+      </c>
+      <c r="F813">
+        <v>0.49</v>
       </c>
       <c r="G813" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="814">
@@ -25344,7 +25427,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -25353,10 +25436,13 @@
         </is>
       </c>
       <c r="E814">
-        <v>3.813333333333333</v>
+        <v>3.76</v>
+      </c>
+      <c r="F814">
+        <v>-1.4</v>
       </c>
       <c r="G814" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="815">
@@ -25372,7 +25458,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -25381,10 +25467,13 @@
         </is>
       </c>
       <c r="E815">
-        <v>5.46</v>
+        <v>5.89</v>
+      </c>
+      <c r="F815">
+        <v>7.88</v>
       </c>
       <c r="G815" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="816">
@@ -25400,7 +25489,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -25409,10 +25498,13 @@
         </is>
       </c>
       <c r="E816">
-        <v>4.48</v>
+        <v>5.756666666666667</v>
+      </c>
+      <c r="F816">
+        <v>28.5</v>
       </c>
       <c r="G816" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="817">
@@ -25428,7 +25520,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -25437,10 +25529,13 @@
         </is>
       </c>
       <c r="E817">
-        <v>28.26666666666667</v>
+        <v>28.72</v>
+      </c>
+      <c r="F817">
+        <v>1.6</v>
       </c>
       <c r="G817" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="818">
@@ -25456,7 +25551,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -25465,10 +25560,13 @@
         </is>
       </c>
       <c r="E818">
-        <v>16.94666666666667</v>
+        <v>17.21333333333333</v>
+      </c>
+      <c r="F818">
+        <v>1.57</v>
       </c>
       <c r="G818" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="819">
@@ -25484,7 +25582,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -25495,8 +25593,11 @@
       <c r="E819">
         <v>8.99</v>
       </c>
+      <c r="F819">
+        <v>0</v>
+      </c>
       <c r="G819" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="820">
@@ -25512,7 +25613,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -25521,10 +25622,13 @@
         </is>
       </c>
       <c r="E820">
-        <v>7.763333333333333</v>
+        <v>7.706666666666666</v>
+      </c>
+      <c r="F820">
+        <v>-0.73</v>
       </c>
       <c r="G820" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="821">
@@ -25540,7 +25644,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -25549,13 +25653,13 @@
         </is>
       </c>
       <c r="E821">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="F821">
-        <v>6.65</v>
+        <v>-2.44</v>
       </c>
       <c r="G821" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="822">
@@ -25571,7 +25675,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -25580,13 +25684,13 @@
         </is>
       </c>
       <c r="E822">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="F822">
-        <v>-6.67</v>
+        <v>0.48</v>
       </c>
       <c r="G822" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="823">
@@ -25602,7 +25706,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -25611,13 +25715,13 @@
         </is>
       </c>
       <c r="E823">
-        <v>5.29</v>
+        <v>4.99</v>
       </c>
       <c r="F823">
-        <v>-9.109999999999999</v>
+        <v>-5.67</v>
       </c>
       <c r="G823" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="824">
@@ -25633,7 +25737,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -25642,13 +25746,13 @@
         </is>
       </c>
       <c r="E824">
-        <v>7.456666666666667</v>
+        <v>8.99</v>
       </c>
       <c r="F824">
-        <v>66.06999999999999</v>
+        <v>20.56</v>
       </c>
       <c r="G824" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="825">
@@ -25664,7 +25768,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -25673,13 +25777,13 @@
         </is>
       </c>
       <c r="E825">
-        <v>31.37333333333333</v>
+        <v>28.76666666666667</v>
       </c>
       <c r="F825">
-        <v>-3.02</v>
+        <v>-8.31</v>
       </c>
       <c r="G825" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="826">
@@ -25695,7 +25799,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -25704,13 +25808,13 @@
         </is>
       </c>
       <c r="E826">
-        <v>48.68</v>
+        <v>50.02666666666666</v>
       </c>
       <c r="F826">
-        <v>0.49</v>
+        <v>2.77</v>
       </c>
       <c r="G826" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="827">
@@ -25726,7 +25830,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -25735,13 +25839,13 @@
         </is>
       </c>
       <c r="E827">
-        <v>3.76</v>
+        <v>3.506666666666666</v>
       </c>
       <c r="F827">
-        <v>-1.4</v>
+        <v>-6.74</v>
       </c>
       <c r="G827" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="828">
@@ -25757,7 +25861,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -25766,13 +25870,13 @@
         </is>
       </c>
       <c r="E828">
-        <v>5.89</v>
+        <v>5.896666666666667</v>
       </c>
       <c r="F828">
-        <v>7.88</v>
+        <v>0.11</v>
       </c>
       <c r="G828" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="829">
@@ -25788,7 +25892,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -25797,13 +25901,13 @@
         </is>
       </c>
       <c r="E829">
-        <v>5.756666666666667</v>
+        <v>5.656666666666667</v>
       </c>
       <c r="F829">
-        <v>28.5</v>
+        <v>-1.74</v>
       </c>
       <c r="G829" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="830">
@@ -25819,7 +25923,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -25828,13 +25932,13 @@
         </is>
       </c>
       <c r="E830">
-        <v>28.72</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="F830">
-        <v>1.6</v>
+        <v>-0.19</v>
       </c>
       <c r="G830" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="831">
@@ -25850,7 +25954,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -25859,13 +25963,13 @@
         </is>
       </c>
       <c r="E831">
-        <v>17.21333333333333</v>
+        <v>17.56333333333333</v>
       </c>
       <c r="F831">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="G831" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="832">
@@ -25881,7 +25985,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -25890,13 +25994,13 @@
         </is>
       </c>
       <c r="E832">
-        <v>8.99</v>
+        <v>13.59333333333333</v>
       </c>
       <c r="F832">
-        <v>0</v>
+        <v>51.21</v>
       </c>
       <c r="G832" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="833">
@@ -25912,7 +26016,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -25921,19 +26025,19 @@
         </is>
       </c>
       <c r="E833">
-        <v>7.706666666666666</v>
+        <v>7.443333333333333</v>
       </c>
       <c r="F833">
-        <v>-0.73</v>
+        <v>-3.42</v>
       </c>
       <c r="G833" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -25943,7 +26047,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -25952,19 +26056,16 @@
         </is>
       </c>
       <c r="E834">
-        <v>3.6</v>
-      </c>
-      <c r="F834">
-        <v>-2.44</v>
+        <v>3.716666666666666</v>
       </c>
       <c r="G834" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -25974,7 +26075,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -25983,19 +26084,16 @@
         </is>
       </c>
       <c r="E835">
-        <v>4.17</v>
-      </c>
-      <c r="F835">
-        <v>0.48</v>
+        <v>3.753333333333333</v>
       </c>
       <c r="G835" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -26005,7 +26103,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -26014,19 +26112,16 @@
         </is>
       </c>
       <c r="E836">
-        <v>4.99</v>
-      </c>
-      <c r="F836">
-        <v>-5.67</v>
+        <v>6.183333333333334</v>
       </c>
       <c r="G836" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -26036,7 +26131,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -26045,19 +26140,16 @@
         </is>
       </c>
       <c r="E837">
-        <v>8.99</v>
-      </c>
-      <c r="F837">
-        <v>20.56</v>
+        <v>4.26</v>
       </c>
       <c r="G837" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -26067,7 +26159,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -26076,19 +26168,16 @@
         </is>
       </c>
       <c r="E838">
-        <v>28.76666666666667</v>
-      </c>
-      <c r="F838">
-        <v>-8.31</v>
+        <v>28.61</v>
       </c>
       <c r="G838" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -26098,7 +26187,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -26107,19 +26196,16 @@
         </is>
       </c>
       <c r="E839">
-        <v>50.02666666666666</v>
-      </c>
-      <c r="F839">
-        <v>2.77</v>
+        <v>52.79333333333334</v>
       </c>
       <c r="G839" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -26129,7 +26215,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -26138,19 +26224,16 @@
         </is>
       </c>
       <c r="E840">
-        <v>3.506666666666666</v>
-      </c>
-      <c r="F840">
-        <v>-6.74</v>
+        <v>3.406666666666667</v>
       </c>
       <c r="G840" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -26160,7 +26243,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -26169,19 +26252,16 @@
         </is>
       </c>
       <c r="E841">
-        <v>5.896666666666667</v>
-      </c>
-      <c r="F841">
-        <v>0.11</v>
+        <v>5.123333333333333</v>
       </c>
       <c r="G841" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -26191,7 +26271,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -26200,19 +26280,16 @@
         </is>
       </c>
       <c r="E842">
-        <v>5.656666666666667</v>
-      </c>
-      <c r="F842">
-        <v>-1.74</v>
+        <v>3.8</v>
       </c>
       <c r="G842" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -26222,7 +26299,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -26231,19 +26308,16 @@
         </is>
       </c>
       <c r="E843">
-        <v>28.66666666666667</v>
-      </c>
-      <c r="F843">
-        <v>-0.19</v>
+        <v>26.67333333333333</v>
       </c>
       <c r="G843" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -26253,7 +26327,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -26262,19 +26336,16 @@
         </is>
       </c>
       <c r="E844">
-        <v>17.56333333333333</v>
-      </c>
-      <c r="F844">
-        <v>2.03</v>
+        <v>13.35333333333333</v>
       </c>
       <c r="G844" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -26284,7 +26355,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -26293,19 +26364,16 @@
         </is>
       </c>
       <c r="E845">
-        <v>13.59333333333333</v>
-      </c>
-      <c r="F845">
-        <v>51.21</v>
+        <v>12.98</v>
       </c>
       <c r="G845" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -26315,7 +26383,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -26324,13 +26392,10 @@
         </is>
       </c>
       <c r="E846">
-        <v>7.443333333333333</v>
-      </c>
-      <c r="F846">
-        <v>-3.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G846" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="847">
@@ -26346,7 +26411,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -26355,10 +26420,13 @@
         </is>
       </c>
       <c r="E847">
-        <v>3.716666666666666</v>
+        <v>3.44</v>
+      </c>
+      <c r="F847">
+        <v>-7.44</v>
       </c>
       <c r="G847" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="848">
@@ -26374,7 +26442,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -26383,10 +26451,13 @@
         </is>
       </c>
       <c r="E848">
-        <v>3.753333333333333</v>
+        <v>4.21</v>
+      </c>
+      <c r="F848">
+        <v>12.17</v>
       </c>
       <c r="G848" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="849">
@@ -26402,7 +26473,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -26411,10 +26482,13 @@
         </is>
       </c>
       <c r="E849">
-        <v>6.183333333333334</v>
+        <v>5.24</v>
+      </c>
+      <c r="F849">
+        <v>-15.26</v>
       </c>
       <c r="G849" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="850">
@@ -26430,7 +26504,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -26439,10 +26513,13 @@
         </is>
       </c>
       <c r="E850">
-        <v>4.26</v>
+        <v>4.79</v>
+      </c>
+      <c r="F850">
+        <v>12.44</v>
       </c>
       <c r="G850" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="851">
@@ -26458,7 +26535,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -26467,10 +26544,13 @@
         </is>
       </c>
       <c r="E851">
-        <v>28.61</v>
+        <v>27.24</v>
+      </c>
+      <c r="F851">
+        <v>-4.79</v>
       </c>
       <c r="G851" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="852">
@@ -26486,7 +26566,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -26495,10 +26575,13 @@
         </is>
       </c>
       <c r="E852">
-        <v>52.79333333333334</v>
+        <v>47.93</v>
+      </c>
+      <c r="F852">
+        <v>-9.210000000000001</v>
       </c>
       <c r="G852" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="853">
@@ -26514,7 +26597,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -26523,10 +26606,13 @@
         </is>
       </c>
       <c r="E853">
-        <v>3.406666666666667</v>
+        <v>3.59</v>
+      </c>
+      <c r="F853">
+        <v>5.38</v>
       </c>
       <c r="G853" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="854">
@@ -26542,7 +26628,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -26551,10 +26637,13 @@
         </is>
       </c>
       <c r="E854">
-        <v>5.123333333333333</v>
+        <v>4.890000000000001</v>
+      </c>
+      <c r="F854">
+        <v>-4.55</v>
       </c>
       <c r="G854" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="855">
@@ -26570,7 +26659,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -26579,10 +26668,13 @@
         </is>
       </c>
       <c r="E855">
-        <v>3.8</v>
+        <v>4.75</v>
+      </c>
+      <c r="F855">
+        <v>25</v>
       </c>
       <c r="G855" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="856">
@@ -26598,7 +26690,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -26607,10 +26699,13 @@
         </is>
       </c>
       <c r="E856">
-        <v>26.67333333333333</v>
+        <v>20.54</v>
+      </c>
+      <c r="F856">
+        <v>-22.99</v>
       </c>
       <c r="G856" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="857">
@@ -26626,7 +26721,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -26635,10 +26730,13 @@
         </is>
       </c>
       <c r="E857">
-        <v>13.35333333333333</v>
+        <v>13.4</v>
+      </c>
+      <c r="F857">
+        <v>0.35</v>
       </c>
       <c r="G857" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="858">
@@ -26654,7 +26752,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -26663,10 +26761,13 @@
         </is>
       </c>
       <c r="E858">
-        <v>12.98</v>
+        <v>5.985</v>
+      </c>
+      <c r="F858">
+        <v>-53.89</v>
       </c>
       <c r="G858" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="859">
@@ -26682,7 +26783,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -26691,16 +26792,19 @@
         </is>
       </c>
       <c r="E859">
-        <v>9.199999999999999</v>
+        <v>7.725</v>
+      </c>
+      <c r="F859">
+        <v>-16.03</v>
       </c>
       <c r="G859" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -26710,7 +26814,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -26719,19 +26823,16 @@
         </is>
       </c>
       <c r="E860">
-        <v>3.44</v>
-      </c>
-      <c r="F860">
-        <v>-7.44</v>
+        <v>3.3</v>
       </c>
       <c r="G860" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -26741,7 +26842,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -26750,19 +26851,16 @@
         </is>
       </c>
       <c r="E861">
-        <v>4.21</v>
-      </c>
-      <c r="F861">
-        <v>12.17</v>
+        <v>4.353333333333333</v>
       </c>
       <c r="G861" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -26772,7 +26870,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -26781,19 +26879,16 @@
         </is>
       </c>
       <c r="E862">
-        <v>5.24</v>
-      </c>
-      <c r="F862">
-        <v>-15.26</v>
+        <v>5.976666666666667</v>
       </c>
       <c r="G862" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -26803,7 +26898,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -26812,19 +26907,16 @@
         </is>
       </c>
       <c r="E863">
-        <v>4.79</v>
-      </c>
-      <c r="F863">
-        <v>12.44</v>
+        <v>4.78</v>
       </c>
       <c r="G863" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -26834,7 +26926,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -26843,19 +26935,16 @@
         </is>
       </c>
       <c r="E864">
-        <v>27.24</v>
-      </c>
-      <c r="F864">
-        <v>-4.79</v>
+        <v>27.43</v>
       </c>
       <c r="G864" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -26865,7 +26954,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -26874,19 +26963,16 @@
         </is>
       </c>
       <c r="E865">
-        <v>47.93</v>
-      </c>
-      <c r="F865">
-        <v>-9.210000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="G865" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -26896,7 +26982,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -26905,19 +26991,16 @@
         </is>
       </c>
       <c r="E866">
-        <v>3.59</v>
-      </c>
-      <c r="F866">
-        <v>5.38</v>
+        <v>3.326666666666667</v>
       </c>
       <c r="G866" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -26927,7 +27010,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -26936,19 +27019,16 @@
         </is>
       </c>
       <c r="E867">
-        <v>4.890000000000001</v>
-      </c>
-      <c r="F867">
-        <v>-4.55</v>
+        <v>5.3</v>
       </c>
       <c r="G867" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -26958,7 +27038,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -26967,19 +27047,16 @@
         </is>
       </c>
       <c r="E868">
-        <v>4.75</v>
-      </c>
-      <c r="F868">
-        <v>25</v>
+        <v>3.806666666666667</v>
       </c>
       <c r="G868" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -26989,7 +27066,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -26998,19 +27075,16 @@
         </is>
       </c>
       <c r="E869">
-        <v>20.54</v>
-      </c>
-      <c r="F869">
-        <v>-22.99</v>
+        <v>27.32333333333333</v>
       </c>
       <c r="G869" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -27020,7 +27094,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -27029,19 +27103,16 @@
         </is>
       </c>
       <c r="E870">
-        <v>13.4</v>
-      </c>
-      <c r="F870">
-        <v>0.35</v>
+        <v>15.56666666666667</v>
       </c>
       <c r="G870" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -27051,7 +27122,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -27060,19 +27131,16 @@
         </is>
       </c>
       <c r="E871">
-        <v>5.985</v>
-      </c>
-      <c r="F871">
-        <v>-53.89</v>
+        <v>10.32</v>
       </c>
       <c r="G871" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -27082,7 +27150,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -27091,13 +27159,10 @@
         </is>
       </c>
       <c r="E872">
-        <v>7.725</v>
-      </c>
-      <c r="F872">
-        <v>-16.03</v>
+        <v>7.836666666666667</v>
       </c>
       <c r="G872" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="873">
@@ -27113,7 +27178,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -27122,10 +27187,13 @@
         </is>
       </c>
       <c r="E873">
-        <v>3.3</v>
+        <v>3.39</v>
+      </c>
+      <c r="F873">
+        <v>2.73</v>
       </c>
       <c r="G873" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="874">
@@ -27141,7 +27209,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -27150,10 +27218,13 @@
         </is>
       </c>
       <c r="E874">
-        <v>4.353333333333333</v>
+        <v>4.443333333333333</v>
+      </c>
+      <c r="F874">
+        <v>2.07</v>
       </c>
       <c r="G874" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="875">
@@ -27169,7 +27240,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -27178,10 +27249,13 @@
         </is>
       </c>
       <c r="E875">
-        <v>5.976666666666667</v>
+        <v>6.56</v>
+      </c>
+      <c r="F875">
+        <v>9.76</v>
       </c>
       <c r="G875" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="876">
@@ -27197,7 +27271,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -27206,10 +27280,13 @@
         </is>
       </c>
       <c r="E876">
-        <v>4.78</v>
+        <v>4.98</v>
+      </c>
+      <c r="F876">
+        <v>4.18</v>
       </c>
       <c r="G876" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="877">
@@ -27225,7 +27302,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -27234,10 +27311,13 @@
         </is>
       </c>
       <c r="E877">
-        <v>27.43</v>
+        <v>27.95333333333333</v>
+      </c>
+      <c r="F877">
+        <v>1.91</v>
       </c>
       <c r="G877" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="878">
@@ -27253,7 +27333,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -27262,10 +27342,13 @@
         </is>
       </c>
       <c r="E878">
-        <v>44.9</v>
+        <v>55.32666666666667</v>
+      </c>
+      <c r="F878">
+        <v>23.22</v>
       </c>
       <c r="G878" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="879">
@@ -27281,7 +27364,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -27290,10 +27373,13 @@
         </is>
       </c>
       <c r="E879">
-        <v>3.326666666666667</v>
+        <v>3.45</v>
+      </c>
+      <c r="F879">
+        <v>3.71</v>
       </c>
       <c r="G879" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="880">
@@ -27309,7 +27395,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -27318,10 +27404,13 @@
         </is>
       </c>
       <c r="E880">
-        <v>5.3</v>
+        <v>5.376666666666667</v>
+      </c>
+      <c r="F880">
+        <v>1.45</v>
       </c>
       <c r="G880" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="881">
@@ -27337,7 +27426,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -27346,10 +27435,13 @@
         </is>
       </c>
       <c r="E881">
-        <v>3.806666666666667</v>
+        <v>4.22</v>
+      </c>
+      <c r="F881">
+        <v>10.86</v>
       </c>
       <c r="G881" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="882">
@@ -27365,7 +27457,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -27374,10 +27466,13 @@
         </is>
       </c>
       <c r="E882">
-        <v>27.32333333333333</v>
+        <v>28.10333333333333</v>
+      </c>
+      <c r="F882">
+        <v>2.85</v>
       </c>
       <c r="G882" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="883">
@@ -27393,7 +27488,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -27402,10 +27497,13 @@
         </is>
       </c>
       <c r="E883">
-        <v>15.56666666666667</v>
+        <v>15.9</v>
+      </c>
+      <c r="F883">
+        <v>2.14</v>
       </c>
       <c r="G883" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="884">
@@ -27421,7 +27519,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -27430,10 +27528,13 @@
         </is>
       </c>
       <c r="E884">
-        <v>10.32</v>
+        <v>10.65333333333333</v>
+      </c>
+      <c r="F884">
+        <v>3.23</v>
       </c>
       <c r="G884" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="885">
@@ -27449,7 +27550,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -27458,10 +27559,13 @@
         </is>
       </c>
       <c r="E885">
-        <v>7.836666666666667</v>
+        <v>7.993333333333333</v>
+      </c>
+      <c r="F885">
+        <v>2</v>
       </c>
       <c r="G885" s="2">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="886">
@@ -27477,7 +27581,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -27486,13 +27590,13 @@
         </is>
       </c>
       <c r="E886">
-        <v>3.39</v>
+        <v>3.206666666666667</v>
       </c>
       <c r="F886">
-        <v>2.73</v>
+        <v>-5.41</v>
       </c>
       <c r="G886" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="887">
@@ -27508,7 +27612,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -27517,13 +27621,13 @@
         </is>
       </c>
       <c r="E887">
-        <v>4.443333333333333</v>
+        <v>3.663333333333334</v>
       </c>
       <c r="F887">
-        <v>2.07</v>
+        <v>-17.55</v>
       </c>
       <c r="G887" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="888">
@@ -27539,7 +27643,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
@@ -27548,13 +27652,13 @@
         </is>
       </c>
       <c r="E888">
-        <v>6.56</v>
+        <v>5.49</v>
       </c>
       <c r="F888">
-        <v>9.76</v>
+        <v>-16.31</v>
       </c>
       <c r="G888" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="889">
@@ -27570,7 +27674,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -27579,13 +27683,13 @@
         </is>
       </c>
       <c r="E889">
-        <v>4.98</v>
+        <v>4.853333333333333</v>
       </c>
       <c r="F889">
-        <v>4.18</v>
+        <v>-2.54</v>
       </c>
       <c r="G889" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="890">
@@ -27601,7 +27705,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -27610,13 +27714,13 @@
         </is>
       </c>
       <c r="E890">
-        <v>27.95333333333333</v>
+        <v>23.21</v>
       </c>
       <c r="F890">
-        <v>1.91</v>
+        <v>-16.97</v>
       </c>
       <c r="G890" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="891">
@@ -27632,7 +27736,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -27641,13 +27745,13 @@
         </is>
       </c>
       <c r="E891">
-        <v>55.32666666666667</v>
+        <v>49.02666666666666</v>
       </c>
       <c r="F891">
-        <v>23.22</v>
+        <v>-11.39</v>
       </c>
       <c r="G891" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="892">
@@ -27663,7 +27767,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -27672,13 +27776,13 @@
         </is>
       </c>
       <c r="E892">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="F892">
-        <v>3.71</v>
+        <v>4.64</v>
       </c>
       <c r="G892" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="893">
@@ -27694,7 +27798,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -27703,13 +27807,13 @@
         </is>
       </c>
       <c r="E893">
-        <v>5.376666666666667</v>
+        <v>5.846666666666667</v>
       </c>
       <c r="F893">
-        <v>1.45</v>
+        <v>8.74</v>
       </c>
       <c r="G893" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="894">
@@ -27725,7 +27829,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -27734,13 +27838,13 @@
         </is>
       </c>
       <c r="E894">
-        <v>4.22</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F894">
-        <v>10.86</v>
+        <v>16.51</v>
       </c>
       <c r="G894" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="895">
@@ -27756,7 +27860,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -27765,13 +27869,13 @@
         </is>
       </c>
       <c r="E895">
-        <v>28.10333333333333</v>
+        <v>24.68666666666667</v>
       </c>
       <c r="F895">
-        <v>2.85</v>
+        <v>-12.16</v>
       </c>
       <c r="G895" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="896">
@@ -27787,7 +27891,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -27796,13 +27900,13 @@
         </is>
       </c>
       <c r="E896">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="F896">
-        <v>2.14</v>
+        <v>-12.58</v>
       </c>
       <c r="G896" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="897">
@@ -27818,7 +27922,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -27827,13 +27931,13 @@
         </is>
       </c>
       <c r="E897">
-        <v>10.65333333333333</v>
+        <v>5.816666666666667</v>
       </c>
       <c r="F897">
-        <v>3.23</v>
+        <v>-45.4</v>
       </c>
       <c r="G897" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="898">
@@ -27849,7 +27953,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -27858,13 +27962,13 @@
         </is>
       </c>
       <c r="E898">
-        <v>7.993333333333333</v>
+        <v>7.043333333333333</v>
       </c>
       <c r="F898">
-        <v>2</v>
+        <v>-11.88</v>
       </c>
       <c r="G898" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="899">
@@ -27880,7 +27984,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -27889,13 +27993,13 @@
         </is>
       </c>
       <c r="E899">
-        <v>3.206666666666667</v>
+        <v>3.406666666666667</v>
       </c>
       <c r="F899">
-        <v>-5.41</v>
+        <v>6.24</v>
       </c>
       <c r="G899" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="900">
@@ -27911,7 +28015,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -27920,13 +28024,13 @@
         </is>
       </c>
       <c r="E900">
-        <v>3.663333333333334</v>
+        <v>3.643333333333333</v>
       </c>
       <c r="F900">
-        <v>-17.55</v>
+        <v>-0.55</v>
       </c>
       <c r="G900" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="901">
@@ -27942,7 +28046,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -27954,10 +28058,10 @@
         <v>5.49</v>
       </c>
       <c r="F901">
-        <v>-16.31</v>
+        <v>0</v>
       </c>
       <c r="G901" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="902">
@@ -27973,7 +28077,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -27982,13 +28086,13 @@
         </is>
       </c>
       <c r="E902">
-        <v>4.853333333333333</v>
+        <v>4.98</v>
       </c>
       <c r="F902">
-        <v>-2.54</v>
+        <v>2.61</v>
       </c>
       <c r="G902" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="903">
@@ -28004,7 +28108,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -28013,13 +28117,13 @@
         </is>
       </c>
       <c r="E903">
-        <v>23.21</v>
+        <v>22.64333333333333</v>
       </c>
       <c r="F903">
-        <v>-16.97</v>
+        <v>-2.44</v>
       </c>
       <c r="G903" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="904">
@@ -28035,7 +28139,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -28044,13 +28148,13 @@
         </is>
       </c>
       <c r="E904">
-        <v>49.02666666666666</v>
+        <v>47.77333333333333</v>
       </c>
       <c r="F904">
-        <v>-11.39</v>
+        <v>-2.56</v>
       </c>
       <c r="G904" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="905">
@@ -28066,7 +28170,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -28075,13 +28179,13 @@
         </is>
       </c>
       <c r="E905">
-        <v>3.61</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="F905">
-        <v>4.64</v>
+        <v>-0.74</v>
       </c>
       <c r="G905" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="906">
@@ -28097,7 +28201,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -28106,13 +28210,13 @@
         </is>
       </c>
       <c r="E906">
-        <v>5.846666666666667</v>
+        <v>6.086666666666667</v>
       </c>
       <c r="F906">
-        <v>8.74</v>
+        <v>4.1</v>
       </c>
       <c r="G906" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="907">
@@ -28128,7 +28232,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -28137,13 +28241,13 @@
         </is>
       </c>
       <c r="E907">
-        <v>4.916666666666667</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="F907">
-        <v>16.51</v>
+        <v>-1.69</v>
       </c>
       <c r="G907" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="908">
@@ -28159,7 +28263,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -28168,13 +28272,13 @@
         </is>
       </c>
       <c r="E908">
-        <v>24.68666666666667</v>
+        <v>25.47</v>
       </c>
       <c r="F908">
-        <v>-12.16</v>
+        <v>3.17</v>
       </c>
       <c r="G908" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="909">
@@ -28190,7 +28294,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -28199,13 +28303,13 @@
         </is>
       </c>
       <c r="E909">
-        <v>13.9</v>
+        <v>14.23333333333333</v>
       </c>
       <c r="F909">
-        <v>-12.58</v>
+        <v>2.4</v>
       </c>
       <c r="G909" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="910">
@@ -28221,7 +28325,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -28230,13 +28334,13 @@
         </is>
       </c>
       <c r="E910">
-        <v>5.816666666666667</v>
+        <v>11.98</v>
       </c>
       <c r="F910">
-        <v>-45.4</v>
+        <v>105.96</v>
       </c>
       <c r="G910" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="911">
@@ -28252,7 +28356,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -28261,19 +28365,19 @@
         </is>
       </c>
       <c r="E911">
-        <v>7.043333333333333</v>
+        <v>7.123333333333333</v>
       </c>
       <c r="F911">
-        <v>-11.88</v>
+        <v>1.14</v>
       </c>
       <c r="G911" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -28283,7 +28387,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -28292,19 +28396,16 @@
         </is>
       </c>
       <c r="E912">
-        <v>3.406666666666667</v>
-      </c>
-      <c r="F912">
-        <v>6.24</v>
+        <v>3.393333333333334</v>
       </c>
       <c r="G912" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -28314,7 +28415,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -28323,19 +28424,16 @@
         </is>
       </c>
       <c r="E913">
-        <v>3.643333333333333</v>
-      </c>
-      <c r="F913">
-        <v>-0.55</v>
+        <v>3.69</v>
       </c>
       <c r="G913" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -28345,7 +28443,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -28354,19 +28452,16 @@
         </is>
       </c>
       <c r="E914">
-        <v>5.49</v>
-      </c>
-      <c r="F914">
-        <v>0</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="G914" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -28376,7 +28471,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -28385,19 +28480,16 @@
         </is>
       </c>
       <c r="E915">
-        <v>4.98</v>
-      </c>
-      <c r="F915">
-        <v>2.61</v>
+        <v>3.826666666666667</v>
       </c>
       <c r="G915" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -28407,7 +28499,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -28416,19 +28508,16 @@
         </is>
       </c>
       <c r="E916">
-        <v>22.64333333333333</v>
-      </c>
-      <c r="F916">
-        <v>-2.44</v>
+        <v>28.97</v>
       </c>
       <c r="G916" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -28438,7 +28527,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -28447,19 +28536,16 @@
         </is>
       </c>
       <c r="E917">
-        <v>47.77333333333333</v>
-      </c>
-      <c r="F917">
-        <v>-2.56</v>
+        <v>43.38</v>
       </c>
       <c r="G917" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -28469,7 +28555,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -28478,19 +28564,16 @@
         </is>
       </c>
       <c r="E918">
-        <v>3.583333333333333</v>
-      </c>
-      <c r="F918">
-        <v>-0.74</v>
+        <v>3.7</v>
       </c>
       <c r="G918" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -28500,7 +28583,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -28509,19 +28592,16 @@
         </is>
       </c>
       <c r="E919">
-        <v>6.086666666666667</v>
-      </c>
-      <c r="F919">
-        <v>4.1</v>
+        <v>4.903333333333333</v>
       </c>
       <c r="G919" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -28531,7 +28611,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -28540,19 +28620,16 @@
         </is>
       </c>
       <c r="E920">
-        <v>4.833333333333333</v>
-      </c>
-      <c r="F920">
-        <v>-1.69</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="G920" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -28562,7 +28639,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -28571,19 +28648,16 @@
         </is>
       </c>
       <c r="E921">
-        <v>25.47</v>
-      </c>
-      <c r="F921">
-        <v>3.17</v>
+        <v>23.95333333333333</v>
       </c>
       <c r="G921" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -28593,7 +28667,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -28602,19 +28676,16 @@
         </is>
       </c>
       <c r="E922">
-        <v>14.23333333333333</v>
-      </c>
-      <c r="F922">
-        <v>2.4</v>
+        <v>14.2</v>
       </c>
       <c r="G922" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -28624,7 +28695,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -28633,19 +28704,16 @@
         </is>
       </c>
       <c r="E923">
-        <v>11.98</v>
-      </c>
-      <c r="F923">
-        <v>105.96</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G923" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -28655,7 +28723,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -28664,13 +28732,10 @@
         </is>
       </c>
       <c r="E924">
-        <v>7.123333333333333</v>
-      </c>
-      <c r="F924">
-        <v>1.14</v>
+        <v>6.693333333333333</v>
       </c>
       <c r="G924" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="925">
@@ -28686,7 +28751,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -28695,10 +28760,13 @@
         </is>
       </c>
       <c r="E925">
-        <v>3.393333333333334</v>
+        <v>3.67</v>
+      </c>
+      <c r="F925">
+        <v>8.15</v>
       </c>
       <c r="G925" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="926">
@@ -28714,7 +28782,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -28723,10 +28791,13 @@
         </is>
       </c>
       <c r="E926">
-        <v>3.69</v>
+        <v>3.766666666666667</v>
+      </c>
+      <c r="F926">
+        <v>2.08</v>
       </c>
       <c r="G926" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="927">
@@ -28742,7 +28813,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -28751,10 +28822,13 @@
         </is>
       </c>
       <c r="E927">
-        <v>6.066666666666666</v>
+        <v>4.42</v>
+      </c>
+      <c r="F927">
+        <v>-27.14</v>
       </c>
       <c r="G927" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="928">
@@ -28770,7 +28844,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -28779,10 +28853,13 @@
         </is>
       </c>
       <c r="E928">
-        <v>3.826666666666667</v>
+        <v>4.99</v>
+      </c>
+      <c r="F928">
+        <v>30.4</v>
       </c>
       <c r="G928" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="929">
@@ -28798,7 +28875,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
@@ -28807,10 +28884,13 @@
         </is>
       </c>
       <c r="E929">
-        <v>28.97</v>
+        <v>25.06</v>
+      </c>
+      <c r="F929">
+        <v>-13.5</v>
       </c>
       <c r="G929" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="930">
@@ -28826,7 +28906,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -28835,10 +28915,13 @@
         </is>
       </c>
       <c r="E930">
-        <v>43.38</v>
+        <v>50.46</v>
+      </c>
+      <c r="F930">
+        <v>16.32</v>
       </c>
       <c r="G930" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="931">
@@ -28854,7 +28937,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
@@ -28863,10 +28946,13 @@
         </is>
       </c>
       <c r="E931">
-        <v>3.7</v>
+        <v>4.413333333333334</v>
+      </c>
+      <c r="F931">
+        <v>19.28</v>
       </c>
       <c r="G931" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="932">
@@ -28882,7 +28968,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -28891,10 +28977,13 @@
         </is>
       </c>
       <c r="E932">
-        <v>4.903333333333333</v>
+        <v>6.783333333333333</v>
+      </c>
+      <c r="F932">
+        <v>38.34</v>
       </c>
       <c r="G932" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="933">
@@ -28910,7 +28999,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -28919,10 +29008,13 @@
         </is>
       </c>
       <c r="E933">
-        <v>3.783333333333333</v>
+        <v>5.33</v>
+      </c>
+      <c r="F933">
+        <v>40.88</v>
       </c>
       <c r="G933" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="934">
@@ -28938,7 +29030,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -28947,10 +29039,13 @@
         </is>
       </c>
       <c r="E934">
-        <v>23.95333333333333</v>
+        <v>23.74</v>
+      </c>
+      <c r="F934">
+        <v>-0.89</v>
       </c>
       <c r="G934" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="935">
@@ -28966,7 +29061,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -28975,10 +29070,13 @@
         </is>
       </c>
       <c r="E935">
-        <v>14.2</v>
+        <v>12.435</v>
+      </c>
+      <c r="F935">
+        <v>-12.43</v>
       </c>
       <c r="G935" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="936">
@@ -28994,7 +29092,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -29003,10 +29101,13 @@
         </is>
       </c>
       <c r="E936">
-        <v>8.130000000000001</v>
+        <v>7.976666666666667</v>
+      </c>
+      <c r="F936">
+        <v>-1.89</v>
       </c>
       <c r="G936" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="937">
@@ -29022,7 +29123,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -29031,16 +29132,19 @@
         </is>
       </c>
       <c r="E937">
-        <v>6.693333333333333</v>
+        <v>7.606666666666666</v>
+      </c>
+      <c r="F937">
+        <v>13.65</v>
       </c>
       <c r="G937" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -29050,7 +29154,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -29059,16 +29163,19 @@
         </is>
       </c>
       <c r="E938">
-        <v>2.705</v>
+        <v>4.113333333333333</v>
+      </c>
+      <c r="F938">
+        <v>12.08</v>
       </c>
       <c r="G938" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -29078,7 +29185,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -29087,16 +29194,19 @@
         </is>
       </c>
       <c r="E939">
-        <v>3.72</v>
+        <v>3.7</v>
+      </c>
+      <c r="F939">
+        <v>-1.77</v>
       </c>
       <c r="G939" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -29106,7 +29216,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -29115,16 +29225,19 @@
         </is>
       </c>
       <c r="E940">
-        <v>5.140000000000001</v>
+        <v>4.42</v>
+      </c>
+      <c r="F940">
+        <v>0</v>
       </c>
       <c r="G940" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -29134,7 +29247,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -29143,16 +29256,19 @@
         </is>
       </c>
       <c r="E941">
-        <v>4.390000000000001</v>
+        <v>6.99</v>
+      </c>
+      <c r="F941">
+        <v>40.08</v>
       </c>
       <c r="G941" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -29162,7 +29278,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -29171,16 +29287,19 @@
         </is>
       </c>
       <c r="E942">
-        <v>48.94</v>
+        <v>25.49</v>
+      </c>
+      <c r="F942">
+        <v>1.72</v>
       </c>
       <c r="G942" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -29190,7 +29309,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -29199,16 +29318,19 @@
         </is>
       </c>
       <c r="E943">
-        <v>55.07</v>
+        <v>51</v>
+      </c>
+      <c r="F943">
+        <v>1.07</v>
       </c>
       <c r="G943" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -29218,7 +29340,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -29227,16 +29349,19 @@
         </is>
       </c>
       <c r="E944">
-        <v>3.12</v>
+        <v>4.43</v>
+      </c>
+      <c r="F944">
+        <v>0.38</v>
       </c>
       <c r="G944" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -29246,7 +29371,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -29255,16 +29380,19 @@
         </is>
       </c>
       <c r="E945">
-        <v>4.84</v>
+        <v>7.24</v>
+      </c>
+      <c r="F945">
+        <v>6.73</v>
       </c>
       <c r="G945" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -29274,7 +29402,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -29283,16 +29411,19 @@
         </is>
       </c>
       <c r="E946">
-        <v>4.234999999999999</v>
+        <v>5.68</v>
+      </c>
+      <c r="F946">
+        <v>6.57</v>
       </c>
       <c r="G946" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -29302,7 +29433,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -29311,16 +29442,19 @@
         </is>
       </c>
       <c r="E947">
-        <v>13.96</v>
+        <v>27.63666666666667</v>
+      </c>
+      <c r="F947">
+        <v>16.41</v>
       </c>
       <c r="G947" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -29330,7 +29464,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -29339,16 +29473,19 @@
         </is>
       </c>
       <c r="E948">
-        <v>14.94</v>
+        <v>12.435</v>
+      </c>
+      <c r="F948">
+        <v>0</v>
       </c>
       <c r="G948" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -29358,7 +29495,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -29367,16 +29504,19 @@
         </is>
       </c>
       <c r="E949">
-        <v>8.24</v>
+        <v>9.776666666666667</v>
+      </c>
+      <c r="F949">
+        <v>22.57</v>
       </c>
       <c r="G949" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
@@ -29386,7 +29526,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -29395,16 +29535,19 @@
         </is>
       </c>
       <c r="E950">
-        <v>8.460000000000001</v>
+        <v>7.673333333333333</v>
+      </c>
+      <c r="F950">
+        <v>0.88</v>
       </c>
       <c r="G950" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -29423,7 +29566,7 @@
         </is>
       </c>
       <c r="E951">
-        <v>2.633333333333333</v>
+        <v>2.705</v>
       </c>
       <c r="G951" s="2">
         <v>46113</v>
@@ -29432,7 +29575,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -29451,7 +29594,7 @@
         </is>
       </c>
       <c r="E952">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="G952" s="2">
         <v>46113</v>
@@ -29460,7 +29603,7 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -29479,7 +29622,7 @@
         </is>
       </c>
       <c r="E953">
-        <v>5.29</v>
+        <v>5.140000000000001</v>
       </c>
       <c r="G953" s="2">
         <v>46113</v>
@@ -29488,7 +29631,7 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
@@ -29507,7 +29650,7 @@
         </is>
       </c>
       <c r="E954">
-        <v>5.09</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="G954" s="2">
         <v>46113</v>
@@ -29516,7 +29659,7 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -29535,7 +29678,7 @@
         </is>
       </c>
       <c r="E955">
-        <v>52.37</v>
+        <v>48.94</v>
       </c>
       <c r="G955" s="2">
         <v>46113</v>
@@ -29544,7 +29687,7 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
@@ -29563,7 +29706,7 @@
         </is>
       </c>
       <c r="E956">
-        <v>60.96666666666667</v>
+        <v>55.07</v>
       </c>
       <c r="G956" s="2">
         <v>46113</v>
@@ -29572,7 +29715,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -29591,7 +29734,7 @@
         </is>
       </c>
       <c r="E957">
-        <v>3.836666666666666</v>
+        <v>3.12</v>
       </c>
       <c r="G957" s="2">
         <v>46113</v>
@@ -29600,7 +29743,7 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -29619,7 +29762,7 @@
         </is>
       </c>
       <c r="E958">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="G958" s="2">
         <v>46113</v>
@@ -29628,7 +29771,7 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -29647,7 +29790,7 @@
         </is>
       </c>
       <c r="E959">
-        <v>4.426666666666667</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="G959" s="2">
         <v>46113</v>
@@ -29656,7 +29799,7 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
@@ -29675,7 +29818,7 @@
         </is>
       </c>
       <c r="E960">
-        <v>16.92333333333333</v>
+        <v>13.96</v>
       </c>
       <c r="G960" s="2">
         <v>46113</v>
@@ -29684,7 +29827,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -29703,7 +29846,7 @@
         </is>
       </c>
       <c r="E961">
-        <v>17.86</v>
+        <v>14.94</v>
       </c>
       <c r="G961" s="2">
         <v>46113</v>
@@ -29712,7 +29855,7 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -29731,7 +29874,7 @@
         </is>
       </c>
       <c r="E962">
-        <v>8.933333333333334</v>
+        <v>8.24</v>
       </c>
       <c r="G962" s="2">
         <v>46113</v>
@@ -29740,7 +29883,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -29759,7 +29902,7 @@
         </is>
       </c>
       <c r="E963">
-        <v>8.673333333333334</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G963" s="2">
         <v>46113</v>
@@ -29778,7 +29921,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -29787,13 +29930,10 @@
         </is>
       </c>
       <c r="E964">
-        <v>3.256666666666667</v>
-      </c>
-      <c r="F964">
-        <v>23.67</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="G964" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="965">
@@ -29809,7 +29949,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -29818,13 +29958,10 @@
         </is>
       </c>
       <c r="E965">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F965">
-        <v>6.55</v>
+        <v>4.17</v>
       </c>
       <c r="G965" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="966">
@@ -29840,7 +29977,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -29849,13 +29986,10 @@
         </is>
       </c>
       <c r="E966">
-        <v>4.99</v>
-      </c>
-      <c r="F966">
-        <v>-5.67</v>
+        <v>5.29</v>
       </c>
       <c r="G966" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="967">
@@ -29871,7 +30005,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -29880,13 +30014,10 @@
         </is>
       </c>
       <c r="E967">
-        <v>6.293333333333334</v>
-      </c>
-      <c r="F967">
-        <v>23.64</v>
+        <v>5.09</v>
       </c>
       <c r="G967" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="968">
@@ -29902,7 +30033,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -29911,13 +30042,10 @@
         </is>
       </c>
       <c r="E968">
-        <v>23.41333333333333</v>
-      </c>
-      <c r="F968">
-        <v>-55.29</v>
+        <v>52.37</v>
       </c>
       <c r="G968" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="969">
@@ -29933,7 +30061,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -29942,13 +30070,10 @@
         </is>
       </c>
       <c r="E969">
-        <v>48.88</v>
-      </c>
-      <c r="F969">
-        <v>-19.83</v>
+        <v>60.96666666666667</v>
       </c>
       <c r="G969" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="970">
@@ -29964,7 +30089,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -29973,13 +30098,10 @@
         </is>
       </c>
       <c r="E970">
-        <v>3.996666666666667</v>
-      </c>
-      <c r="F970">
-        <v>4.17</v>
+        <v>3.836666666666666</v>
       </c>
       <c r="G970" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="971">
@@ -29995,7 +30117,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -30004,13 +30126,10 @@
         </is>
       </c>
       <c r="E971">
-        <v>6.433333333333334</v>
-      </c>
-      <c r="F971">
-        <v>31.56</v>
+        <v>4.89</v>
       </c>
       <c r="G971" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="972">
@@ -30026,7 +30145,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -30035,13 +30154,10 @@
         </is>
       </c>
       <c r="E972">
-        <v>5.12</v>
-      </c>
-      <c r="F972">
-        <v>15.66</v>
+        <v>4.426666666666667</v>
       </c>
       <c r="G972" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="973">
@@ -30057,7 +30173,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -30066,13 +30182,10 @@
         </is>
       </c>
       <c r="E973">
-        <v>31.21666666666667</v>
-      </c>
-      <c r="F973">
-        <v>84.45999999999999</v>
+        <v>16.92333333333333</v>
       </c>
       <c r="G973" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="974">
@@ -30088,7 +30201,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
@@ -30097,13 +30210,10 @@
         </is>
       </c>
       <c r="E974">
-        <v>15.26</v>
-      </c>
-      <c r="F974">
-        <v>-14.56</v>
+        <v>17.86</v>
       </c>
       <c r="G974" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="975">
@@ -30119,7 +30229,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -30128,13 +30238,10 @@
         </is>
       </c>
       <c r="E975">
-        <v>5.76</v>
-      </c>
-      <c r="F975">
-        <v>-35.52</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="G975" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="976">
@@ -30150,7 +30257,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -30159,13 +30266,10 @@
         </is>
       </c>
       <c r="E976">
-        <v>7.956666666666667</v>
-      </c>
-      <c r="F976">
-        <v>-8.26</v>
+        <v>8.673333333333334</v>
       </c>
       <c r="G976" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="977">
@@ -30181,7 +30285,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -30193,10 +30297,10 @@
         <v>3.256666666666667</v>
       </c>
       <c r="F977">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="G977" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="978">
@@ -30212,7 +30316,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -30224,10 +30328,10 @@
         <v>4.443333333333333</v>
       </c>
       <c r="F978">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="G978" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="979">
@@ -30243,7 +30347,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -30255,10 +30359,10 @@
         <v>4.99</v>
       </c>
       <c r="F979">
-        <v>0</v>
+        <v>-5.67</v>
       </c>
       <c r="G979" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="980">
@@ -30274,7 +30378,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -30283,13 +30387,13 @@
         </is>
       </c>
       <c r="E980">
-        <v>5.96</v>
+        <v>6.293333333333334</v>
       </c>
       <c r="F980">
-        <v>-5.3</v>
+        <v>23.64</v>
       </c>
       <c r="G980" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="981">
@@ -30305,7 +30409,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -30314,13 +30418,13 @@
         </is>
       </c>
       <c r="E981">
-        <v>22.8</v>
+        <v>23.41333333333333</v>
       </c>
       <c r="F981">
-        <v>-2.62</v>
+        <v>-55.29</v>
       </c>
       <c r="G981" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="982">
@@ -30336,7 +30440,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -30345,13 +30449,13 @@
         </is>
       </c>
       <c r="E982">
-        <v>48.27333333333333</v>
+        <v>48.88</v>
       </c>
       <c r="F982">
-        <v>-1.24</v>
+        <v>-19.83</v>
       </c>
       <c r="G982" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="983">
@@ -30367,7 +30471,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -30379,10 +30483,10 @@
         <v>3.996666666666667</v>
       </c>
       <c r="F983">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="G983" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="984">
@@ -30398,7 +30502,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -30410,10 +30514,10 @@
         <v>6.433333333333334</v>
       </c>
       <c r="F984">
-        <v>0</v>
+        <v>31.56</v>
       </c>
       <c r="G984" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="985">
@@ -30429,7 +30533,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -30438,13 +30542,13 @@
         </is>
       </c>
       <c r="E985">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="F985">
-        <v>-0.98</v>
+        <v>15.66</v>
       </c>
       <c r="G985" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="986">
@@ -30460,7 +30564,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -30469,13 +30573,13 @@
         </is>
       </c>
       <c r="E986">
-        <v>30.76333333333333</v>
+        <v>31.21666666666667</v>
       </c>
       <c r="F986">
-        <v>-1.45</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="G986" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="987">
@@ -30491,7 +30595,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -30503,10 +30607,10 @@
         <v>15.26</v>
       </c>
       <c r="F987">
-        <v>0</v>
+        <v>-14.56</v>
       </c>
       <c r="G987" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="988">
@@ -30522,7 +30626,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -30531,13 +30635,13 @@
         </is>
       </c>
       <c r="E988">
-        <v>5.49</v>
+        <v>5.76</v>
       </c>
       <c r="F988">
-        <v>-4.69</v>
+        <v>-35.52</v>
       </c>
       <c r="G988" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="989">
@@ -30553,7 +30657,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -30562,19 +30666,19 @@
         </is>
       </c>
       <c r="E989">
-        <v>7.906666666666667</v>
+        <v>7.956666666666667</v>
       </c>
       <c r="F989">
-        <v>-0.63</v>
+        <v>-8.26</v>
       </c>
       <c r="G989" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -30584,7 +30688,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -30593,16 +30697,19 @@
         </is>
       </c>
       <c r="E990">
-        <v>3.49</v>
+        <v>3.256666666666667</v>
+      </c>
+      <c r="F990">
+        <v>0</v>
       </c>
       <c r="G990" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -30612,7 +30719,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -30621,16 +30728,19 @@
         </is>
       </c>
       <c r="E991">
-        <v>3.75</v>
+        <v>4.443333333333333</v>
+      </c>
+      <c r="F991">
+        <v>0</v>
       </c>
       <c r="G991" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -30640,7 +30750,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -30649,16 +30759,19 @@
         </is>
       </c>
       <c r="E992">
-        <v>6.806666666666667</v>
+        <v>4.99</v>
+      </c>
+      <c r="F992">
+        <v>0</v>
       </c>
       <c r="G992" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -30668,7 +30781,7 @@
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -30677,16 +30790,19 @@
         </is>
       </c>
       <c r="E993">
-        <v>6.46</v>
+        <v>5.96</v>
+      </c>
+      <c r="F993">
+        <v>-5.3</v>
       </c>
       <c r="G993" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -30696,7 +30812,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -30705,16 +30821,19 @@
         </is>
       </c>
       <c r="E994">
-        <v>23.12333333333333</v>
+        <v>22.8</v>
+      </c>
+      <c r="F994">
+        <v>-2.62</v>
       </c>
       <c r="G994" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -30724,7 +30843,7 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -30733,16 +30852,19 @@
         </is>
       </c>
       <c r="E995">
-        <v>52.01666666666667</v>
+        <v>48.27333333333333</v>
+      </c>
+      <c r="F995">
+        <v>-1.24</v>
       </c>
       <c r="G995" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -30752,7 +30874,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -30761,16 +30883,19 @@
         </is>
       </c>
       <c r="E996">
-        <v>3.386666666666667</v>
+        <v>3.996666666666667</v>
+      </c>
+      <c r="F996">
+        <v>0</v>
       </c>
       <c r="G996" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -30780,7 +30905,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -30789,16 +30914,19 @@
         </is>
       </c>
       <c r="E997">
-        <v>5.926666666666667</v>
+        <v>6.433333333333334</v>
+      </c>
+      <c r="F997">
+        <v>0</v>
       </c>
       <c r="G997" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -30808,7 +30936,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -30817,16 +30945,19 @@
         </is>
       </c>
       <c r="E998">
-        <v>4.91</v>
+        <v>5.07</v>
+      </c>
+      <c r="F998">
+        <v>-0.98</v>
       </c>
       <c r="G998" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -30836,7 +30967,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -30845,16 +30976,19 @@
         </is>
       </c>
       <c r="E999">
-        <v>26.97</v>
+        <v>30.76333333333333</v>
+      </c>
+      <c r="F999">
+        <v>-1.45</v>
       </c>
       <c r="G999" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -30864,7 +30998,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -30873,16 +31007,19 @@
         </is>
       </c>
       <c r="E1000">
-        <v>15.68666666666667</v>
+        <v>15.26</v>
+      </c>
+      <c r="F1000">
+        <v>0</v>
       </c>
       <c r="G1000" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -30892,7 +31029,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -30901,16 +31038,19 @@
         </is>
       </c>
       <c r="E1001">
-        <v>8.286666666666667</v>
+        <v>5.49</v>
+      </c>
+      <c r="F1001">
+        <v>-4.69</v>
       </c>
       <c r="G1001" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -30920,7 +31060,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -30929,10 +31069,13 @@
         </is>
       </c>
       <c r="E1002">
-        <v>7.036666666666667</v>
+        <v>7.906666666666667</v>
+      </c>
+      <c r="F1002">
+        <v>-0.63</v>
       </c>
       <c r="G1002" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1003">
@@ -30948,7 +31091,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -30957,13 +31100,10 @@
         </is>
       </c>
       <c r="E1003">
-        <v>3.866666666666667</v>
-      </c>
-      <c r="F1003">
-        <v>10.79</v>
+        <v>3.49</v>
       </c>
       <c r="G1003" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1004">
@@ -30979,7 +31119,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -30988,13 +31128,10 @@
         </is>
       </c>
       <c r="E1004">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="F1004">
-        <v>-0.44</v>
+        <v>3.75</v>
       </c>
       <c r="G1004" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1005">
@@ -31010,7 +31147,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -31019,13 +31156,10 @@
         </is>
       </c>
       <c r="E1005">
-        <v>6.6</v>
-      </c>
-      <c r="F1005">
-        <v>-3.04</v>
+        <v>6.806666666666667</v>
       </c>
       <c r="G1005" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1006">
@@ -31041,7 +31175,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -31050,13 +31184,10 @@
         </is>
       </c>
       <c r="E1006">
-        <v>6.75</v>
-      </c>
-      <c r="F1006">
-        <v>4.49</v>
+        <v>6.46</v>
       </c>
       <c r="G1006" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1007">
@@ -31072,7 +31203,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -31081,13 +31212,10 @@
         </is>
       </c>
       <c r="E1007">
-        <v>23.51</v>
-      </c>
-      <c r="F1007">
-        <v>1.67</v>
+        <v>23.12333333333333</v>
       </c>
       <c r="G1007" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1008">
@@ -31103,7 +31231,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -31112,13 +31240,10 @@
         </is>
       </c>
       <c r="E1008">
-        <v>51.06</v>
-      </c>
-      <c r="F1008">
-        <v>-1.84</v>
+        <v>52.01666666666667</v>
       </c>
       <c r="G1008" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1009">
@@ -31134,7 +31259,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -31143,13 +31268,10 @@
         </is>
       </c>
       <c r="E1009">
-        <v>3.673333333333333</v>
-      </c>
-      <c r="F1009">
-        <v>8.460000000000001</v>
+        <v>3.386666666666667</v>
       </c>
       <c r="G1009" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1010">
@@ -31165,7 +31287,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
@@ -31174,13 +31296,10 @@
         </is>
       </c>
       <c r="E1010">
-        <v>6.32</v>
-      </c>
-      <c r="F1010">
-        <v>6.64</v>
+        <v>5.926666666666667</v>
       </c>
       <c r="G1010" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1011">
@@ -31196,7 +31315,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -31205,13 +31324,10 @@
         </is>
       </c>
       <c r="E1011">
-        <v>4.853333333333333</v>
-      </c>
-      <c r="F1011">
-        <v>-1.15</v>
+        <v>4.91</v>
       </c>
       <c r="G1011" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1012">
@@ -31227,7 +31343,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -31236,13 +31352,10 @@
         </is>
       </c>
       <c r="E1012">
-        <v>26.59333333333333</v>
-      </c>
-      <c r="F1012">
-        <v>-1.4</v>
+        <v>26.97</v>
       </c>
       <c r="G1012" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1013">
@@ -31258,7 +31371,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -31267,13 +31380,10 @@
         </is>
       </c>
       <c r="E1013">
-        <v>16.85</v>
-      </c>
-      <c r="F1013">
-        <v>7.42</v>
+        <v>15.68666666666667</v>
       </c>
       <c r="G1013" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1014">
@@ -31289,7 +31399,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -31298,13 +31408,10 @@
         </is>
       </c>
       <c r="E1014">
-        <v>13.12</v>
-      </c>
-      <c r="F1014">
-        <v>58.33</v>
+        <v>8.286666666666667</v>
       </c>
       <c r="G1014" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1015">
@@ -31320,7 +31427,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -31329,19 +31436,16 @@
         </is>
       </c>
       <c r="E1015">
-        <v>7.166666666666667</v>
-      </c>
-      <c r="F1015">
-        <v>1.85</v>
+        <v>7.036666666666667</v>
       </c>
       <c r="G1015" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
@@ -31351,7 +31455,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -31360,16 +31464,19 @@
         </is>
       </c>
       <c r="E1016">
-        <v>3.096666666666667</v>
+        <v>3.866666666666667</v>
+      </c>
+      <c r="F1016">
+        <v>10.79</v>
       </c>
       <c r="G1016" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -31379,7 +31486,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -31388,16 +31495,19 @@
         </is>
       </c>
       <c r="E1017">
-        <v>3.763333333333333</v>
+        <v>3.733333333333333</v>
+      </c>
+      <c r="F1017">
+        <v>-0.44</v>
       </c>
       <c r="G1017" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
@@ -31407,7 +31517,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -31416,16 +31526,19 @@
         </is>
       </c>
       <c r="E1018">
-        <v>5.626666666666667</v>
+        <v>6.6</v>
+      </c>
+      <c r="F1018">
+        <v>-3.04</v>
       </c>
       <c r="G1018" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -31435,7 +31548,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -31444,16 +31557,19 @@
         </is>
       </c>
       <c r="E1019">
-        <v>5.49</v>
+        <v>6.75</v>
+      </c>
+      <c r="F1019">
+        <v>4.49</v>
       </c>
       <c r="G1019" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
@@ -31463,7 +31579,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -31472,16 +31588,19 @@
         </is>
       </c>
       <c r="E1020">
-        <v>23.57333333333333</v>
+        <v>23.51</v>
+      </c>
+      <c r="F1020">
+        <v>1.67</v>
       </c>
       <c r="G1020" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -31491,7 +31610,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -31500,16 +31619,19 @@
         </is>
       </c>
       <c r="E1021">
-        <v>53.28666666666666</v>
+        <v>51.06</v>
+      </c>
+      <c r="F1021">
+        <v>-1.84</v>
       </c>
       <c r="G1021" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -31519,7 +31641,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -31528,16 +31650,19 @@
         </is>
       </c>
       <c r="E1022">
-        <v>4.1</v>
+        <v>3.673333333333333</v>
+      </c>
+      <c r="F1022">
+        <v>8.460000000000001</v>
       </c>
       <c r="G1022" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -31547,7 +31672,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -31556,16 +31681,19 @@
         </is>
       </c>
       <c r="E1023">
-        <v>6.54</v>
+        <v>6.32</v>
+      </c>
+      <c r="F1023">
+        <v>6.64</v>
       </c>
       <c r="G1023" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
@@ -31575,7 +31703,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -31584,16 +31712,19 @@
         </is>
       </c>
       <c r="E1024">
-        <v>5.776666666666666</v>
+        <v>4.853333333333333</v>
+      </c>
+      <c r="F1024">
+        <v>-1.15</v>
       </c>
       <c r="G1024" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -31603,7 +31734,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -31612,16 +31743,19 @@
         </is>
       </c>
       <c r="E1025">
-        <v>28.01666666666667</v>
+        <v>26.59333333333333</v>
+      </c>
+      <c r="F1025">
+        <v>-1.4</v>
       </c>
       <c r="G1025" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -31631,7 +31765,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
@@ -31640,16 +31774,19 @@
         </is>
       </c>
       <c r="E1026">
-        <v>14.9</v>
+        <v>16.85</v>
+      </c>
+      <c r="F1026">
+        <v>7.42</v>
       </c>
       <c r="G1026" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -31659,7 +31796,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -31668,16 +31805,19 @@
         </is>
       </c>
       <c r="E1027">
-        <v>9.120000000000001</v>
+        <v>13.12</v>
+      </c>
+      <c r="F1027">
+        <v>58.33</v>
       </c>
       <c r="G1027" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
@@ -31687,7 +31827,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -31696,10 +31836,13 @@
         </is>
       </c>
       <c r="E1028">
-        <v>8.6</v>
+        <v>7.166666666666667</v>
+      </c>
+      <c r="F1028">
+        <v>1.85</v>
       </c>
       <c r="G1028" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1029">
@@ -31715,7 +31858,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -31724,13 +31867,10 @@
         </is>
       </c>
       <c r="E1029">
-        <v>3.596666666666667</v>
-      </c>
-      <c r="F1029">
-        <v>16.15</v>
+        <v>3.096666666666667</v>
       </c>
       <c r="G1029" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1030">
@@ -31746,7 +31886,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -31755,13 +31895,10 @@
         </is>
       </c>
       <c r="E1030">
-        <v>3.693333333333333</v>
-      </c>
-      <c r="F1030">
-        <v>-1.86</v>
+        <v>3.763333333333333</v>
       </c>
       <c r="G1030" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1031">
@@ -31777,7 +31914,7 @@
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -31788,11 +31925,8 @@
       <c r="E1031">
         <v>5.626666666666667</v>
       </c>
-      <c r="F1031">
-        <v>0</v>
-      </c>
       <c r="G1031" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1032">
@@ -31808,7 +31942,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -31817,13 +31951,10 @@
         </is>
       </c>
       <c r="E1032">
-        <v>7.926666666666667</v>
-      </c>
-      <c r="F1032">
-        <v>44.38</v>
+        <v>5.49</v>
       </c>
       <c r="G1032" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1033">
@@ -31839,7 +31970,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -31848,13 +31979,10 @@
         </is>
       </c>
       <c r="E1033">
-        <v>26.01333333333333</v>
-      </c>
-      <c r="F1033">
-        <v>10.35</v>
+        <v>23.57333333333333</v>
       </c>
       <c r="G1033" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1034">
@@ -31870,7 +31998,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -31879,13 +32007,10 @@
         </is>
       </c>
       <c r="E1034">
-        <v>52.74</v>
-      </c>
-      <c r="F1034">
-        <v>-1.03</v>
+        <v>53.28666666666666</v>
       </c>
       <c r="G1034" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1035">
@@ -31901,7 +32026,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -31910,13 +32035,10 @@
         </is>
       </c>
       <c r="E1035">
-        <v>3.88</v>
-      </c>
-      <c r="F1035">
-        <v>-5.37</v>
+        <v>4.1</v>
       </c>
       <c r="G1035" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1036">
@@ -31932,7 +32054,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -31941,13 +32063,10 @@
         </is>
       </c>
       <c r="E1036">
-        <v>7.143333333333334</v>
-      </c>
-      <c r="F1036">
-        <v>9.23</v>
+        <v>6.54</v>
       </c>
       <c r="G1036" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1037">
@@ -31963,7 +32082,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -31972,13 +32091,10 @@
         </is>
       </c>
       <c r="E1037">
-        <v>5.826666666666667</v>
-      </c>
-      <c r="F1037">
-        <v>0.87</v>
+        <v>5.776666666666666</v>
       </c>
       <c r="G1037" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1038">
@@ -31994,7 +32110,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -32003,13 +32119,10 @@
         </is>
       </c>
       <c r="E1038">
-        <v>29.14666666666666</v>
-      </c>
-      <c r="F1038">
-        <v>4.03</v>
+        <v>28.01666666666667</v>
       </c>
       <c r="G1038" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1039">
@@ -32025,7 +32138,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -32036,11 +32149,8 @@
       <c r="E1039">
         <v>14.9</v>
       </c>
-      <c r="F1039">
-        <v>0</v>
-      </c>
       <c r="G1039" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1040">
@@ -32056,7 +32166,7 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -32065,13 +32175,10 @@
         </is>
       </c>
       <c r="E1040">
-        <v>12.32</v>
-      </c>
-      <c r="F1040">
-        <v>35.09</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="G1040" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1041">
@@ -32087,21 +32194,421 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1041">
+        <v>8.6</v>
+      </c>
+      <c r="G1041" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="D1041" t="inlineStr">
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1042">
+        <v>3.596666666666667</v>
+      </c>
+      <c r="F1042">
+        <v>16.15</v>
+      </c>
+      <c r="G1042" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1043">
+        <v>3.693333333333333</v>
+      </c>
+      <c r="F1043">
+        <v>-1.86</v>
+      </c>
+      <c r="G1043" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1044">
+        <v>5.626666666666667</v>
+      </c>
+      <c r="F1044">
+        <v>0</v>
+      </c>
+      <c r="G1044" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1045">
+        <v>7.926666666666667</v>
+      </c>
+      <c r="F1045">
+        <v>44.38</v>
+      </c>
+      <c r="G1045" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1046">
+        <v>26.01333333333333</v>
+      </c>
+      <c r="F1046">
+        <v>10.35</v>
+      </c>
+      <c r="G1046" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1047">
+        <v>52.74</v>
+      </c>
+      <c r="F1047">
+        <v>-1.03</v>
+      </c>
+      <c r="G1047" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1048">
+        <v>3.88</v>
+      </c>
+      <c r="F1048">
+        <v>-5.37</v>
+      </c>
+      <c r="G1048" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1049">
+        <v>7.143333333333334</v>
+      </c>
+      <c r="F1049">
+        <v>9.23</v>
+      </c>
+      <c r="G1049" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1050">
+        <v>5.826666666666667</v>
+      </c>
+      <c r="F1050">
+        <v>0.87</v>
+      </c>
+      <c r="G1050" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1051">
+        <v>29.14666666666666</v>
+      </c>
+      <c r="F1051">
+        <v>4.03</v>
+      </c>
+      <c r="G1051" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1052">
+        <v>14.9</v>
+      </c>
+      <c r="F1052">
+        <v>0</v>
+      </c>
+      <c r="G1052" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1053">
+        <v>12.32</v>
+      </c>
+      <c r="F1053">
+        <v>35.09</v>
+      </c>
+      <c r="G1053" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E1041">
+      <c r="E1054">
         <v>8.91</v>
       </c>
-      <c r="F1041">
+      <c r="F1054">
         <v>3.6</v>
       </c>
-      <c r="G1041" s="2">
+      <c r="G1054" s="2">
         <v>46266</v>
       </c>
     </row>

--- a/PRECOS.xlsx
+++ b/PRECOS.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1054"/>
+  <dimension ref="A1:G1080"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -26420,10 +26420,10 @@
         </is>
       </c>
       <c r="E847">
-        <v>3.44</v>
+        <v>3.623333333333334</v>
       </c>
       <c r="F847">
-        <v>-7.44</v>
+        <v>-2.51</v>
       </c>
       <c r="G847" s="2">
         <v>46235</v>
@@ -26451,10 +26451,10 @@
         </is>
       </c>
       <c r="E848">
-        <v>4.21</v>
+        <v>3.62</v>
       </c>
       <c r="F848">
-        <v>12.17</v>
+        <v>-3.55</v>
       </c>
       <c r="G848" s="2">
         <v>46235</v>
@@ -26482,10 +26482,10 @@
         </is>
       </c>
       <c r="E849">
-        <v>5.24</v>
+        <v>5.156666666666667</v>
       </c>
       <c r="F849">
-        <v>-15.26</v>
+        <v>-16.6</v>
       </c>
       <c r="G849" s="2">
         <v>46235</v>
@@ -26513,10 +26513,10 @@
         </is>
       </c>
       <c r="E850">
-        <v>4.79</v>
+        <v>4.856666666666666</v>
       </c>
       <c r="F850">
-        <v>12.44</v>
+        <v>14.01</v>
       </c>
       <c r="G850" s="2">
         <v>46235</v>
@@ -26544,10 +26544,10 @@
         </is>
       </c>
       <c r="E851">
-        <v>27.24</v>
+        <v>25.15666666666667</v>
       </c>
       <c r="F851">
-        <v>-4.79</v>
+        <v>-12.07</v>
       </c>
       <c r="G851" s="2">
         <v>46235</v>
@@ -26575,10 +26575,10 @@
         </is>
       </c>
       <c r="E852">
-        <v>47.93</v>
+        <v>51.25333333333333</v>
       </c>
       <c r="F852">
-        <v>-9.210000000000001</v>
+        <v>-2.92</v>
       </c>
       <c r="G852" s="2">
         <v>46235</v>
@@ -26606,10 +26606,10 @@
         </is>
       </c>
       <c r="E853">
-        <v>3.59</v>
+        <v>3.613333333333333</v>
       </c>
       <c r="F853">
-        <v>5.38</v>
+        <v>6.07</v>
       </c>
       <c r="G853" s="2">
         <v>46235</v>
@@ -26637,10 +26637,10 @@
         </is>
       </c>
       <c r="E854">
-        <v>4.890000000000001</v>
+        <v>5.09</v>
       </c>
       <c r="F854">
-        <v>-4.55</v>
+        <v>-0.65</v>
       </c>
       <c r="G854" s="2">
         <v>46235</v>
@@ -26668,10 +26668,10 @@
         </is>
       </c>
       <c r="E855">
-        <v>4.75</v>
+        <v>4.526666666666666</v>
       </c>
       <c r="F855">
-        <v>25</v>
+        <v>19.12</v>
       </c>
       <c r="G855" s="2">
         <v>46235</v>
@@ -26699,10 +26699,10 @@
         </is>
       </c>
       <c r="E856">
-        <v>20.54</v>
+        <v>24.49</v>
       </c>
       <c r="F856">
-        <v>-22.99</v>
+        <v>-8.19</v>
       </c>
       <c r="G856" s="2">
         <v>46235</v>
@@ -26730,10 +26730,10 @@
         </is>
       </c>
       <c r="E857">
-        <v>13.4</v>
+        <v>13.23</v>
       </c>
       <c r="F857">
-        <v>0.35</v>
+        <v>-0.92</v>
       </c>
       <c r="G857" s="2">
         <v>46235</v>
@@ -26761,10 +26761,10 @@
         </is>
       </c>
       <c r="E858">
-        <v>5.985</v>
+        <v>6.99</v>
       </c>
       <c r="F858">
-        <v>-53.89</v>
+        <v>-46.15</v>
       </c>
       <c r="G858" s="2">
         <v>46235</v>
@@ -26792,10 +26792,10 @@
         </is>
       </c>
       <c r="E859">
-        <v>7.725</v>
+        <v>7.363333333333333</v>
       </c>
       <c r="F859">
-        <v>-16.03</v>
+        <v>-19.96</v>
       </c>
       <c r="G859" s="2">
         <v>46235</v>
@@ -26804,7 +26804,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -26823,16 +26823,19 @@
         </is>
       </c>
       <c r="E860">
-        <v>3.3</v>
+        <v>3.26</v>
+      </c>
+      <c r="F860">
+        <v>-10.03</v>
       </c>
       <c r="G860" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -26842,7 +26845,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -26851,16 +26854,19 @@
         </is>
       </c>
       <c r="E861">
-        <v>4.353333333333333</v>
+        <v>3.49</v>
+      </c>
+      <c r="F861">
+        <v>-3.59</v>
       </c>
       <c r="G861" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -26870,7 +26876,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -26879,16 +26885,19 @@
         </is>
       </c>
       <c r="E862">
-        <v>5.976666666666667</v>
+        <v>4.99</v>
+      </c>
+      <c r="F862">
+        <v>-3.23</v>
       </c>
       <c r="G862" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -26898,7 +26907,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -26907,16 +26916,19 @@
         </is>
       </c>
       <c r="E863">
-        <v>4.78</v>
+        <v>7.99</v>
+      </c>
+      <c r="F863">
+        <v>64.52</v>
       </c>
       <c r="G863" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -26926,7 +26938,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -26935,16 +26947,19 @@
         </is>
       </c>
       <c r="E864">
-        <v>27.43</v>
+        <v>21.99</v>
+      </c>
+      <c r="F864">
+        <v>-12.59</v>
       </c>
       <c r="G864" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -26954,7 +26969,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -26963,16 +26978,19 @@
         </is>
       </c>
       <c r="E865">
-        <v>44.9</v>
+        <v>46.23</v>
+      </c>
+      <c r="F865">
+        <v>-9.800000000000001</v>
       </c>
       <c r="G865" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -26982,7 +27000,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -26991,16 +27009,19 @@
         </is>
       </c>
       <c r="E866">
-        <v>3.326666666666667</v>
+        <v>3.99</v>
+      </c>
+      <c r="F866">
+        <v>10.42</v>
       </c>
       <c r="G866" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -27010,7 +27031,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -27019,16 +27040,19 @@
         </is>
       </c>
       <c r="E867">
-        <v>5.3</v>
+        <v>4.56</v>
+      </c>
+      <c r="F867">
+        <v>-10.41</v>
       </c>
       <c r="G867" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -27038,7 +27062,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -27047,16 +27071,19 @@
         </is>
       </c>
       <c r="E868">
-        <v>3.806666666666667</v>
+        <v>4.66</v>
+      </c>
+      <c r="F868">
+        <v>2.95</v>
       </c>
       <c r="G868" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -27066,7 +27093,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -27075,16 +27102,19 @@
         </is>
       </c>
       <c r="E869">
-        <v>27.32333333333333</v>
+        <v>23.94</v>
+      </c>
+      <c r="F869">
+        <v>-2.25</v>
       </c>
       <c r="G869" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -27094,7 +27124,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -27103,16 +27133,19 @@
         </is>
       </c>
       <c r="E870">
-        <v>15.56666666666667</v>
+        <v>15.9</v>
+      </c>
+      <c r="F870">
+        <v>20.18</v>
       </c>
       <c r="G870" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -27122,7 +27155,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -27131,16 +27164,19 @@
         </is>
       </c>
       <c r="E871">
-        <v>10.32</v>
+        <v>12.99</v>
+      </c>
+      <c r="F871">
+        <v>85.84</v>
       </c>
       <c r="G871" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -27150,7 +27186,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -27159,16 +27195,19 @@
         </is>
       </c>
       <c r="E872">
-        <v>7.836666666666667</v>
+        <v>7.06</v>
+      </c>
+      <c r="F872">
+        <v>-4.12</v>
       </c>
       <c r="G872" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -27176,30 +27215,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C873" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D873" t="inlineStr">
         <is>
           <t>Arroz tipo 1</t>
         </is>
       </c>
       <c r="E873">
-        <v>3.39</v>
+        <v>3.696666666666667</v>
       </c>
       <c r="F873">
-        <v>2.73</v>
-      </c>
-      <c r="G873" s="2">
-        <v>46113</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -27207,30 +27238,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C874" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D874" t="inlineStr">
         <is>
           <t>Açúcar Refinado</t>
         </is>
       </c>
       <c r="E874">
-        <v>4.443333333333333</v>
+        <v>3.396666666666667</v>
       </c>
       <c r="F874">
-        <v>2.07</v>
-      </c>
-      <c r="G874" s="2">
-        <v>46113</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -27238,30 +27261,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C875" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D875" t="inlineStr">
         <is>
           <t>Banana</t>
         </is>
       </c>
       <c r="E875">
-        <v>6.56</v>
+        <v>5.653333333333333</v>
       </c>
       <c r="F875">
-        <v>9.76</v>
-      </c>
-      <c r="G875" s="2">
-        <v>46113</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -27269,30 +27284,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C876" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D876" t="inlineStr">
         <is>
           <t>Batata</t>
         </is>
       </c>
       <c r="E876">
-        <v>4.98</v>
+        <v>6.653333333333333</v>
       </c>
       <c r="F876">
-        <v>4.18</v>
-      </c>
-      <c r="G876" s="2">
-        <v>46113</v>
+        <v>-16.73</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -27300,30 +27307,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D877" t="inlineStr">
         <is>
           <t>Café em pó</t>
         </is>
       </c>
       <c r="E877">
-        <v>27.95333333333333</v>
+        <v>23.74</v>
       </c>
       <c r="F877">
-        <v>1.91</v>
-      </c>
-      <c r="G877" s="2">
-        <v>46113</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -27331,30 +27330,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D878" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
       <c r="E878">
-        <v>55.32666666666667</v>
+        <v>49.56</v>
       </c>
       <c r="F878">
-        <v>23.22</v>
-      </c>
-      <c r="G878" s="2">
-        <v>46113</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -27362,30 +27353,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D879" t="inlineStr">
         <is>
           <t>Farinha de Trigo</t>
         </is>
       </c>
       <c r="E879">
-        <v>3.45</v>
+        <v>3.78</v>
       </c>
       <c r="F879">
-        <v>3.71</v>
-      </c>
-      <c r="G879" s="2">
-        <v>46113</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -27393,30 +27376,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C880" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D880" t="inlineStr">
         <is>
           <t>Feijão Preto</t>
         </is>
       </c>
       <c r="E880">
-        <v>5.376666666666667</v>
+        <v>5.92</v>
       </c>
       <c r="F880">
-        <v>1.45</v>
-      </c>
-      <c r="G880" s="2">
-        <v>46113</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -27424,30 +27399,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D881" t="inlineStr">
         <is>
           <t>Leite</t>
         </is>
       </c>
       <c r="E881">
-        <v>4.22</v>
+        <v>5.056666666666667</v>
       </c>
       <c r="F881">
-        <v>10.86</v>
-      </c>
-      <c r="G881" s="2">
-        <v>46113</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -27455,30 +27422,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C882" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D882" t="inlineStr">
         <is>
           <t>Manteiga</t>
         </is>
       </c>
       <c r="E882">
-        <v>28.10333333333333</v>
+        <v>25.02666666666667</v>
       </c>
       <c r="F882">
-        <v>2.85</v>
-      </c>
-      <c r="G882" s="2">
-        <v>46113</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -27486,30 +27445,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C883" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D883" t="inlineStr">
         <is>
           <t>Pão Francês</t>
         </is>
       </c>
       <c r="E883">
-        <v>15.9</v>
+        <v>14.92666666666667</v>
       </c>
       <c r="F883">
-        <v>2.14</v>
-      </c>
-      <c r="G883" s="2">
-        <v>46113</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -27517,30 +27468,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C884" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D884" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
       <c r="E884">
-        <v>10.65333333333333</v>
+        <v>9.286666666666667</v>
       </c>
       <c r="F884">
-        <v>3.23</v>
-      </c>
-      <c r="G884" s="2">
-        <v>46113</v>
+        <v>-28.51</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -27548,24 +27491,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C885" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
       <c r="D885" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
       <c r="E885">
-        <v>7.993333333333333</v>
+        <v>7.436666666666667</v>
       </c>
       <c r="F885">
-        <v>2</v>
-      </c>
-      <c r="G885" s="2">
-        <v>46113</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="886">
@@ -27581,7 +27516,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -27590,13 +27525,10 @@
         </is>
       </c>
       <c r="E886">
-        <v>3.206666666666667</v>
-      </c>
-      <c r="F886">
-        <v>-5.41</v>
+        <v>3.3</v>
       </c>
       <c r="G886" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="887">
@@ -27612,7 +27544,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -27621,13 +27553,10 @@
         </is>
       </c>
       <c r="E887">
-        <v>3.663333333333334</v>
-      </c>
-      <c r="F887">
-        <v>-17.55</v>
+        <v>4.353333333333333</v>
       </c>
       <c r="G887" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="888">
@@ -27643,7 +27572,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
@@ -27652,13 +27581,10 @@
         </is>
       </c>
       <c r="E888">
-        <v>5.49</v>
-      </c>
-      <c r="F888">
-        <v>-16.31</v>
+        <v>5.976666666666667</v>
       </c>
       <c r="G888" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="889">
@@ -27674,7 +27600,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -27683,13 +27609,10 @@
         </is>
       </c>
       <c r="E889">
-        <v>4.853333333333333</v>
-      </c>
-      <c r="F889">
-        <v>-2.54</v>
+        <v>4.78</v>
       </c>
       <c r="G889" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="890">
@@ -27705,7 +27628,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -27714,13 +27637,10 @@
         </is>
       </c>
       <c r="E890">
-        <v>23.21</v>
-      </c>
-      <c r="F890">
-        <v>-16.97</v>
+        <v>27.43</v>
       </c>
       <c r="G890" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="891">
@@ -27736,7 +27656,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -27745,13 +27665,10 @@
         </is>
       </c>
       <c r="E891">
-        <v>49.02666666666666</v>
-      </c>
-      <c r="F891">
-        <v>-11.39</v>
+        <v>44.9</v>
       </c>
       <c r="G891" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="892">
@@ -27767,7 +27684,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -27776,13 +27693,10 @@
         </is>
       </c>
       <c r="E892">
-        <v>3.61</v>
-      </c>
-      <c r="F892">
-        <v>4.64</v>
+        <v>3.326666666666667</v>
       </c>
       <c r="G892" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="893">
@@ -27798,7 +27712,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -27807,13 +27721,10 @@
         </is>
       </c>
       <c r="E893">
-        <v>5.846666666666667</v>
-      </c>
-      <c r="F893">
-        <v>8.74</v>
+        <v>5.3</v>
       </c>
       <c r="G893" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="894">
@@ -27829,7 +27740,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -27838,13 +27749,10 @@
         </is>
       </c>
       <c r="E894">
-        <v>4.916666666666667</v>
-      </c>
-      <c r="F894">
-        <v>16.51</v>
+        <v>3.806666666666667</v>
       </c>
       <c r="G894" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="895">
@@ -27860,7 +27768,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -27869,13 +27777,10 @@
         </is>
       </c>
       <c r="E895">
-        <v>24.68666666666667</v>
-      </c>
-      <c r="F895">
-        <v>-12.16</v>
+        <v>27.32333333333333</v>
       </c>
       <c r="G895" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="896">
@@ -27891,7 +27796,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -27900,13 +27805,10 @@
         </is>
       </c>
       <c r="E896">
-        <v>13.9</v>
-      </c>
-      <c r="F896">
-        <v>-12.58</v>
+        <v>15.56666666666667</v>
       </c>
       <c r="G896" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="897">
@@ -27922,7 +27824,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -27931,13 +27833,10 @@
         </is>
       </c>
       <c r="E897">
-        <v>5.816666666666667</v>
-      </c>
-      <c r="F897">
-        <v>-45.4</v>
+        <v>10.32</v>
       </c>
       <c r="G897" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="898">
@@ -27953,7 +27852,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -27962,13 +27861,10 @@
         </is>
       </c>
       <c r="E898">
-        <v>7.043333333333333</v>
-      </c>
-      <c r="F898">
-        <v>-11.88</v>
+        <v>7.836666666666667</v>
       </c>
       <c r="G898" s="2">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="899">
@@ -27984,7 +27880,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -27993,13 +27889,13 @@
         </is>
       </c>
       <c r="E899">
-        <v>3.406666666666667</v>
+        <v>3.39</v>
       </c>
       <c r="F899">
-        <v>6.24</v>
+        <v>2.73</v>
       </c>
       <c r="G899" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="900">
@@ -28015,7 +27911,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -28024,13 +27920,13 @@
         </is>
       </c>
       <c r="E900">
-        <v>3.643333333333333</v>
+        <v>4.443333333333333</v>
       </c>
       <c r="F900">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G900" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="901">
@@ -28046,7 +27942,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -28055,13 +27951,13 @@
         </is>
       </c>
       <c r="E901">
-        <v>5.49</v>
+        <v>6.56</v>
       </c>
       <c r="F901">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="G901" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="902">
@@ -28077,7 +27973,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -28089,10 +27985,10 @@
         <v>4.98</v>
       </c>
       <c r="F902">
-        <v>2.61</v>
+        <v>4.18</v>
       </c>
       <c r="G902" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="903">
@@ -28108,7 +28004,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -28117,13 +28013,13 @@
         </is>
       </c>
       <c r="E903">
-        <v>22.64333333333333</v>
+        <v>27.95333333333333</v>
       </c>
       <c r="F903">
-        <v>-2.44</v>
+        <v>1.91</v>
       </c>
       <c r="G903" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="904">
@@ -28139,7 +28035,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -28148,13 +28044,13 @@
         </is>
       </c>
       <c r="E904">
-        <v>47.77333333333333</v>
+        <v>55.32666666666667</v>
       </c>
       <c r="F904">
-        <v>-2.56</v>
+        <v>23.22</v>
       </c>
       <c r="G904" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="905">
@@ -28170,7 +28066,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -28179,13 +28075,13 @@
         </is>
       </c>
       <c r="E905">
-        <v>3.583333333333333</v>
+        <v>3.45</v>
       </c>
       <c r="F905">
-        <v>-0.74</v>
+        <v>3.71</v>
       </c>
       <c r="G905" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="906">
@@ -28201,7 +28097,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -28210,13 +28106,13 @@
         </is>
       </c>
       <c r="E906">
-        <v>6.086666666666667</v>
+        <v>5.376666666666667</v>
       </c>
       <c r="F906">
-        <v>4.1</v>
+        <v>1.45</v>
       </c>
       <c r="G906" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="907">
@@ -28232,7 +28128,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -28241,13 +28137,13 @@
         </is>
       </c>
       <c r="E907">
-        <v>4.833333333333333</v>
+        <v>4.22</v>
       </c>
       <c r="F907">
-        <v>-1.69</v>
+        <v>10.86</v>
       </c>
       <c r="G907" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="908">
@@ -28263,7 +28159,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -28272,13 +28168,13 @@
         </is>
       </c>
       <c r="E908">
-        <v>25.47</v>
+        <v>28.10333333333333</v>
       </c>
       <c r="F908">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="G908" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="909">
@@ -28294,7 +28190,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -28303,13 +28199,13 @@
         </is>
       </c>
       <c r="E909">
-        <v>14.23333333333333</v>
+        <v>15.9</v>
       </c>
       <c r="F909">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="G909" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="910">
@@ -28325,7 +28221,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -28334,13 +28230,13 @@
         </is>
       </c>
       <c r="E910">
-        <v>11.98</v>
+        <v>10.65333333333333</v>
       </c>
       <c r="F910">
-        <v>105.96</v>
+        <v>3.23</v>
       </c>
       <c r="G910" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="911">
@@ -28356,7 +28252,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -28365,19 +28261,19 @@
         </is>
       </c>
       <c r="E911">
-        <v>7.123333333333333</v>
+        <v>7.993333333333333</v>
       </c>
       <c r="F911">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="G911" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -28387,7 +28283,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -28396,16 +28292,19 @@
         </is>
       </c>
       <c r="E912">
-        <v>3.393333333333334</v>
+        <v>3.206666666666667</v>
+      </c>
+      <c r="F912">
+        <v>-5.41</v>
       </c>
       <c r="G912" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -28415,7 +28314,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -28424,16 +28323,19 @@
         </is>
       </c>
       <c r="E913">
-        <v>3.69</v>
+        <v>3.663333333333334</v>
+      </c>
+      <c r="F913">
+        <v>-17.55</v>
       </c>
       <c r="G913" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -28443,7 +28345,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -28452,16 +28354,19 @@
         </is>
       </c>
       <c r="E914">
-        <v>6.066666666666666</v>
+        <v>5.49</v>
+      </c>
+      <c r="F914">
+        <v>-16.31</v>
       </c>
       <c r="G914" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -28471,7 +28376,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -28480,16 +28385,19 @@
         </is>
       </c>
       <c r="E915">
-        <v>3.826666666666667</v>
+        <v>4.853333333333333</v>
+      </c>
+      <c r="F915">
+        <v>-2.54</v>
       </c>
       <c r="G915" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -28499,7 +28407,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -28508,16 +28416,19 @@
         </is>
       </c>
       <c r="E916">
-        <v>28.97</v>
+        <v>23.21</v>
+      </c>
+      <c r="F916">
+        <v>-16.97</v>
       </c>
       <c r="G916" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -28527,7 +28438,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -28536,16 +28447,19 @@
         </is>
       </c>
       <c r="E917">
-        <v>43.38</v>
+        <v>49.02666666666666</v>
+      </c>
+      <c r="F917">
+        <v>-11.39</v>
       </c>
       <c r="G917" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -28555,7 +28469,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -28564,16 +28478,19 @@
         </is>
       </c>
       <c r="E918">
-        <v>3.7</v>
+        <v>3.61</v>
+      </c>
+      <c r="F918">
+        <v>4.64</v>
       </c>
       <c r="G918" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -28583,7 +28500,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -28592,16 +28509,19 @@
         </is>
       </c>
       <c r="E919">
-        <v>4.903333333333333</v>
+        <v>5.846666666666667</v>
+      </c>
+      <c r="F919">
+        <v>8.74</v>
       </c>
       <c r="G919" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -28611,7 +28531,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -28620,16 +28540,19 @@
         </is>
       </c>
       <c r="E920">
-        <v>3.783333333333333</v>
+        <v>4.916666666666667</v>
+      </c>
+      <c r="F920">
+        <v>16.51</v>
       </c>
       <c r="G920" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -28639,7 +28562,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -28648,16 +28571,19 @@
         </is>
       </c>
       <c r="E921">
-        <v>23.95333333333333</v>
+        <v>24.68666666666667</v>
+      </c>
+      <c r="F921">
+        <v>-12.16</v>
       </c>
       <c r="G921" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -28667,7 +28593,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -28676,16 +28602,19 @@
         </is>
       </c>
       <c r="E922">
-        <v>14.2</v>
+        <v>13.9</v>
+      </c>
+      <c r="F922">
+        <v>-12.58</v>
       </c>
       <c r="G922" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -28695,7 +28624,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -28704,16 +28633,19 @@
         </is>
       </c>
       <c r="E923">
-        <v>8.130000000000001</v>
+        <v>5.816666666666667</v>
+      </c>
+      <c r="F923">
+        <v>-45.4</v>
       </c>
       <c r="G923" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -28723,7 +28655,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -28732,16 +28664,19 @@
         </is>
       </c>
       <c r="E924">
-        <v>6.693333333333333</v>
+        <v>7.043333333333333</v>
+      </c>
+      <c r="F924">
+        <v>-11.88</v>
       </c>
       <c r="G924" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -28751,7 +28686,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -28760,19 +28695,19 @@
         </is>
       </c>
       <c r="E925">
-        <v>3.67</v>
+        <v>3.406666666666667</v>
       </c>
       <c r="F925">
-        <v>8.15</v>
+        <v>6.24</v>
       </c>
       <c r="G925" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -28782,7 +28717,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -28791,19 +28726,19 @@
         </is>
       </c>
       <c r="E926">
-        <v>3.766666666666667</v>
+        <v>3.643333333333333</v>
       </c>
       <c r="F926">
-        <v>2.08</v>
+        <v>-0.55</v>
       </c>
       <c r="G926" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -28813,7 +28748,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -28822,19 +28757,19 @@
         </is>
       </c>
       <c r="E927">
-        <v>4.42</v>
+        <v>5.49</v>
       </c>
       <c r="F927">
-        <v>-27.14</v>
+        <v>0</v>
       </c>
       <c r="G927" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -28844,7 +28779,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -28853,19 +28788,19 @@
         </is>
       </c>
       <c r="E928">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="F928">
-        <v>30.4</v>
+        <v>2.61</v>
       </c>
       <c r="G928" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -28875,7 +28810,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
@@ -28884,19 +28819,19 @@
         </is>
       </c>
       <c r="E929">
-        <v>25.06</v>
+        <v>22.64333333333333</v>
       </c>
       <c r="F929">
-        <v>-13.5</v>
+        <v>-2.44</v>
       </c>
       <c r="G929" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -28906,7 +28841,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -28915,19 +28850,19 @@
         </is>
       </c>
       <c r="E930">
-        <v>50.46</v>
+        <v>47.77333333333333</v>
       </c>
       <c r="F930">
-        <v>16.32</v>
+        <v>-2.56</v>
       </c>
       <c r="G930" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -28937,7 +28872,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
@@ -28946,19 +28881,19 @@
         </is>
       </c>
       <c r="E931">
-        <v>4.413333333333334</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="F931">
-        <v>19.28</v>
+        <v>-0.74</v>
       </c>
       <c r="G931" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -28968,7 +28903,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -28977,19 +28912,19 @@
         </is>
       </c>
       <c r="E932">
-        <v>6.783333333333333</v>
+        <v>6.086666666666667</v>
       </c>
       <c r="F932">
-        <v>38.34</v>
+        <v>4.1</v>
       </c>
       <c r="G932" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -28999,7 +28934,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -29008,19 +28943,19 @@
         </is>
       </c>
       <c r="E933">
-        <v>5.33</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="F933">
-        <v>40.88</v>
+        <v>-1.69</v>
       </c>
       <c r="G933" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -29030,7 +28965,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -29039,19 +28974,19 @@
         </is>
       </c>
       <c r="E934">
-        <v>23.74</v>
+        <v>25.47</v>
       </c>
       <c r="F934">
-        <v>-0.89</v>
+        <v>3.17</v>
       </c>
       <c r="G934" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -29061,7 +28996,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -29070,19 +29005,19 @@
         </is>
       </c>
       <c r="E935">
-        <v>12.435</v>
+        <v>14.23333333333333</v>
       </c>
       <c r="F935">
-        <v>-12.43</v>
+        <v>2.4</v>
       </c>
       <c r="G935" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -29092,7 +29027,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -29101,19 +29036,19 @@
         </is>
       </c>
       <c r="E936">
-        <v>7.976666666666667</v>
+        <v>11.98</v>
       </c>
       <c r="F936">
-        <v>-1.89</v>
+        <v>105.96</v>
       </c>
       <c r="G936" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -29123,7 +29058,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -29132,13 +29067,13 @@
         </is>
       </c>
       <c r="E937">
-        <v>7.606666666666666</v>
+        <v>7.123333333333333</v>
       </c>
       <c r="F937">
-        <v>13.65</v>
+        <v>1.14</v>
       </c>
       <c r="G937" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="938">
@@ -29154,7 +29089,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -29163,13 +29098,10 @@
         </is>
       </c>
       <c r="E938">
-        <v>4.113333333333333</v>
-      </c>
-      <c r="F938">
-        <v>12.08</v>
+        <v>3.393333333333334</v>
       </c>
       <c r="G938" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="939">
@@ -29185,7 +29117,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -29194,13 +29126,10 @@
         </is>
       </c>
       <c r="E939">
-        <v>3.7</v>
-      </c>
-      <c r="F939">
-        <v>-1.77</v>
+        <v>3.69</v>
       </c>
       <c r="G939" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="940">
@@ -29216,7 +29145,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -29225,13 +29154,10 @@
         </is>
       </c>
       <c r="E940">
-        <v>4.42</v>
-      </c>
-      <c r="F940">
-        <v>0</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="G940" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="941">
@@ -29247,7 +29173,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -29256,13 +29182,10 @@
         </is>
       </c>
       <c r="E941">
-        <v>6.99</v>
-      </c>
-      <c r="F941">
-        <v>40.08</v>
+        <v>3.826666666666667</v>
       </c>
       <c r="G941" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="942">
@@ -29278,7 +29201,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -29287,13 +29210,10 @@
         </is>
       </c>
       <c r="E942">
-        <v>25.49</v>
-      </c>
-      <c r="F942">
-        <v>1.72</v>
+        <v>28.97</v>
       </c>
       <c r="G942" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="943">
@@ -29309,7 +29229,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -29318,13 +29238,10 @@
         </is>
       </c>
       <c r="E943">
-        <v>51</v>
-      </c>
-      <c r="F943">
-        <v>1.07</v>
+        <v>43.38</v>
       </c>
       <c r="G943" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="944">
@@ -29340,7 +29257,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -29349,13 +29266,10 @@
         </is>
       </c>
       <c r="E944">
-        <v>4.43</v>
-      </c>
-      <c r="F944">
-        <v>0.38</v>
+        <v>3.7</v>
       </c>
       <c r="G944" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="945">
@@ -29371,7 +29285,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -29380,13 +29294,10 @@
         </is>
       </c>
       <c r="E945">
-        <v>7.24</v>
-      </c>
-      <c r="F945">
-        <v>6.73</v>
+        <v>4.903333333333333</v>
       </c>
       <c r="G945" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="946">
@@ -29402,7 +29313,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -29411,13 +29322,10 @@
         </is>
       </c>
       <c r="E946">
-        <v>5.68</v>
-      </c>
-      <c r="F946">
-        <v>6.57</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="G946" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="947">
@@ -29433,7 +29341,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -29442,13 +29350,10 @@
         </is>
       </c>
       <c r="E947">
-        <v>27.63666666666667</v>
-      </c>
-      <c r="F947">
-        <v>16.41</v>
+        <v>23.95333333333333</v>
       </c>
       <c r="G947" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="948">
@@ -29464,7 +29369,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -29473,13 +29378,10 @@
         </is>
       </c>
       <c r="E948">
-        <v>12.435</v>
-      </c>
-      <c r="F948">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="G948" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="949">
@@ -29495,7 +29397,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -29504,13 +29406,10 @@
         </is>
       </c>
       <c r="E949">
-        <v>9.776666666666667</v>
-      </c>
-      <c r="F949">
-        <v>22.57</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G949" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="950">
@@ -29526,7 +29425,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -29535,19 +29434,16 @@
         </is>
       </c>
       <c r="E950">
-        <v>7.673333333333333</v>
-      </c>
-      <c r="F950">
-        <v>0.88</v>
+        <v>6.693333333333333</v>
       </c>
       <c r="G950" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -29557,7 +29453,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -29566,16 +29462,19 @@
         </is>
       </c>
       <c r="E951">
-        <v>2.705</v>
+        <v>3.67</v>
+      </c>
+      <c r="F951">
+        <v>8.15</v>
       </c>
       <c r="G951" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -29585,7 +29484,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -29594,16 +29493,19 @@
         </is>
       </c>
       <c r="E952">
-        <v>3.72</v>
+        <v>3.766666666666667</v>
+      </c>
+      <c r="F952">
+        <v>2.08</v>
       </c>
       <c r="G952" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -29613,7 +29515,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -29622,16 +29524,19 @@
         </is>
       </c>
       <c r="E953">
-        <v>5.140000000000001</v>
+        <v>4.42</v>
+      </c>
+      <c r="F953">
+        <v>-27.14</v>
       </c>
       <c r="G953" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
@@ -29641,7 +29546,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -29650,16 +29555,19 @@
         </is>
       </c>
       <c r="E954">
-        <v>4.390000000000001</v>
+        <v>4.99</v>
+      </c>
+      <c r="F954">
+        <v>30.4</v>
       </c>
       <c r="G954" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -29669,7 +29577,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -29678,16 +29586,19 @@
         </is>
       </c>
       <c r="E955">
-        <v>48.94</v>
+        <v>25.06</v>
+      </c>
+      <c r="F955">
+        <v>-13.5</v>
       </c>
       <c r="G955" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
@@ -29697,7 +29608,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -29706,16 +29617,19 @@
         </is>
       </c>
       <c r="E956">
-        <v>55.07</v>
+        <v>50.46</v>
+      </c>
+      <c r="F956">
+        <v>16.32</v>
       </c>
       <c r="G956" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -29725,7 +29639,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -29734,16 +29648,19 @@
         </is>
       </c>
       <c r="E957">
-        <v>3.12</v>
+        <v>4.413333333333334</v>
+      </c>
+      <c r="F957">
+        <v>19.28</v>
       </c>
       <c r="G957" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -29753,7 +29670,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -29762,16 +29679,19 @@
         </is>
       </c>
       <c r="E958">
-        <v>4.84</v>
+        <v>6.783333333333333</v>
+      </c>
+      <c r="F958">
+        <v>38.34</v>
       </c>
       <c r="G958" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -29781,7 +29701,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -29790,16 +29710,19 @@
         </is>
       </c>
       <c r="E959">
-        <v>4.234999999999999</v>
+        <v>5.33</v>
+      </c>
+      <c r="F959">
+        <v>40.88</v>
       </c>
       <c r="G959" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
@@ -29809,7 +29732,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -29818,16 +29741,19 @@
         </is>
       </c>
       <c r="E960">
-        <v>13.96</v>
+        <v>23.74</v>
+      </c>
+      <c r="F960">
+        <v>-0.89</v>
       </c>
       <c r="G960" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -29837,7 +29763,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -29846,16 +29772,19 @@
         </is>
       </c>
       <c r="E961">
-        <v>14.94</v>
+        <v>12.435</v>
+      </c>
+      <c r="F961">
+        <v>-12.43</v>
       </c>
       <c r="G961" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -29865,7 +29794,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -29874,16 +29803,19 @@
         </is>
       </c>
       <c r="E962">
-        <v>8.24</v>
+        <v>7.976666666666667</v>
+      </c>
+      <c r="F962">
+        <v>-1.89</v>
       </c>
       <c r="G962" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -29893,7 +29825,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -29902,16 +29834,19 @@
         </is>
       </c>
       <c r="E963">
-        <v>8.460000000000001</v>
+        <v>7.606666666666666</v>
+      </c>
+      <c r="F963">
+        <v>13.65</v>
       </c>
       <c r="G963" s="2">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -29921,7 +29856,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -29930,16 +29865,19 @@
         </is>
       </c>
       <c r="E964">
-        <v>2.633333333333333</v>
+        <v>4.113333333333333</v>
+      </c>
+      <c r="F964">
+        <v>12.08</v>
       </c>
       <c r="G964" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -29949,7 +29887,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -29958,16 +29896,19 @@
         </is>
       </c>
       <c r="E965">
-        <v>4.17</v>
+        <v>3.7</v>
+      </c>
+      <c r="F965">
+        <v>-1.77</v>
       </c>
       <c r="G965" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -29977,7 +29918,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -29986,16 +29927,19 @@
         </is>
       </c>
       <c r="E966">
-        <v>5.29</v>
+        <v>4.42</v>
+      </c>
+      <c r="F966">
+        <v>0</v>
       </c>
       <c r="G966" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -30005,7 +29949,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -30014,16 +29958,19 @@
         </is>
       </c>
       <c r="E967">
-        <v>5.09</v>
+        <v>6.99</v>
+      </c>
+      <c r="F967">
+        <v>40.08</v>
       </c>
       <c r="G967" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -30033,7 +29980,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -30042,16 +29989,19 @@
         </is>
       </c>
       <c r="E968">
-        <v>52.37</v>
+        <v>25.49</v>
+      </c>
+      <c r="F968">
+        <v>1.72</v>
       </c>
       <c r="G968" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -30061,7 +30011,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -30070,16 +30020,19 @@
         </is>
       </c>
       <c r="E969">
-        <v>60.96666666666667</v>
+        <v>51</v>
+      </c>
+      <c r="F969">
+        <v>1.07</v>
       </c>
       <c r="G969" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -30089,7 +30042,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -30098,16 +30051,19 @@
         </is>
       </c>
       <c r="E970">
-        <v>3.836666666666666</v>
+        <v>4.43</v>
+      </c>
+      <c r="F970">
+        <v>0.38</v>
       </c>
       <c r="G970" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -30117,7 +30073,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -30126,16 +30082,19 @@
         </is>
       </c>
       <c r="E971">
-        <v>4.89</v>
+        <v>7.24</v>
+      </c>
+      <c r="F971">
+        <v>6.73</v>
       </c>
       <c r="G971" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -30145,7 +30104,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -30154,16 +30113,19 @@
         </is>
       </c>
       <c r="E972">
-        <v>4.426666666666667</v>
+        <v>5.68</v>
+      </c>
+      <c r="F972">
+        <v>6.57</v>
       </c>
       <c r="G972" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -30173,7 +30135,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -30182,16 +30144,19 @@
         </is>
       </c>
       <c r="E973">
-        <v>16.92333333333333</v>
+        <v>27.63666666666667</v>
+      </c>
+      <c r="F973">
+        <v>16.41</v>
       </c>
       <c r="G973" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -30201,7 +30166,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
@@ -30210,16 +30175,19 @@
         </is>
       </c>
       <c r="E974">
-        <v>17.86</v>
+        <v>12.435</v>
+      </c>
+      <c r="F974">
+        <v>0</v>
       </c>
       <c r="G974" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -30229,7 +30197,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -30238,16 +30206,19 @@
         </is>
       </c>
       <c r="E975">
-        <v>8.933333333333334</v>
+        <v>9.776666666666667</v>
+      </c>
+      <c r="F975">
+        <v>22.57</v>
       </c>
       <c r="G975" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -30257,7 +30228,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -30266,16 +30237,19 @@
         </is>
       </c>
       <c r="E976">
-        <v>8.673333333333334</v>
+        <v>7.673333333333333</v>
+      </c>
+      <c r="F976">
+        <v>0.88</v>
       </c>
       <c r="G976" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -30285,7 +30259,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -30294,19 +30268,16 @@
         </is>
       </c>
       <c r="E977">
-        <v>3.256666666666667</v>
-      </c>
-      <c r="F977">
-        <v>23.67</v>
+        <v>2.705</v>
       </c>
       <c r="G977" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -30316,7 +30287,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -30325,19 +30296,16 @@
         </is>
       </c>
       <c r="E978">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F978">
-        <v>6.55</v>
+        <v>3.72</v>
       </c>
       <c r="G978" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -30347,7 +30315,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -30356,19 +30324,16 @@
         </is>
       </c>
       <c r="E979">
-        <v>4.99</v>
-      </c>
-      <c r="F979">
-        <v>-5.67</v>
+        <v>5.140000000000001</v>
       </c>
       <c r="G979" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -30378,7 +30343,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -30387,19 +30352,16 @@
         </is>
       </c>
       <c r="E980">
-        <v>6.293333333333334</v>
-      </c>
-      <c r="F980">
-        <v>23.64</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="G980" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -30409,7 +30371,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -30418,19 +30380,16 @@
         </is>
       </c>
       <c r="E981">
-        <v>23.41333333333333</v>
-      </c>
-      <c r="F981">
-        <v>-55.29</v>
+        <v>48.94</v>
       </c>
       <c r="G981" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -30440,7 +30399,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -30449,19 +30408,16 @@
         </is>
       </c>
       <c r="E982">
-        <v>48.88</v>
-      </c>
-      <c r="F982">
-        <v>-19.83</v>
+        <v>55.07</v>
       </c>
       <c r="G982" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -30471,7 +30427,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -30480,19 +30436,16 @@
         </is>
       </c>
       <c r="E983">
-        <v>3.996666666666667</v>
-      </c>
-      <c r="F983">
-        <v>4.17</v>
+        <v>3.12</v>
       </c>
       <c r="G983" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -30502,7 +30455,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -30511,19 +30464,16 @@
         </is>
       </c>
       <c r="E984">
-        <v>6.433333333333334</v>
-      </c>
-      <c r="F984">
-        <v>31.56</v>
+        <v>4.84</v>
       </c>
       <c r="G984" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -30533,7 +30483,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -30542,19 +30492,16 @@
         </is>
       </c>
       <c r="E985">
-        <v>5.12</v>
-      </c>
-      <c r="F985">
-        <v>15.66</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="G985" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -30564,7 +30511,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -30573,19 +30520,16 @@
         </is>
       </c>
       <c r="E986">
-        <v>31.21666666666667</v>
-      </c>
-      <c r="F986">
-        <v>84.45999999999999</v>
+        <v>13.96</v>
       </c>
       <c r="G986" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -30595,7 +30539,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -30604,19 +30548,16 @@
         </is>
       </c>
       <c r="E987">
-        <v>15.26</v>
-      </c>
-      <c r="F987">
-        <v>-14.56</v>
+        <v>14.94</v>
       </c>
       <c r="G987" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -30626,7 +30567,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -30635,19 +30576,16 @@
         </is>
       </c>
       <c r="E988">
-        <v>5.76</v>
-      </c>
-      <c r="F988">
-        <v>-35.52</v>
+        <v>8.24</v>
       </c>
       <c r="G988" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -30657,7 +30595,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -30666,13 +30604,10 @@
         </is>
       </c>
       <c r="E989">
-        <v>7.956666666666667</v>
-      </c>
-      <c r="F989">
-        <v>-8.26</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G989" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="990">
@@ -30688,7 +30623,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -30697,13 +30632,10 @@
         </is>
       </c>
       <c r="E990">
-        <v>3.256666666666667</v>
-      </c>
-      <c r="F990">
-        <v>0</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="G990" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="991">
@@ -30719,7 +30651,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -30728,13 +30660,10 @@
         </is>
       </c>
       <c r="E991">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F991">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="G991" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="992">
@@ -30750,7 +30679,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -30759,13 +30688,10 @@
         </is>
       </c>
       <c r="E992">
-        <v>4.99</v>
-      </c>
-      <c r="F992">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="G992" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="993">
@@ -30781,7 +30707,7 @@
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -30790,13 +30716,10 @@
         </is>
       </c>
       <c r="E993">
-        <v>5.96</v>
-      </c>
-      <c r="F993">
-        <v>-5.3</v>
+        <v>5.09</v>
       </c>
       <c r="G993" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="994">
@@ -30812,7 +30735,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -30821,13 +30744,10 @@
         </is>
       </c>
       <c r="E994">
-        <v>22.8</v>
-      </c>
-      <c r="F994">
-        <v>-2.62</v>
+        <v>52.37</v>
       </c>
       <c r="G994" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="995">
@@ -30843,7 +30763,7 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -30852,13 +30772,10 @@
         </is>
       </c>
       <c r="E995">
-        <v>48.27333333333333</v>
-      </c>
-      <c r="F995">
-        <v>-1.24</v>
+        <v>60.96666666666667</v>
       </c>
       <c r="G995" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="996">
@@ -30874,7 +30791,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -30883,13 +30800,10 @@
         </is>
       </c>
       <c r="E996">
-        <v>3.996666666666667</v>
-      </c>
-      <c r="F996">
-        <v>0</v>
+        <v>3.836666666666666</v>
       </c>
       <c r="G996" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="997">
@@ -30905,7 +30819,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -30914,13 +30828,10 @@
         </is>
       </c>
       <c r="E997">
-        <v>6.433333333333334</v>
-      </c>
-      <c r="F997">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="G997" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="998">
@@ -30936,7 +30847,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -30945,13 +30856,10 @@
         </is>
       </c>
       <c r="E998">
-        <v>5.07</v>
-      </c>
-      <c r="F998">
-        <v>-0.98</v>
+        <v>4.426666666666667</v>
       </c>
       <c r="G998" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="999">
@@ -30967,7 +30875,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
@@ -30976,13 +30884,10 @@
         </is>
       </c>
       <c r="E999">
-        <v>30.76333333333333</v>
-      </c>
-      <c r="F999">
-        <v>-1.45</v>
+        <v>16.92333333333333</v>
       </c>
       <c r="G999" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1000">
@@ -30998,7 +30903,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -31007,13 +30912,10 @@
         </is>
       </c>
       <c r="E1000">
-        <v>15.26</v>
-      </c>
-      <c r="F1000">
-        <v>0</v>
+        <v>17.86</v>
       </c>
       <c r="G1000" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1001">
@@ -31029,7 +30931,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -31038,13 +30940,10 @@
         </is>
       </c>
       <c r="E1001">
-        <v>5.49</v>
-      </c>
-      <c r="F1001">
-        <v>-4.69</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="G1001" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1002">
@@ -31060,7 +30959,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -31069,19 +30968,16 @@
         </is>
       </c>
       <c r="E1002">
-        <v>7.906666666666667</v>
-      </c>
-      <c r="F1002">
-        <v>-0.63</v>
+        <v>8.673333333333334</v>
       </c>
       <c r="G1002" s="2">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -31100,7 +30996,10 @@
         </is>
       </c>
       <c r="E1003">
-        <v>3.49</v>
+        <v>3.256666666666667</v>
+      </c>
+      <c r="F1003">
+        <v>23.67</v>
       </c>
       <c r="G1003" s="2">
         <v>46235</v>
@@ -31109,7 +31008,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
@@ -31128,7 +31027,10 @@
         </is>
       </c>
       <c r="E1004">
-        <v>3.75</v>
+        <v>4.443333333333333</v>
+      </c>
+      <c r="F1004">
+        <v>6.55</v>
       </c>
       <c r="G1004" s="2">
         <v>46235</v>
@@ -31137,7 +31039,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -31156,7 +31058,10 @@
         </is>
       </c>
       <c r="E1005">
-        <v>6.806666666666667</v>
+        <v>4.99</v>
+      </c>
+      <c r="F1005">
+        <v>-5.67</v>
       </c>
       <c r="G1005" s="2">
         <v>46235</v>
@@ -31165,7 +31070,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -31184,7 +31089,10 @@
         </is>
       </c>
       <c r="E1006">
-        <v>6.46</v>
+        <v>6.293333333333334</v>
+      </c>
+      <c r="F1006">
+        <v>23.64</v>
       </c>
       <c r="G1006" s="2">
         <v>46235</v>
@@ -31193,7 +31101,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -31212,7 +31120,10 @@
         </is>
       </c>
       <c r="E1007">
-        <v>23.12333333333333</v>
+        <v>23.41333333333333</v>
+      </c>
+      <c r="F1007">
+        <v>-55.29</v>
       </c>
       <c r="G1007" s="2">
         <v>46235</v>
@@ -31221,7 +31132,7 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
@@ -31240,7 +31151,10 @@
         </is>
       </c>
       <c r="E1008">
-        <v>52.01666666666667</v>
+        <v>48.88</v>
+      </c>
+      <c r="F1008">
+        <v>-19.83</v>
       </c>
       <c r="G1008" s="2">
         <v>46235</v>
@@ -31249,7 +31163,7 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -31268,7 +31182,10 @@
         </is>
       </c>
       <c r="E1009">
-        <v>3.386666666666667</v>
+        <v>3.996666666666667</v>
+      </c>
+      <c r="F1009">
+        <v>4.17</v>
       </c>
       <c r="G1009" s="2">
         <v>46235</v>
@@ -31277,7 +31194,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
@@ -31296,7 +31213,10 @@
         </is>
       </c>
       <c r="E1010">
-        <v>5.926666666666667</v>
+        <v>6.433333333333334</v>
+      </c>
+      <c r="F1010">
+        <v>31.56</v>
       </c>
       <c r="G1010" s="2">
         <v>46235</v>
@@ -31305,7 +31225,7 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -31324,7 +31244,10 @@
         </is>
       </c>
       <c r="E1011">
-        <v>4.91</v>
+        <v>5.12</v>
+      </c>
+      <c r="F1011">
+        <v>15.66</v>
       </c>
       <c r="G1011" s="2">
         <v>46235</v>
@@ -31333,7 +31256,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
@@ -31352,7 +31275,10 @@
         </is>
       </c>
       <c r="E1012">
-        <v>26.97</v>
+        <v>31.21666666666667</v>
+      </c>
+      <c r="F1012">
+        <v>84.45999999999999</v>
       </c>
       <c r="G1012" s="2">
         <v>46235</v>
@@ -31361,7 +31287,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -31380,7 +31306,10 @@
         </is>
       </c>
       <c r="E1013">
-        <v>15.68666666666667</v>
+        <v>15.26</v>
+      </c>
+      <c r="F1013">
+        <v>-14.56</v>
       </c>
       <c r="G1013" s="2">
         <v>46235</v>
@@ -31389,7 +31318,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
@@ -31408,7 +31337,10 @@
         </is>
       </c>
       <c r="E1014">
-        <v>8.286666666666667</v>
+        <v>5.76</v>
+      </c>
+      <c r="F1014">
+        <v>-35.52</v>
       </c>
       <c r="G1014" s="2">
         <v>46235</v>
@@ -31417,7 +31349,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -31436,7 +31368,10 @@
         </is>
       </c>
       <c r="E1015">
-        <v>7.036666666666667</v>
+        <v>7.956666666666667</v>
+      </c>
+      <c r="F1015">
+        <v>-8.26</v>
       </c>
       <c r="G1015" s="2">
         <v>46235</v>
@@ -31445,7 +31380,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
@@ -31464,10 +31399,10 @@
         </is>
       </c>
       <c r="E1016">
-        <v>3.866666666666667</v>
+        <v>3.256666666666667</v>
       </c>
       <c r="F1016">
-        <v>10.79</v>
+        <v>0</v>
       </c>
       <c r="G1016" s="2">
         <v>46266</v>
@@ -31476,7 +31411,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -31495,10 +31430,10 @@
         </is>
       </c>
       <c r="E1017">
-        <v>3.733333333333333</v>
+        <v>4.443333333333333</v>
       </c>
       <c r="F1017">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="G1017" s="2">
         <v>46266</v>
@@ -31507,7 +31442,7 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
@@ -31526,10 +31461,10 @@
         </is>
       </c>
       <c r="E1018">
-        <v>6.6</v>
+        <v>4.99</v>
       </c>
       <c r="F1018">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="G1018" s="2">
         <v>46266</v>
@@ -31538,7 +31473,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -31557,10 +31492,10 @@
         </is>
       </c>
       <c r="E1019">
-        <v>6.75</v>
+        <v>5.96</v>
       </c>
       <c r="F1019">
-        <v>4.49</v>
+        <v>-5.3</v>
       </c>
       <c r="G1019" s="2">
         <v>46266</v>
@@ -31569,7 +31504,7 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
@@ -31588,10 +31523,10 @@
         </is>
       </c>
       <c r="E1020">
-        <v>23.51</v>
+        <v>22.8</v>
       </c>
       <c r="F1020">
-        <v>1.67</v>
+        <v>-2.62</v>
       </c>
       <c r="G1020" s="2">
         <v>46266</v>
@@ -31600,7 +31535,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -31619,10 +31554,10 @@
         </is>
       </c>
       <c r="E1021">
-        <v>51.06</v>
+        <v>48.27333333333333</v>
       </c>
       <c r="F1021">
-        <v>-1.84</v>
+        <v>-1.24</v>
       </c>
       <c r="G1021" s="2">
         <v>46266</v>
@@ -31631,7 +31566,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -31650,10 +31585,10 @@
         </is>
       </c>
       <c r="E1022">
-        <v>3.673333333333333</v>
+        <v>3.996666666666667</v>
       </c>
       <c r="F1022">
-        <v>8.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="G1022" s="2">
         <v>46266</v>
@@ -31662,7 +31597,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -31681,10 +31616,10 @@
         </is>
       </c>
       <c r="E1023">
-        <v>6.32</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="F1023">
-        <v>6.64</v>
+        <v>0</v>
       </c>
       <c r="G1023" s="2">
         <v>46266</v>
@@ -31693,7 +31628,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
@@ -31712,10 +31647,10 @@
         </is>
       </c>
       <c r="E1024">
-        <v>4.853333333333333</v>
+        <v>5.07</v>
       </c>
       <c r="F1024">
-        <v>-1.15</v>
+        <v>-0.98</v>
       </c>
       <c r="G1024" s="2">
         <v>46266</v>
@@ -31724,7 +31659,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -31743,10 +31678,10 @@
         </is>
       </c>
       <c r="E1025">
-        <v>26.59333333333333</v>
+        <v>30.76333333333333</v>
       </c>
       <c r="F1025">
-        <v>-1.4</v>
+        <v>-1.45</v>
       </c>
       <c r="G1025" s="2">
         <v>46266</v>
@@ -31755,7 +31690,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -31774,10 +31709,10 @@
         </is>
       </c>
       <c r="E1026">
-        <v>16.85</v>
+        <v>15.26</v>
       </c>
       <c r="F1026">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="G1026" s="2">
         <v>46266</v>
@@ -31786,7 +31721,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -31805,10 +31740,10 @@
         </is>
       </c>
       <c r="E1027">
-        <v>13.12</v>
+        <v>5.49</v>
       </c>
       <c r="F1027">
-        <v>58.33</v>
+        <v>-4.69</v>
       </c>
       <c r="G1027" s="2">
         <v>46266</v>
@@ -31817,7 +31752,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
@@ -31836,10 +31771,10 @@
         </is>
       </c>
       <c r="E1028">
-        <v>7.166666666666667</v>
+        <v>7.906666666666667</v>
       </c>
       <c r="F1028">
-        <v>1.85</v>
+        <v>-0.63</v>
       </c>
       <c r="G1028" s="2">
         <v>46266</v>
@@ -31848,7 +31783,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -31867,7 +31802,7 @@
         </is>
       </c>
       <c r="E1029">
-        <v>3.096666666666667</v>
+        <v>3.49</v>
       </c>
       <c r="G1029" s="2">
         <v>46235</v>
@@ -31876,7 +31811,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
@@ -31895,7 +31830,7 @@
         </is>
       </c>
       <c r="E1030">
-        <v>3.763333333333333</v>
+        <v>3.75</v>
       </c>
       <c r="G1030" s="2">
         <v>46235</v>
@@ -31904,7 +31839,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -31923,7 +31858,7 @@
         </is>
       </c>
       <c r="E1031">
-        <v>5.626666666666667</v>
+        <v>6.806666666666667</v>
       </c>
       <c r="G1031" s="2">
         <v>46235</v>
@@ -31932,7 +31867,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
@@ -31951,7 +31886,7 @@
         </is>
       </c>
       <c r="E1032">
-        <v>5.49</v>
+        <v>6.46</v>
       </c>
       <c r="G1032" s="2">
         <v>46235</v>
@@ -31960,7 +31895,7 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -31979,7 +31914,7 @@
         </is>
       </c>
       <c r="E1033">
-        <v>23.57333333333333</v>
+        <v>23.12333333333333</v>
       </c>
       <c r="G1033" s="2">
         <v>46235</v>
@@ -31988,7 +31923,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
@@ -32007,7 +31942,7 @@
         </is>
       </c>
       <c r="E1034">
-        <v>53.28666666666666</v>
+        <v>52.01666666666667</v>
       </c>
       <c r="G1034" s="2">
         <v>46235</v>
@@ -32016,7 +31951,7 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -32035,7 +31970,7 @@
         </is>
       </c>
       <c r="E1035">
-        <v>4.1</v>
+        <v>3.386666666666667</v>
       </c>
       <c r="G1035" s="2">
         <v>46235</v>
@@ -32044,7 +31979,7 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
@@ -32063,7 +31998,7 @@
         </is>
       </c>
       <c r="E1036">
-        <v>6.54</v>
+        <v>5.926666666666667</v>
       </c>
       <c r="G1036" s="2">
         <v>46235</v>
@@ -32072,7 +32007,7 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -32091,7 +32026,7 @@
         </is>
       </c>
       <c r="E1037">
-        <v>5.776666666666666</v>
+        <v>4.91</v>
       </c>
       <c r="G1037" s="2">
         <v>46235</v>
@@ -32100,7 +32035,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
@@ -32119,7 +32054,7 @@
         </is>
       </c>
       <c r="E1038">
-        <v>28.01666666666667</v>
+        <v>26.97</v>
       </c>
       <c r="G1038" s="2">
         <v>46235</v>
@@ -32128,7 +32063,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -32147,7 +32082,7 @@
         </is>
       </c>
       <c r="E1039">
-        <v>14.9</v>
+        <v>15.68666666666667</v>
       </c>
       <c r="G1039" s="2">
         <v>46235</v>
@@ -32156,7 +32091,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
@@ -32175,7 +32110,7 @@
         </is>
       </c>
       <c r="E1040">
-        <v>9.120000000000001</v>
+        <v>8.286666666666667</v>
       </c>
       <c r="G1040" s="2">
         <v>46235</v>
@@ -32184,7 +32119,7 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -32203,7 +32138,7 @@
         </is>
       </c>
       <c r="E1041">
-        <v>8.6</v>
+        <v>7.036666666666667</v>
       </c>
       <c r="G1041" s="2">
         <v>46235</v>
@@ -32212,7 +32147,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
@@ -32231,10 +32166,10 @@
         </is>
       </c>
       <c r="E1042">
-        <v>3.596666666666667</v>
+        <v>3.866666666666667</v>
       </c>
       <c r="F1042">
-        <v>16.15</v>
+        <v>10.79</v>
       </c>
       <c r="G1042" s="2">
         <v>46266</v>
@@ -32243,7 +32178,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -32262,10 +32197,10 @@
         </is>
       </c>
       <c r="E1043">
-        <v>3.693333333333333</v>
+        <v>3.733333333333333</v>
       </c>
       <c r="F1043">
-        <v>-1.86</v>
+        <v>-0.44</v>
       </c>
       <c r="G1043" s="2">
         <v>46266</v>
@@ -32274,7 +32209,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
@@ -32293,10 +32228,10 @@
         </is>
       </c>
       <c r="E1044">
-        <v>5.626666666666667</v>
+        <v>6.6</v>
       </c>
       <c r="F1044">
-        <v>0</v>
+        <v>-3.04</v>
       </c>
       <c r="G1044" s="2">
         <v>46266</v>
@@ -32305,7 +32240,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -32324,10 +32259,10 @@
         </is>
       </c>
       <c r="E1045">
-        <v>7.926666666666667</v>
+        <v>6.75</v>
       </c>
       <c r="F1045">
-        <v>44.38</v>
+        <v>4.49</v>
       </c>
       <c r="G1045" s="2">
         <v>46266</v>
@@ -32336,7 +32271,7 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
@@ -32355,10 +32290,10 @@
         </is>
       </c>
       <c r="E1046">
-        <v>26.01333333333333</v>
+        <v>23.51</v>
       </c>
       <c r="F1046">
-        <v>10.35</v>
+        <v>1.67</v>
       </c>
       <c r="G1046" s="2">
         <v>46266</v>
@@ -32367,7 +32302,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -32386,10 +32321,10 @@
         </is>
       </c>
       <c r="E1047">
-        <v>52.74</v>
+        <v>51.06</v>
       </c>
       <c r="F1047">
-        <v>-1.03</v>
+        <v>-1.84</v>
       </c>
       <c r="G1047" s="2">
         <v>46266</v>
@@ -32398,7 +32333,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
@@ -32417,10 +32352,10 @@
         </is>
       </c>
       <c r="E1048">
-        <v>3.88</v>
+        <v>3.673333333333333</v>
       </c>
       <c r="F1048">
-        <v>-5.37</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G1048" s="2">
         <v>46266</v>
@@ -32429,7 +32364,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -32448,10 +32383,10 @@
         </is>
       </c>
       <c r="E1049">
-        <v>7.143333333333334</v>
+        <v>6.32</v>
       </c>
       <c r="F1049">
-        <v>9.23</v>
+        <v>6.64</v>
       </c>
       <c r="G1049" s="2">
         <v>46266</v>
@@ -32460,7 +32395,7 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
@@ -32479,10 +32414,10 @@
         </is>
       </c>
       <c r="E1050">
-        <v>5.826666666666667</v>
+        <v>4.853333333333333</v>
       </c>
       <c r="F1050">
-        <v>0.87</v>
+        <v>-1.15</v>
       </c>
       <c r="G1050" s="2">
         <v>46266</v>
@@ -32491,7 +32426,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -32510,10 +32445,10 @@
         </is>
       </c>
       <c r="E1051">
-        <v>29.14666666666666</v>
+        <v>26.59333333333333</v>
       </c>
       <c r="F1051">
-        <v>4.03</v>
+        <v>-1.4</v>
       </c>
       <c r="G1051" s="2">
         <v>46266</v>
@@ -32522,7 +32457,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
@@ -32541,10 +32476,10 @@
         </is>
       </c>
       <c r="E1052">
-        <v>14.9</v>
+        <v>16.85</v>
       </c>
       <c r="F1052">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="G1052" s="2">
         <v>46266</v>
@@ -32553,7 +32488,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -32572,10 +32507,10 @@
         </is>
       </c>
       <c r="E1053">
-        <v>12.32</v>
+        <v>13.12</v>
       </c>
       <c r="F1053">
-        <v>35.09</v>
+        <v>58.33</v>
       </c>
       <c r="G1053" s="2">
         <v>46266</v>
@@ -32584,31 +32519,798 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
+          <t>Balneário Camboriú</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1054">
+        <v>7.166666666666667</v>
+      </c>
+      <c r="F1054">
+        <v>1.85</v>
+      </c>
+      <c r="G1054" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
           <t>Pomerode</t>
         </is>
       </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C1054" t="inlineStr">
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1055">
+        <v>3.096666666666667</v>
+      </c>
+      <c r="G1055" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1056">
+        <v>3.763333333333333</v>
+      </c>
+      <c r="G1056" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1057">
+        <v>5.626666666666667</v>
+      </c>
+      <c r="G1057" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1058">
+        <v>5.49</v>
+      </c>
+      <c r="G1058" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1059">
+        <v>23.57333333333333</v>
+      </c>
+      <c r="G1059" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1060">
+        <v>53.28666666666666</v>
+      </c>
+      <c r="G1060" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1061">
+        <v>4.1</v>
+      </c>
+      <c r="G1061" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1062">
+        <v>6.54</v>
+      </c>
+      <c r="G1062" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1063">
+        <v>5.776666666666666</v>
+      </c>
+      <c r="G1063" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1064">
+        <v>28.01666666666667</v>
+      </c>
+      <c r="G1064" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1065">
+        <v>14.9</v>
+      </c>
+      <c r="G1065" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1066">
+        <v>9.120000000000001</v>
+      </c>
+      <c r="G1066" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1067">
+        <v>8.6</v>
+      </c>
+      <c r="G1067" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
         <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="D1054" t="inlineStr">
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1068">
+        <v>3.596666666666667</v>
+      </c>
+      <c r="F1068">
+        <v>16.15</v>
+      </c>
+      <c r="G1068" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1069">
+        <v>3.693333333333333</v>
+      </c>
+      <c r="F1069">
+        <v>-1.86</v>
+      </c>
+      <c r="G1069" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1070">
+        <v>5.626666666666667</v>
+      </c>
+      <c r="F1070">
+        <v>0</v>
+      </c>
+      <c r="G1070" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1071">
+        <v>7.926666666666667</v>
+      </c>
+      <c r="F1071">
+        <v>44.38</v>
+      </c>
+      <c r="G1071" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1072">
+        <v>26.01333333333333</v>
+      </c>
+      <c r="F1072">
+        <v>10.35</v>
+      </c>
+      <c r="G1072" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1073">
+        <v>52.74</v>
+      </c>
+      <c r="F1073">
+        <v>-1.03</v>
+      </c>
+      <c r="G1073" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1074">
+        <v>3.88</v>
+      </c>
+      <c r="F1074">
+        <v>-5.37</v>
+      </c>
+      <c r="G1074" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1075">
+        <v>7.143333333333334</v>
+      </c>
+      <c r="F1075">
+        <v>9.23</v>
+      </c>
+      <c r="G1075" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1076">
+        <v>5.826666666666667</v>
+      </c>
+      <c r="F1076">
+        <v>0.87</v>
+      </c>
+      <c r="G1076" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1077">
+        <v>29.14666666666666</v>
+      </c>
+      <c r="F1077">
+        <v>4.03</v>
+      </c>
+      <c r="G1077" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1078">
+        <v>14.9</v>
+      </c>
+      <c r="F1078">
+        <v>0</v>
+      </c>
+      <c r="G1078" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1079">
+        <v>12.32</v>
+      </c>
+      <c r="F1079">
+        <v>35.09</v>
+      </c>
+      <c r="G1079" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E1054">
+      <c r="E1080">
         <v>8.91</v>
       </c>
-      <c r="F1054">
+      <c r="F1080">
         <v>3.6</v>
       </c>
-      <c r="G1054" s="2">
+      <c r="G1080" s="2">
         <v>46266</v>
       </c>
     </row>

--- a/PRECOS.xlsx
+++ b/PRECOS.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1080"/>
+  <dimension ref="A1:G1093"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -22891,12 +22891,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -22910,21 +22910,24 @@
         </is>
       </c>
       <c r="E730">
-        <v>3.425</v>
+        <v>4.163333333333333</v>
+      </c>
+      <c r="F730">
+        <v>-0.87</v>
       </c>
       <c r="G730" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -22938,21 +22941,24 @@
         </is>
       </c>
       <c r="E731">
-        <v>3.985</v>
+        <v>3.79</v>
+      </c>
+      <c r="F731">
+        <v>-5.72</v>
       </c>
       <c r="G731" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -22966,21 +22972,24 @@
         </is>
       </c>
       <c r="E732">
-        <v>7.345000000000001</v>
+        <v>6.453333333333333</v>
+      </c>
+      <c r="F732">
+        <v>7.8</v>
       </c>
       <c r="G732" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -22994,21 +23003,24 @@
         </is>
       </c>
       <c r="E733">
-        <v>3.18</v>
+        <v>6.99</v>
+      </c>
+      <c r="F733">
+        <v>31.64</v>
       </c>
       <c r="G733" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -23022,21 +23034,24 @@
         </is>
       </c>
       <c r="E734">
-        <v>30.17</v>
+        <v>25.88</v>
+      </c>
+      <c r="F734">
+        <v>-0.42</v>
       </c>
       <c r="G734" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -23050,21 +23065,24 @@
         </is>
       </c>
       <c r="E735">
-        <v>47.55</v>
+        <v>35.99</v>
+      </c>
+      <c r="F735">
+        <v>-8.859999999999999</v>
       </c>
       <c r="G735" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -23078,21 +23096,24 @@
         </is>
       </c>
       <c r="E736">
-        <v>3.575</v>
+        <v>3.906666666666666</v>
+      </c>
+      <c r="F736">
+        <v>0.86</v>
       </c>
       <c r="G736" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -23106,21 +23127,24 @@
         </is>
       </c>
       <c r="E737">
-        <v>4.78</v>
+        <v>6.493333333333333</v>
+      </c>
+      <c r="F737">
+        <v>2.8</v>
       </c>
       <c r="G737" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -23134,21 +23158,24 @@
         </is>
       </c>
       <c r="E738">
-        <v>4.529999999999999</v>
+        <v>5.12</v>
+      </c>
+      <c r="F738">
+        <v>0</v>
       </c>
       <c r="G738" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -23162,21 +23189,24 @@
         </is>
       </c>
       <c r="E739">
-        <v>28.02</v>
+        <v>29.15666666666667</v>
+      </c>
+      <c r="F739">
+        <v>5.42</v>
       </c>
       <c r="G739" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -23190,21 +23220,24 @@
         </is>
       </c>
       <c r="E740">
-        <v>17.425</v>
+        <v>14.23333333333333</v>
+      </c>
+      <c r="F740">
+        <v>4.91</v>
       </c>
       <c r="G740" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -23218,21 +23251,24 @@
         </is>
       </c>
       <c r="E741">
-        <v>6.359999999999999</v>
+        <v>12.31</v>
+      </c>
+      <c r="F741">
+        <v>51.17</v>
       </c>
       <c r="G741" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Gaspar</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -23246,10 +23282,13 @@
         </is>
       </c>
       <c r="E742">
-        <v>7.57</v>
+        <v>7.546666666666667</v>
+      </c>
+      <c r="F742">
+        <v>0.89</v>
       </c>
       <c r="G742" s="2">
-        <v>45901</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="743">
@@ -23265,7 +23304,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -23274,13 +23313,10 @@
         </is>
       </c>
       <c r="E743">
-        <v>3.18</v>
-      </c>
-      <c r="F743">
-        <v>-7.15</v>
+        <v>3.425</v>
       </c>
       <c r="G743" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="744">
@@ -23296,7 +23332,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -23305,13 +23341,10 @@
         </is>
       </c>
       <c r="E744">
-        <v>3.925</v>
-      </c>
-      <c r="F744">
-        <v>-1.51</v>
+        <v>3.985</v>
       </c>
       <c r="G744" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="745">
@@ -23327,7 +23360,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -23336,13 +23369,10 @@
         </is>
       </c>
       <c r="E745">
-        <v>7.515</v>
-      </c>
-      <c r="F745">
-        <v>2.31</v>
+        <v>7.345000000000001</v>
       </c>
       <c r="G745" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="746">
@@ -23358,7 +23388,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -23367,13 +23397,10 @@
         </is>
       </c>
       <c r="E746">
-        <v>3.005</v>
-      </c>
-      <c r="F746">
-        <v>-5.5</v>
+        <v>3.18</v>
       </c>
       <c r="G746" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="747">
@@ -23389,7 +23416,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -23398,13 +23425,10 @@
         </is>
       </c>
       <c r="E747">
-        <v>30.065</v>
-      </c>
-      <c r="F747">
-        <v>-0.35</v>
+        <v>30.17</v>
       </c>
       <c r="G747" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="748">
@@ -23420,7 +23444,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -23429,13 +23453,10 @@
         </is>
       </c>
       <c r="E748">
-        <v>47.545</v>
-      </c>
-      <c r="F748">
-        <v>-0.01</v>
+        <v>47.55</v>
       </c>
       <c r="G748" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="749">
@@ -23451,7 +23472,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -23460,13 +23481,10 @@
         </is>
       </c>
       <c r="E749">
-        <v>3.655</v>
-      </c>
-      <c r="F749">
-        <v>2.24</v>
+        <v>3.575</v>
       </c>
       <c r="G749" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="750">
@@ -23482,7 +23500,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -23491,13 +23509,10 @@
         </is>
       </c>
       <c r="E750">
-        <v>4.905</v>
-      </c>
-      <c r="F750">
-        <v>2.62</v>
+        <v>4.78</v>
       </c>
       <c r="G750" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="751">
@@ -23513,7 +23528,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -23522,13 +23537,10 @@
         </is>
       </c>
       <c r="E751">
-        <v>4.45</v>
-      </c>
-      <c r="F751">
-        <v>-1.77</v>
+        <v>4.529999999999999</v>
       </c>
       <c r="G751" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="752">
@@ -23544,7 +23556,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -23553,13 +23565,10 @@
         </is>
       </c>
       <c r="E752">
-        <v>27.435</v>
-      </c>
-      <c r="F752">
-        <v>-2.09</v>
+        <v>28.02</v>
       </c>
       <c r="G752" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="753">
@@ -23575,7 +23584,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -23586,11 +23595,8 @@
       <c r="E753">
         <v>17.425</v>
       </c>
-      <c r="F753">
-        <v>0</v>
-      </c>
       <c r="G753" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="754">
@@ -23606,7 +23612,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -23615,13 +23621,10 @@
         </is>
       </c>
       <c r="E754">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F754">
-        <v>31.76</v>
+        <v>6.359999999999999</v>
       </c>
       <c r="G754" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="755">
@@ -23637,7 +23640,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Outubro</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -23646,13 +23649,10 @@
         </is>
       </c>
       <c r="E755">
-        <v>7.775</v>
-      </c>
-      <c r="F755">
-        <v>2.71</v>
+        <v>7.57</v>
       </c>
       <c r="G755" s="2">
-        <v>45931</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="756">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -23677,13 +23677,13 @@
         </is>
       </c>
       <c r="E756">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="F756">
-        <v>-0.63</v>
+        <v>-7.15</v>
       </c>
       <c r="G756" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="757">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -23708,13 +23708,13 @@
         </is>
       </c>
       <c r="E757">
-        <v>3.73</v>
+        <v>3.925</v>
       </c>
       <c r="F757">
-        <v>-4.97</v>
+        <v>-1.51</v>
       </c>
       <c r="G757" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="758">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -23739,13 +23739,13 @@
         </is>
       </c>
       <c r="E758">
-        <v>7.11</v>
+        <v>7.515</v>
       </c>
       <c r="F758">
-        <v>-5.39</v>
+        <v>2.31</v>
       </c>
       <c r="G758" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="759">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -23770,13 +23770,13 @@
         </is>
       </c>
       <c r="E759">
-        <v>2.79</v>
+        <v>3.005</v>
       </c>
       <c r="F759">
-        <v>-7.15</v>
+        <v>-5.5</v>
       </c>
       <c r="G759" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="760">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -23801,13 +23801,13 @@
         </is>
       </c>
       <c r="E760">
-        <v>29.79</v>
+        <v>30.065</v>
       </c>
       <c r="F760">
-        <v>-0.91</v>
+        <v>-0.35</v>
       </c>
       <c r="G760" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="761">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -23832,13 +23832,13 @@
         </is>
       </c>
       <c r="E761">
-        <v>47.23</v>
+        <v>47.545</v>
       </c>
       <c r="F761">
-        <v>-0.66</v>
+        <v>-0.01</v>
       </c>
       <c r="G761" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="762">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -23863,13 +23863,13 @@
         </is>
       </c>
       <c r="E762">
-        <v>3.45</v>
+        <v>3.655</v>
       </c>
       <c r="F762">
-        <v>-5.61</v>
+        <v>2.24</v>
       </c>
       <c r="G762" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="763">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -23894,13 +23894,13 @@
         </is>
       </c>
       <c r="E763">
-        <v>4.56</v>
+        <v>4.905</v>
       </c>
       <c r="F763">
-        <v>-7.03</v>
+        <v>2.62</v>
       </c>
       <c r="G763" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="764">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -23925,13 +23925,13 @@
         </is>
       </c>
       <c r="E764">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="F764">
-        <v>-11.91</v>
+        <v>-1.77</v>
       </c>
       <c r="G764" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="765">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -23956,13 +23956,13 @@
         </is>
       </c>
       <c r="E765">
-        <v>25.37</v>
+        <v>27.435</v>
       </c>
       <c r="F765">
-        <v>-7.53</v>
+        <v>-2.09</v>
       </c>
       <c r="G765" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="766">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -23987,13 +23987,13 @@
         </is>
       </c>
       <c r="E766">
-        <v>17.9</v>
+        <v>17.425</v>
       </c>
       <c r="F766">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="G766" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="767">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="E767">
-        <v>6.79</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F767">
-        <v>-18.97</v>
+        <v>31.76</v>
       </c>
       <c r="G767" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="768">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Novembro</t>
+          <t>Outubro</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -24049,13 +24049,13 @@
         </is>
       </c>
       <c r="E768">
-        <v>7.96</v>
+        <v>7.775</v>
       </c>
       <c r="F768">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="G768" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="769">
@@ -24066,12 +24066,12 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -24080,13 +24080,13 @@
         </is>
       </c>
       <c r="E769">
-        <v>3.753333333333333</v>
+        <v>3.16</v>
       </c>
       <c r="F769">
-        <v>18.78</v>
+        <v>-0.63</v>
       </c>
       <c r="G769" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="770">
@@ -24097,12 +24097,12 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -24111,13 +24111,13 @@
         </is>
       </c>
       <c r="E770">
-        <v>3.4875</v>
+        <v>3.73</v>
       </c>
       <c r="F770">
-        <v>-6.5</v>
+        <v>-4.97</v>
       </c>
       <c r="G770" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="771">
@@ -24128,12 +24128,12 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -24142,13 +24142,13 @@
         </is>
       </c>
       <c r="E771">
-        <v>5.918333333333333</v>
+        <v>7.11</v>
       </c>
       <c r="F771">
-        <v>-16.76</v>
+        <v>-5.39</v>
       </c>
       <c r="G771" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="772">
@@ -24159,12 +24159,12 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -24173,13 +24173,13 @@
         </is>
       </c>
       <c r="E772">
-        <v>5.4375</v>
+        <v>2.79</v>
       </c>
       <c r="F772">
-        <v>94.89</v>
+        <v>-7.15</v>
       </c>
       <c r="G772" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="773">
@@ -24190,12 +24190,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -24204,13 +24204,13 @@
         </is>
       </c>
       <c r="E773">
-        <v>23.59166666666667</v>
+        <v>29.79</v>
       </c>
       <c r="F773">
-        <v>-20.81</v>
+        <v>-0.91</v>
       </c>
       <c r="G773" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="774">
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -24235,13 +24235,13 @@
         </is>
       </c>
       <c r="E774">
-        <v>54.75333333333333</v>
+        <v>47.23</v>
       </c>
       <c r="F774">
-        <v>15.93</v>
+        <v>-0.66</v>
       </c>
       <c r="G774" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="775">
@@ -24252,12 +24252,12 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -24266,13 +24266,13 @@
         </is>
       </c>
       <c r="E775">
-        <v>3.5875</v>
+        <v>3.45</v>
       </c>
       <c r="F775">
-        <v>3.99</v>
+        <v>-5.61</v>
       </c>
       <c r="G775" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="776">
@@ -24283,12 +24283,12 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -24297,13 +24297,13 @@
         </is>
       </c>
       <c r="E776">
-        <v>6.6125</v>
+        <v>4.56</v>
       </c>
       <c r="F776">
-        <v>45.01</v>
+        <v>-7.03</v>
       </c>
       <c r="G776" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="777">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -24328,13 +24328,13 @@
         </is>
       </c>
       <c r="E777">
-        <v>5.126666666666667</v>
+        <v>3.92</v>
       </c>
       <c r="F777">
-        <v>30.78</v>
+        <v>-11.91</v>
       </c>
       <c r="G777" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="778">
@@ -24345,12 +24345,12 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -24359,13 +24359,13 @@
         </is>
       </c>
       <c r="E778">
-        <v>29.4425</v>
+        <v>25.37</v>
       </c>
       <c r="F778">
-        <v>16.05</v>
+        <v>-7.53</v>
       </c>
       <c r="G778" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="779">
@@ -24376,12 +24376,12 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -24390,13 +24390,13 @@
         </is>
       </c>
       <c r="E779">
-        <v>15.70666666666667</v>
+        <v>17.9</v>
       </c>
       <c r="F779">
-        <v>-12.25</v>
+        <v>2.73</v>
       </c>
       <c r="G779" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="780">
@@ -24407,12 +24407,12 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -24421,13 +24421,13 @@
         </is>
       </c>
       <c r="E780">
-        <v>7.433333333333334</v>
+        <v>6.79</v>
       </c>
       <c r="F780">
-        <v>9.470000000000001</v>
+        <v>-18.97</v>
       </c>
       <c r="G780" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="781">
@@ -24438,12 +24438,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Novembro</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -24452,13 +24452,13 @@
         </is>
       </c>
       <c r="E781">
-        <v>7.036666666666667</v>
+        <v>7.96</v>
       </c>
       <c r="F781">
-        <v>-11.6</v>
+        <v>2.38</v>
       </c>
       <c r="G781" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="782">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -24483,13 +24483,13 @@
         </is>
       </c>
       <c r="E782">
-        <v>3.4975</v>
+        <v>3.753333333333333</v>
       </c>
       <c r="F782">
-        <v>-6.82</v>
+        <v>18.78</v>
       </c>
       <c r="G782" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="783">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -24514,13 +24514,13 @@
         </is>
       </c>
       <c r="E783">
-        <v>3.425</v>
+        <v>3.4875</v>
       </c>
       <c r="F783">
-        <v>-1.79</v>
+        <v>-6.5</v>
       </c>
       <c r="G783" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="784">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -24545,13 +24545,13 @@
         </is>
       </c>
       <c r="E784">
-        <v>5.362500000000001</v>
+        <v>5.918333333333333</v>
       </c>
       <c r="F784">
-        <v>-9.390000000000001</v>
+        <v>-16.76</v>
       </c>
       <c r="G784" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="785">
@@ -24567,7 +24567,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -24576,13 +24576,13 @@
         </is>
       </c>
       <c r="E785">
-        <v>5.9625</v>
+        <v>5.4375</v>
       </c>
       <c r="F785">
-        <v>9.66</v>
+        <v>94.89</v>
       </c>
       <c r="G785" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="786">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -24607,13 +24607,13 @@
         </is>
       </c>
       <c r="E786">
-        <v>22.15666666666667</v>
+        <v>23.59166666666667</v>
       </c>
       <c r="F786">
-        <v>-6.08</v>
+        <v>-20.81</v>
       </c>
       <c r="G786" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="787">
@@ -24629,7 +24629,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="E787">
-        <v>49.65833333333333</v>
+        <v>54.75333333333333</v>
       </c>
       <c r="F787">
-        <v>-9.31</v>
+        <v>15.93</v>
       </c>
       <c r="G787" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="788">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -24669,13 +24669,13 @@
         </is>
       </c>
       <c r="E788">
-        <v>3.69</v>
+        <v>3.5875</v>
       </c>
       <c r="F788">
-        <v>2.86</v>
+        <v>3.99</v>
       </c>
       <c r="G788" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="789">
@@ -24691,7 +24691,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -24700,13 +24700,13 @@
         </is>
       </c>
       <c r="E789">
-        <v>5.9575</v>
+        <v>6.6125</v>
       </c>
       <c r="F789">
-        <v>-9.91</v>
+        <v>45.01</v>
       </c>
       <c r="G789" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="790">
@@ -24722,7 +24722,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -24731,13 +24731,13 @@
         </is>
       </c>
       <c r="E790">
-        <v>5.065</v>
+        <v>5.126666666666667</v>
       </c>
       <c r="F790">
-        <v>-1.2</v>
+        <v>30.78</v>
       </c>
       <c r="G790" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="791">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -24762,13 +24762,13 @@
         </is>
       </c>
       <c r="E791">
-        <v>27.06833333333334</v>
+        <v>29.4425</v>
       </c>
       <c r="F791">
-        <v>-8.06</v>
+        <v>16.05</v>
       </c>
       <c r="G791" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="792">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -24793,13 +24793,13 @@
         </is>
       </c>
       <c r="E792">
-        <v>15.60833333333333</v>
+        <v>15.70666666666667</v>
       </c>
       <c r="F792">
-        <v>-0.63</v>
+        <v>-12.25</v>
       </c>
       <c r="G792" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="793">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -24824,13 +24824,13 @@
         </is>
       </c>
       <c r="E793">
-        <v>11.41833333333333</v>
+        <v>7.433333333333334</v>
       </c>
       <c r="F793">
-        <v>53.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G793" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="794">
@@ -24846,7 +24846,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -24855,19 +24855,19 @@
         </is>
       </c>
       <c r="E794">
-        <v>7.003333333333334</v>
+        <v>7.036666666666667</v>
       </c>
       <c r="F794">
-        <v>-0.47</v>
+        <v>-11.6</v>
       </c>
       <c r="G794" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
@@ -24886,16 +24886,19 @@
         </is>
       </c>
       <c r="E795">
-        <v>3.46</v>
+        <v>3.4975</v>
+      </c>
+      <c r="F795">
+        <v>-6.82</v>
       </c>
       <c r="G795" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -24905,7 +24908,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -24914,16 +24917,19 @@
         </is>
       </c>
       <c r="E796">
-        <v>4.446666666666667</v>
+        <v>3.425</v>
+      </c>
+      <c r="F796">
+        <v>-1.79</v>
       </c>
       <c r="G796" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -24933,7 +24939,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -24942,16 +24948,19 @@
         </is>
       </c>
       <c r="E797">
-        <v>5.82</v>
+        <v>5.362500000000001</v>
+      </c>
+      <c r="F797">
+        <v>-9.390000000000001</v>
       </c>
       <c r="G797" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -24961,7 +24970,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -24970,16 +24979,19 @@
         </is>
       </c>
       <c r="E798">
-        <v>4.49</v>
+        <v>5.9625</v>
+      </c>
+      <c r="F798">
+        <v>9.66</v>
       </c>
       <c r="G798" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -24989,7 +25001,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -24998,16 +25010,19 @@
         </is>
       </c>
       <c r="E799">
-        <v>32.35</v>
+        <v>22.15666666666667</v>
+      </c>
+      <c r="F799">
+        <v>-6.08</v>
       </c>
       <c r="G799" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -25017,7 +25032,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -25026,16 +25041,19 @@
         </is>
       </c>
       <c r="E800">
-        <v>48.44333333333334</v>
+        <v>49.65833333333333</v>
+      </c>
+      <c r="F800">
+        <v>-9.31</v>
       </c>
       <c r="G800" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -25045,7 +25063,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -25054,16 +25072,19 @@
         </is>
       </c>
       <c r="E801">
-        <v>3.813333333333333</v>
+        <v>3.69</v>
+      </c>
+      <c r="F801">
+        <v>2.86</v>
       </c>
       <c r="G801" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -25073,7 +25094,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -25082,16 +25103,19 @@
         </is>
       </c>
       <c r="E802">
-        <v>5.46</v>
+        <v>5.9575</v>
+      </c>
+      <c r="F802">
+        <v>-9.91</v>
       </c>
       <c r="G802" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -25101,7 +25125,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -25110,16 +25134,19 @@
         </is>
       </c>
       <c r="E803">
-        <v>4.48</v>
+        <v>5.065</v>
+      </c>
+      <c r="F803">
+        <v>-1.2</v>
       </c>
       <c r="G803" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -25129,7 +25156,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -25138,16 +25165,19 @@
         </is>
       </c>
       <c r="E804">
-        <v>28.26666666666667</v>
+        <v>27.06833333333334</v>
+      </c>
+      <c r="F804">
+        <v>-8.06</v>
       </c>
       <c r="G804" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -25157,7 +25187,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -25166,16 +25196,19 @@
         </is>
       </c>
       <c r="E805">
-        <v>16.94666666666667</v>
+        <v>15.60833333333333</v>
+      </c>
+      <c r="F805">
+        <v>-0.63</v>
       </c>
       <c r="G805" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -25185,7 +25218,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -25194,16 +25227,19 @@
         </is>
       </c>
       <c r="E806">
-        <v>8.99</v>
+        <v>11.41833333333333</v>
+      </c>
+      <c r="F806">
+        <v>53.61</v>
       </c>
       <c r="G806" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Bombinhas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -25213,7 +25249,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Março</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -25222,10 +25258,13 @@
         </is>
       </c>
       <c r="E807">
-        <v>7.763333333333333</v>
+        <v>7.003333333333334</v>
+      </c>
+      <c r="F807">
+        <v>-0.47</v>
       </c>
       <c r="G807" s="2">
-        <v>46082</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="808">
@@ -25241,7 +25280,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -25250,13 +25289,10 @@
         </is>
       </c>
       <c r="E808">
-        <v>3.69</v>
-      </c>
-      <c r="F808">
-        <v>6.65</v>
+        <v>3.46</v>
       </c>
       <c r="G808" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="809">
@@ -25272,7 +25308,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -25281,13 +25317,10 @@
         </is>
       </c>
       <c r="E809">
-        <v>4.15</v>
-      </c>
-      <c r="F809">
-        <v>-6.67</v>
+        <v>4.446666666666667</v>
       </c>
       <c r="G809" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="810">
@@ -25303,7 +25336,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -25312,13 +25345,10 @@
         </is>
       </c>
       <c r="E810">
-        <v>5.29</v>
-      </c>
-      <c r="F810">
-        <v>-9.109999999999999</v>
+        <v>5.82</v>
       </c>
       <c r="G810" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="811">
@@ -25334,7 +25364,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -25343,13 +25373,10 @@
         </is>
       </c>
       <c r="E811">
-        <v>7.456666666666667</v>
-      </c>
-      <c r="F811">
-        <v>66.06999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="G811" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="812">
@@ -25365,7 +25392,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -25374,13 +25401,10 @@
         </is>
       </c>
       <c r="E812">
-        <v>31.37333333333333</v>
-      </c>
-      <c r="F812">
-        <v>-3.02</v>
+        <v>32.35</v>
       </c>
       <c r="G812" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="813">
@@ -25396,7 +25420,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -25405,13 +25429,10 @@
         </is>
       </c>
       <c r="E813">
-        <v>48.68</v>
-      </c>
-      <c r="F813">
-        <v>0.49</v>
+        <v>48.44333333333334</v>
       </c>
       <c r="G813" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="814">
@@ -25427,7 +25448,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -25436,13 +25457,10 @@
         </is>
       </c>
       <c r="E814">
-        <v>3.76</v>
-      </c>
-      <c r="F814">
-        <v>-1.4</v>
+        <v>3.813333333333333</v>
       </c>
       <c r="G814" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="815">
@@ -25458,7 +25476,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -25467,13 +25485,10 @@
         </is>
       </c>
       <c r="E815">
-        <v>5.89</v>
-      </c>
-      <c r="F815">
-        <v>7.88</v>
+        <v>5.46</v>
       </c>
       <c r="G815" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="816">
@@ -25489,7 +25504,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -25498,13 +25513,10 @@
         </is>
       </c>
       <c r="E816">
-        <v>5.756666666666667</v>
-      </c>
-      <c r="F816">
-        <v>28.5</v>
+        <v>4.48</v>
       </c>
       <c r="G816" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="817">
@@ -25520,7 +25532,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -25529,13 +25541,10 @@
         </is>
       </c>
       <c r="E817">
-        <v>28.72</v>
-      </c>
-      <c r="F817">
-        <v>1.6</v>
+        <v>28.26666666666667</v>
       </c>
       <c r="G817" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="818">
@@ -25551,7 +25560,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -25560,13 +25569,10 @@
         </is>
       </c>
       <c r="E818">
-        <v>17.21333333333333</v>
-      </c>
-      <c r="F818">
-        <v>1.57</v>
+        <v>16.94666666666667</v>
       </c>
       <c r="G818" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="819">
@@ -25582,7 +25588,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -25593,11 +25599,8 @@
       <c r="E819">
         <v>8.99</v>
       </c>
-      <c r="F819">
-        <v>0</v>
-      </c>
       <c r="G819" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="820">
@@ -25613,7 +25616,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -25622,13 +25625,10 @@
         </is>
       </c>
       <c r="E820">
-        <v>7.706666666666666</v>
-      </c>
-      <c r="F820">
-        <v>-0.73</v>
+        <v>7.763333333333333</v>
       </c>
       <c r="G820" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="821">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -25653,13 +25653,13 @@
         </is>
       </c>
       <c r="E821">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="F821">
-        <v>-2.44</v>
+        <v>6.65</v>
       </c>
       <c r="G821" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="822">
@@ -25675,7 +25675,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -25684,13 +25684,13 @@
         </is>
       </c>
       <c r="E822">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="F822">
-        <v>0.48</v>
+        <v>-6.67</v>
       </c>
       <c r="G822" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="823">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -25715,13 +25715,13 @@
         </is>
       </c>
       <c r="E823">
-        <v>4.99</v>
+        <v>5.29</v>
       </c>
       <c r="F823">
-        <v>-5.67</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="G823" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="824">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -25746,13 +25746,13 @@
         </is>
       </c>
       <c r="E824">
-        <v>8.99</v>
+        <v>7.456666666666667</v>
       </c>
       <c r="F824">
-        <v>20.56</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G824" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="825">
@@ -25768,7 +25768,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -25777,13 +25777,13 @@
         </is>
       </c>
       <c r="E825">
-        <v>28.76666666666667</v>
+        <v>31.37333333333333</v>
       </c>
       <c r="F825">
-        <v>-8.31</v>
+        <v>-3.02</v>
       </c>
       <c r="G825" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="826">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -25808,13 +25808,13 @@
         </is>
       </c>
       <c r="E826">
-        <v>50.02666666666666</v>
+        <v>48.68</v>
       </c>
       <c r="F826">
-        <v>2.77</v>
+        <v>0.49</v>
       </c>
       <c r="G826" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="827">
@@ -25830,7 +25830,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -25839,13 +25839,13 @@
         </is>
       </c>
       <c r="E827">
-        <v>3.506666666666666</v>
+        <v>3.76</v>
       </c>
       <c r="F827">
-        <v>-6.74</v>
+        <v>-1.4</v>
       </c>
       <c r="G827" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="828">
@@ -25861,7 +25861,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -25870,13 +25870,13 @@
         </is>
       </c>
       <c r="E828">
-        <v>5.896666666666667</v>
+        <v>5.89</v>
       </c>
       <c r="F828">
-        <v>0.11</v>
+        <v>7.88</v>
       </c>
       <c r="G828" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="829">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -25901,13 +25901,13 @@
         </is>
       </c>
       <c r="E829">
-        <v>5.656666666666667</v>
+        <v>5.756666666666667</v>
       </c>
       <c r="F829">
-        <v>-1.74</v>
+        <v>28.5</v>
       </c>
       <c r="G829" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="830">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -25932,13 +25932,13 @@
         </is>
       </c>
       <c r="E830">
-        <v>28.66666666666667</v>
+        <v>28.72</v>
       </c>
       <c r="F830">
-        <v>-0.19</v>
+        <v>1.6</v>
       </c>
       <c r="G830" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="831">
@@ -25954,7 +25954,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -25963,13 +25963,13 @@
         </is>
       </c>
       <c r="E831">
-        <v>17.56333333333333</v>
+        <v>17.21333333333333</v>
       </c>
       <c r="F831">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="G831" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="832">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -25994,13 +25994,13 @@
         </is>
       </c>
       <c r="E832">
-        <v>13.59333333333333</v>
+        <v>8.99</v>
       </c>
       <c r="F832">
-        <v>51.21</v>
+        <v>0</v>
       </c>
       <c r="G832" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="833">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -26025,19 +26025,19 @@
         </is>
       </c>
       <c r="E833">
-        <v>7.443333333333333</v>
+        <v>7.706666666666666</v>
       </c>
       <c r="F833">
-        <v>-3.42</v>
+        <v>-0.73</v>
       </c>
       <c r="G833" s="2">
-        <v>46143</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -26056,16 +26056,19 @@
         </is>
       </c>
       <c r="E834">
-        <v>3.716666666666666</v>
+        <v>3.6</v>
+      </c>
+      <c r="F834">
+        <v>-2.44</v>
       </c>
       <c r="G834" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -26075,7 +26078,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -26084,16 +26087,19 @@
         </is>
       </c>
       <c r="E835">
-        <v>3.753333333333333</v>
+        <v>4.17</v>
+      </c>
+      <c r="F835">
+        <v>0.48</v>
       </c>
       <c r="G835" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -26103,7 +26109,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -26112,16 +26118,19 @@
         </is>
       </c>
       <c r="E836">
-        <v>6.183333333333334</v>
+        <v>4.99</v>
+      </c>
+      <c r="F836">
+        <v>-5.67</v>
       </c>
       <c r="G836" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -26131,7 +26140,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -26140,16 +26149,19 @@
         </is>
       </c>
       <c r="E837">
-        <v>4.26</v>
+        <v>8.99</v>
+      </c>
+      <c r="F837">
+        <v>20.56</v>
       </c>
       <c r="G837" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -26159,7 +26171,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -26168,16 +26180,19 @@
         </is>
       </c>
       <c r="E838">
-        <v>28.61</v>
+        <v>28.76666666666667</v>
+      </c>
+      <c r="F838">
+        <v>-8.31</v>
       </c>
       <c r="G838" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -26187,7 +26202,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -26196,16 +26211,19 @@
         </is>
       </c>
       <c r="E839">
-        <v>52.79333333333334</v>
+        <v>50.02666666666666</v>
+      </c>
+      <c r="F839">
+        <v>2.77</v>
       </c>
       <c r="G839" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -26215,7 +26233,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -26224,16 +26242,19 @@
         </is>
       </c>
       <c r="E840">
-        <v>3.406666666666667</v>
+        <v>3.506666666666666</v>
+      </c>
+      <c r="F840">
+        <v>-6.74</v>
       </c>
       <c r="G840" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -26243,7 +26264,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -26252,16 +26273,19 @@
         </is>
       </c>
       <c r="E841">
-        <v>5.123333333333333</v>
+        <v>5.896666666666667</v>
+      </c>
+      <c r="F841">
+        <v>0.11</v>
       </c>
       <c r="G841" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -26271,7 +26295,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -26280,16 +26304,19 @@
         </is>
       </c>
       <c r="E842">
-        <v>3.8</v>
+        <v>5.656666666666667</v>
+      </c>
+      <c r="F842">
+        <v>-1.74</v>
       </c>
       <c r="G842" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -26299,7 +26326,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -26308,16 +26335,19 @@
         </is>
       </c>
       <c r="E843">
-        <v>26.67333333333333</v>
+        <v>28.66666666666667</v>
+      </c>
+      <c r="F843">
+        <v>-0.19</v>
       </c>
       <c r="G843" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -26327,7 +26357,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -26336,16 +26366,19 @@
         </is>
       </c>
       <c r="E844">
-        <v>13.35333333333333</v>
+        <v>17.56333333333333</v>
+      </c>
+      <c r="F844">
+        <v>2.03</v>
       </c>
       <c r="G844" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -26355,7 +26388,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -26364,16 +26397,19 @@
         </is>
       </c>
       <c r="E845">
-        <v>12.98</v>
+        <v>13.59333333333333</v>
+      </c>
+      <c r="F845">
+        <v>51.21</v>
       </c>
       <c r="G845" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>Indaial</t>
+          <t>Bombinhas</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -26383,7 +26419,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Maio</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -26392,10 +26428,13 @@
         </is>
       </c>
       <c r="E846">
-        <v>9.199999999999999</v>
+        <v>7.443333333333333</v>
+      </c>
+      <c r="F846">
+        <v>-3.42</v>
       </c>
       <c r="G846" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="847">
@@ -26411,7 +26450,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -26420,13 +26459,10 @@
         </is>
       </c>
       <c r="E847">
-        <v>3.623333333333334</v>
-      </c>
-      <c r="F847">
-        <v>-2.51</v>
+        <v>3.716666666666666</v>
       </c>
       <c r="G847" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="848">
@@ -26442,7 +26478,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -26451,13 +26487,10 @@
         </is>
       </c>
       <c r="E848">
-        <v>3.62</v>
-      </c>
-      <c r="F848">
-        <v>-3.55</v>
+        <v>3.753333333333333</v>
       </c>
       <c r="G848" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="849">
@@ -26473,7 +26506,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -26482,13 +26515,10 @@
         </is>
       </c>
       <c r="E849">
-        <v>5.156666666666667</v>
-      </c>
-      <c r="F849">
-        <v>-16.6</v>
+        <v>6.183333333333334</v>
       </c>
       <c r="G849" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="850">
@@ -26504,7 +26534,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -26513,13 +26543,10 @@
         </is>
       </c>
       <c r="E850">
-        <v>4.856666666666666</v>
-      </c>
-      <c r="F850">
-        <v>14.01</v>
+        <v>4.26</v>
       </c>
       <c r="G850" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="851">
@@ -26535,7 +26562,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -26544,13 +26571,10 @@
         </is>
       </c>
       <c r="E851">
-        <v>25.15666666666667</v>
-      </c>
-      <c r="F851">
-        <v>-12.07</v>
+        <v>28.61</v>
       </c>
       <c r="G851" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="852">
@@ -26566,7 +26590,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -26575,13 +26599,10 @@
         </is>
       </c>
       <c r="E852">
-        <v>51.25333333333333</v>
-      </c>
-      <c r="F852">
-        <v>-2.92</v>
+        <v>52.79333333333334</v>
       </c>
       <c r="G852" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="853">
@@ -26597,7 +26618,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -26606,13 +26627,10 @@
         </is>
       </c>
       <c r="E853">
-        <v>3.613333333333333</v>
-      </c>
-      <c r="F853">
-        <v>6.07</v>
+        <v>3.406666666666667</v>
       </c>
       <c r="G853" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="854">
@@ -26628,7 +26646,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -26637,13 +26655,10 @@
         </is>
       </c>
       <c r="E854">
-        <v>5.09</v>
-      </c>
-      <c r="F854">
-        <v>-0.65</v>
+        <v>5.123333333333333</v>
       </c>
       <c r="G854" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="855">
@@ -26659,7 +26674,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -26668,13 +26683,10 @@
         </is>
       </c>
       <c r="E855">
-        <v>4.526666666666666</v>
-      </c>
-      <c r="F855">
-        <v>19.12</v>
+        <v>3.8</v>
       </c>
       <c r="G855" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="856">
@@ -26690,7 +26702,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -26699,13 +26711,10 @@
         </is>
       </c>
       <c r="E856">
-        <v>24.49</v>
-      </c>
-      <c r="F856">
-        <v>-8.19</v>
+        <v>26.67333333333333</v>
       </c>
       <c r="G856" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="857">
@@ -26721,7 +26730,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -26730,13 +26739,10 @@
         </is>
       </c>
       <c r="E857">
-        <v>13.23</v>
-      </c>
-      <c r="F857">
-        <v>-0.92</v>
+        <v>13.35333333333333</v>
       </c>
       <c r="G857" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="858">
@@ -26752,7 +26758,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -26761,13 +26767,10 @@
         </is>
       </c>
       <c r="E858">
-        <v>6.99</v>
-      </c>
-      <c r="F858">
-        <v>-46.15</v>
+        <v>12.98</v>
       </c>
       <c r="G858" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="859">
@@ -26783,7 +26786,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -26792,13 +26795,10 @@
         </is>
       </c>
       <c r="E859">
-        <v>7.363333333333333</v>
-      </c>
-      <c r="F859">
-        <v>-19.96</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G859" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="860">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -26823,13 +26823,13 @@
         </is>
       </c>
       <c r="E860">
-        <v>3.26</v>
+        <v>3.623333333333334</v>
       </c>
       <c r="F860">
-        <v>-10.03</v>
+        <v>-2.51</v>
       </c>
       <c r="G860" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="861">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -26854,13 +26854,13 @@
         </is>
       </c>
       <c r="E861">
-        <v>3.49</v>
+        <v>3.62</v>
       </c>
       <c r="F861">
-        <v>-3.59</v>
+        <v>-3.55</v>
       </c>
       <c r="G861" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="862">
@@ -26876,7 +26876,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -26885,13 +26885,13 @@
         </is>
       </c>
       <c r="E862">
-        <v>4.99</v>
+        <v>5.156666666666667</v>
       </c>
       <c r="F862">
-        <v>-3.23</v>
+        <v>-16.6</v>
       </c>
       <c r="G862" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="863">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -26916,13 +26916,13 @@
         </is>
       </c>
       <c r="E863">
-        <v>7.99</v>
+        <v>4.856666666666666</v>
       </c>
       <c r="F863">
-        <v>64.52</v>
+        <v>14.01</v>
       </c>
       <c r="G863" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="864">
@@ -26938,7 +26938,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -26947,13 +26947,13 @@
         </is>
       </c>
       <c r="E864">
-        <v>21.99</v>
+        <v>25.15666666666667</v>
       </c>
       <c r="F864">
-        <v>-12.59</v>
+        <v>-12.07</v>
       </c>
       <c r="G864" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="865">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -26978,13 +26978,13 @@
         </is>
       </c>
       <c r="E865">
-        <v>46.23</v>
+        <v>51.25333333333333</v>
       </c>
       <c r="F865">
-        <v>-9.800000000000001</v>
+        <v>-2.92</v>
       </c>
       <c r="G865" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="866">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -27009,13 +27009,13 @@
         </is>
       </c>
       <c r="E866">
-        <v>3.99</v>
+        <v>3.613333333333333</v>
       </c>
       <c r="F866">
-        <v>10.42</v>
+        <v>6.07</v>
       </c>
       <c r="G866" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="867">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -27040,13 +27040,13 @@
         </is>
       </c>
       <c r="E867">
-        <v>4.56</v>
+        <v>5.09</v>
       </c>
       <c r="F867">
-        <v>-10.41</v>
+        <v>-0.65</v>
       </c>
       <c r="G867" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="868">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -27071,13 +27071,13 @@
         </is>
       </c>
       <c r="E868">
-        <v>4.66</v>
+        <v>4.526666666666666</v>
       </c>
       <c r="F868">
-        <v>2.95</v>
+        <v>19.12</v>
       </c>
       <c r="G868" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="869">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -27102,13 +27102,13 @@
         </is>
       </c>
       <c r="E869">
-        <v>23.94</v>
+        <v>24.49</v>
       </c>
       <c r="F869">
-        <v>-2.25</v>
+        <v>-8.19</v>
       </c>
       <c r="G869" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="870">
@@ -27124,7 +27124,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -27133,13 +27133,13 @@
         </is>
       </c>
       <c r="E870">
-        <v>15.9</v>
+        <v>13.23</v>
       </c>
       <c r="F870">
-        <v>20.18</v>
+        <v>-0.92</v>
       </c>
       <c r="G870" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="871">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -27164,13 +27164,13 @@
         </is>
       </c>
       <c r="E871">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
       <c r="F871">
-        <v>85.84</v>
+        <v>-46.15</v>
       </c>
       <c r="G871" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="872">
@@ -27186,7 +27186,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -27195,13 +27195,13 @@
         </is>
       </c>
       <c r="E872">
-        <v>7.06</v>
+        <v>7.363333333333333</v>
       </c>
       <c r="F872">
-        <v>-4.12</v>
+        <v>-19.96</v>
       </c>
       <c r="G872" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="873">
@@ -27215,16 +27215,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D873" t="inlineStr">
         <is>
           <t>Arroz tipo 1</t>
         </is>
       </c>
       <c r="E873">
-        <v>3.696666666666667</v>
+        <v>3.26</v>
       </c>
       <c r="F873">
-        <v>13.39</v>
+        <v>-10.03</v>
+      </c>
+      <c r="G873" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="874">
@@ -27238,16 +27246,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D874" t="inlineStr">
         <is>
           <t>Açúcar Refinado</t>
         </is>
       </c>
       <c r="E874">
-        <v>3.396666666666667</v>
+        <v>3.49</v>
       </c>
       <c r="F874">
-        <v>-2.67</v>
+        <v>-3.59</v>
+      </c>
+      <c r="G874" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="875">
@@ -27261,16 +27277,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D875" t="inlineStr">
         <is>
           <t>Banana</t>
         </is>
       </c>
       <c r="E875">
-        <v>5.653333333333333</v>
+        <v>4.99</v>
       </c>
       <c r="F875">
-        <v>13.29</v>
+        <v>-3.23</v>
+      </c>
+      <c r="G875" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="876">
@@ -27284,16 +27308,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D876" t="inlineStr">
         <is>
           <t>Batata</t>
         </is>
       </c>
       <c r="E876">
-        <v>6.653333333333333</v>
+        <v>7.99</v>
       </c>
       <c r="F876">
-        <v>-16.73</v>
+        <v>64.52</v>
+      </c>
+      <c r="G876" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="877">
@@ -27307,16 +27339,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D877" t="inlineStr">
         <is>
           <t>Café em pó</t>
         </is>
       </c>
       <c r="E877">
-        <v>23.74</v>
+        <v>21.99</v>
       </c>
       <c r="F877">
-        <v>7.96</v>
+        <v>-12.59</v>
+      </c>
+      <c r="G877" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="878">
@@ -27330,16 +27370,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D878" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
       <c r="E878">
-        <v>49.56</v>
+        <v>46.23</v>
       </c>
       <c r="F878">
-        <v>7.2</v>
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="G878" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="879">
@@ -27353,16 +27401,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D879" t="inlineStr">
         <is>
           <t>Farinha de Trigo</t>
         </is>
       </c>
       <c r="E879">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
       <c r="F879">
-        <v>-5.26</v>
+        <v>10.42</v>
+      </c>
+      <c r="G879" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="880">
@@ -27376,16 +27432,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D880" t="inlineStr">
         <is>
           <t>Feijão Preto</t>
         </is>
       </c>
       <c r="E880">
-        <v>5.92</v>
+        <v>4.56</v>
       </c>
       <c r="F880">
-        <v>29.82</v>
+        <v>-10.41</v>
+      </c>
+      <c r="G880" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="881">
@@ -27399,16 +27463,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D881" t="inlineStr">
         <is>
           <t>Leite</t>
         </is>
       </c>
       <c r="E881">
-        <v>5.056666666666667</v>
+        <v>4.66</v>
       </c>
       <c r="F881">
-        <v>8.51</v>
+        <v>2.95</v>
+      </c>
+      <c r="G881" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="882">
@@ -27422,16 +27494,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D882" t="inlineStr">
         <is>
           <t>Manteiga</t>
         </is>
       </c>
       <c r="E882">
-        <v>25.02666666666667</v>
+        <v>23.94</v>
       </c>
       <c r="F882">
-        <v>4.54</v>
+        <v>-2.25</v>
+      </c>
+      <c r="G882" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="883">
@@ -27445,16 +27525,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D883" t="inlineStr">
         <is>
           <t>Pão Francês</t>
         </is>
       </c>
       <c r="E883">
-        <v>14.92666666666667</v>
+        <v>15.9</v>
       </c>
       <c r="F883">
-        <v>-6.12</v>
+        <v>20.18</v>
+      </c>
+      <c r="G883" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="884">
@@ -27468,16 +27556,24 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D884" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
       <c r="E884">
-        <v>9.286666666666667</v>
+        <v>12.99</v>
       </c>
       <c r="F884">
-        <v>-28.51</v>
+        <v>85.84</v>
+      </c>
+      <c r="G884" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="885">
@@ -27491,22 +27587,30 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
       <c r="D885" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
       <c r="E885">
-        <v>7.436666666666667</v>
+        <v>7.06</v>
       </c>
       <c r="F885">
-        <v>5.34</v>
+        <v>-4.12</v>
+      </c>
+      <c r="G885" s="2">
+        <v>46266</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -27514,27 +27618,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C886" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D886" t="inlineStr">
         <is>
           <t>Arroz tipo 1</t>
         </is>
       </c>
       <c r="E886">
-        <v>3.3</v>
-      </c>
-      <c r="G886" s="2">
-        <v>46082</v>
+        <v>3.696666666666667</v>
+      </c>
+      <c r="F886">
+        <v>13.39</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -27542,27 +27641,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C887" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D887" t="inlineStr">
         <is>
           <t>Açúcar Refinado</t>
         </is>
       </c>
       <c r="E887">
-        <v>4.353333333333333</v>
-      </c>
-      <c r="G887" s="2">
-        <v>46082</v>
+        <v>3.396666666666667</v>
+      </c>
+      <c r="F887">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -27570,27 +27664,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C888" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D888" t="inlineStr">
         <is>
           <t>Banana</t>
         </is>
       </c>
       <c r="E888">
-        <v>5.976666666666667</v>
-      </c>
-      <c r="G888" s="2">
-        <v>46082</v>
+        <v>5.653333333333333</v>
+      </c>
+      <c r="F888">
+        <v>13.29</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -27598,27 +27687,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C889" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D889" t="inlineStr">
         <is>
           <t>Batata</t>
         </is>
       </c>
       <c r="E889">
-        <v>4.78</v>
-      </c>
-      <c r="G889" s="2">
-        <v>46082</v>
+        <v>6.653333333333333</v>
+      </c>
+      <c r="F889">
+        <v>-16.73</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -27626,27 +27710,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C890" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D890" t="inlineStr">
         <is>
           <t>Café em pó</t>
         </is>
       </c>
       <c r="E890">
-        <v>27.43</v>
-      </c>
-      <c r="G890" s="2">
-        <v>46082</v>
+        <v>23.74</v>
+      </c>
+      <c r="F890">
+        <v>7.96</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -27654,27 +27733,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C891" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D891" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
       <c r="E891">
-        <v>44.9</v>
-      </c>
-      <c r="G891" s="2">
-        <v>46082</v>
+        <v>49.56</v>
+      </c>
+      <c r="F891">
+        <v>7.2</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -27682,27 +27756,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C892" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D892" t="inlineStr">
         <is>
           <t>Farinha de Trigo</t>
         </is>
       </c>
       <c r="E892">
-        <v>3.326666666666667</v>
-      </c>
-      <c r="G892" s="2">
-        <v>46082</v>
+        <v>3.78</v>
+      </c>
+      <c r="F892">
+        <v>-5.26</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -27710,27 +27779,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C893" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D893" t="inlineStr">
         <is>
           <t>Feijão Preto</t>
         </is>
       </c>
       <c r="E893">
-        <v>5.3</v>
-      </c>
-      <c r="G893" s="2">
-        <v>46082</v>
+        <v>5.92</v>
+      </c>
+      <c r="F893">
+        <v>29.82</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -27738,27 +27802,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C894" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D894" t="inlineStr">
         <is>
           <t>Leite</t>
         </is>
       </c>
       <c r="E894">
-        <v>3.806666666666667</v>
-      </c>
-      <c r="G894" s="2">
-        <v>46082</v>
+        <v>5.056666666666667</v>
+      </c>
+      <c r="F894">
+        <v>8.51</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -27766,27 +27825,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C895" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D895" t="inlineStr">
         <is>
           <t>Manteiga</t>
         </is>
       </c>
       <c r="E895">
-        <v>27.32333333333333</v>
-      </c>
-      <c r="G895" s="2">
-        <v>46082</v>
+        <v>25.02666666666667</v>
+      </c>
+      <c r="F895">
+        <v>4.54</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -27794,27 +27848,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C896" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D896" t="inlineStr">
         <is>
           <t>Pão Francês</t>
         </is>
       </c>
       <c r="E896">
-        <v>15.56666666666667</v>
-      </c>
-      <c r="G896" s="2">
-        <v>46082</v>
+        <v>14.92666666666667</v>
+      </c>
+      <c r="F896">
+        <v>-6.12</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -27822,27 +27871,22 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C897" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D897" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
       <c r="E897">
-        <v>10.32</v>
-      </c>
-      <c r="G897" s="2">
-        <v>46082</v>
+        <v>9.286666666666667</v>
+      </c>
+      <c r="F897">
+        <v>-28.51</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>Jaraguá do Sul</t>
+          <t>Indaial</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -27850,21 +27894,16 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C898" t="inlineStr">
-        <is>
-          <t>Março</t>
-        </is>
-      </c>
       <c r="D898" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
       <c r="E898">
-        <v>7.836666666666667</v>
-      </c>
-      <c r="G898" s="2">
-        <v>46082</v>
+        <v>7.436666666666667</v>
+      </c>
+      <c r="F898">
+        <v>5.34</v>
       </c>
     </row>
     <row r="899">
@@ -27880,7 +27919,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -27889,13 +27928,10 @@
         </is>
       </c>
       <c r="E899">
-        <v>3.39</v>
-      </c>
-      <c r="F899">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="G899" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="900">
@@ -27911,7 +27947,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -27920,13 +27956,10 @@
         </is>
       </c>
       <c r="E900">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F900">
-        <v>2.07</v>
+        <v>4.353333333333333</v>
       </c>
       <c r="G900" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="901">
@@ -27942,7 +27975,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -27951,13 +27984,10 @@
         </is>
       </c>
       <c r="E901">
-        <v>6.56</v>
-      </c>
-      <c r="F901">
-        <v>9.76</v>
+        <v>5.976666666666667</v>
       </c>
       <c r="G901" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="902">
@@ -27973,7 +28003,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -27982,13 +28012,10 @@
         </is>
       </c>
       <c r="E902">
-        <v>4.98</v>
-      </c>
-      <c r="F902">
-        <v>4.18</v>
+        <v>4.78</v>
       </c>
       <c r="G902" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="903">
@@ -28004,7 +28031,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -28013,13 +28040,10 @@
         </is>
       </c>
       <c r="E903">
-        <v>27.95333333333333</v>
-      </c>
-      <c r="F903">
-        <v>1.91</v>
+        <v>27.43</v>
       </c>
       <c r="G903" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="904">
@@ -28035,7 +28059,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -28044,13 +28068,10 @@
         </is>
       </c>
       <c r="E904">
-        <v>55.32666666666667</v>
-      </c>
-      <c r="F904">
-        <v>23.22</v>
+        <v>44.9</v>
       </c>
       <c r="G904" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="905">
@@ -28066,7 +28087,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -28075,13 +28096,10 @@
         </is>
       </c>
       <c r="E905">
-        <v>3.45</v>
-      </c>
-      <c r="F905">
-        <v>3.71</v>
+        <v>3.326666666666667</v>
       </c>
       <c r="G905" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="906">
@@ -28097,7 +28115,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -28106,13 +28124,10 @@
         </is>
       </c>
       <c r="E906">
-        <v>5.376666666666667</v>
-      </c>
-      <c r="F906">
-        <v>1.45</v>
+        <v>5.3</v>
       </c>
       <c r="G906" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="907">
@@ -28128,7 +28143,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -28137,13 +28152,10 @@
         </is>
       </c>
       <c r="E907">
-        <v>4.22</v>
-      </c>
-      <c r="F907">
-        <v>10.86</v>
+        <v>3.806666666666667</v>
       </c>
       <c r="G907" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="908">
@@ -28159,7 +28171,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -28168,13 +28180,10 @@
         </is>
       </c>
       <c r="E908">
-        <v>28.10333333333333</v>
-      </c>
-      <c r="F908">
-        <v>2.85</v>
+        <v>27.32333333333333</v>
       </c>
       <c r="G908" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="909">
@@ -28190,7 +28199,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -28199,13 +28208,10 @@
         </is>
       </c>
       <c r="E909">
-        <v>15.9</v>
-      </c>
-      <c r="F909">
-        <v>2.14</v>
+        <v>15.56666666666667</v>
       </c>
       <c r="G909" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="910">
@@ -28221,7 +28227,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -28230,13 +28236,10 @@
         </is>
       </c>
       <c r="E910">
-        <v>10.65333333333333</v>
-      </c>
-      <c r="F910">
-        <v>3.23</v>
+        <v>10.32</v>
       </c>
       <c r="G910" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="911">
@@ -28252,7 +28255,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Março</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -28261,13 +28264,10 @@
         </is>
       </c>
       <c r="E911">
-        <v>7.993333333333333</v>
-      </c>
-      <c r="F911">
-        <v>2</v>
+        <v>7.836666666666667</v>
       </c>
       <c r="G911" s="2">
-        <v>46113</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="912">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -28292,13 +28292,13 @@
         </is>
       </c>
       <c r="E912">
-        <v>3.206666666666667</v>
+        <v>3.39</v>
       </c>
       <c r="F912">
-        <v>-5.41</v>
+        <v>2.73</v>
       </c>
       <c r="G912" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="913">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -28323,13 +28323,13 @@
         </is>
       </c>
       <c r="E913">
-        <v>3.663333333333334</v>
+        <v>4.443333333333333</v>
       </c>
       <c r="F913">
-        <v>-17.55</v>
+        <v>2.07</v>
       </c>
       <c r="G913" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="914">
@@ -28345,7 +28345,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -28354,13 +28354,13 @@
         </is>
       </c>
       <c r="E914">
-        <v>5.49</v>
+        <v>6.56</v>
       </c>
       <c r="F914">
-        <v>-16.31</v>
+        <v>9.76</v>
       </c>
       <c r="G914" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="915">
@@ -28376,7 +28376,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -28385,13 +28385,13 @@
         </is>
       </c>
       <c r="E915">
-        <v>4.853333333333333</v>
+        <v>4.98</v>
       </c>
       <c r="F915">
-        <v>-2.54</v>
+        <v>4.18</v>
       </c>
       <c r="G915" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="916">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -28416,13 +28416,13 @@
         </is>
       </c>
       <c r="E916">
-        <v>23.21</v>
+        <v>27.95333333333333</v>
       </c>
       <c r="F916">
-        <v>-16.97</v>
+        <v>1.91</v>
       </c>
       <c r="G916" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="917">
@@ -28438,7 +28438,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -28447,13 +28447,13 @@
         </is>
       </c>
       <c r="E917">
-        <v>49.02666666666666</v>
+        <v>55.32666666666667</v>
       </c>
       <c r="F917">
-        <v>-11.39</v>
+        <v>23.22</v>
       </c>
       <c r="G917" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="918">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -28478,13 +28478,13 @@
         </is>
       </c>
       <c r="E918">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="F918">
-        <v>4.64</v>
+        <v>3.71</v>
       </c>
       <c r="G918" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="919">
@@ -28500,7 +28500,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -28509,13 +28509,13 @@
         </is>
       </c>
       <c r="E919">
-        <v>5.846666666666667</v>
+        <v>5.376666666666667</v>
       </c>
       <c r="F919">
-        <v>8.74</v>
+        <v>1.45</v>
       </c>
       <c r="G919" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="920">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -28540,13 +28540,13 @@
         </is>
       </c>
       <c r="E920">
-        <v>4.916666666666667</v>
+        <v>4.22</v>
       </c>
       <c r="F920">
-        <v>16.51</v>
+        <v>10.86</v>
       </c>
       <c r="G920" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="921">
@@ -28562,7 +28562,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -28571,13 +28571,13 @@
         </is>
       </c>
       <c r="E921">
-        <v>24.68666666666667</v>
+        <v>28.10333333333333</v>
       </c>
       <c r="F921">
-        <v>-12.16</v>
+        <v>2.85</v>
       </c>
       <c r="G921" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="922">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -28602,13 +28602,13 @@
         </is>
       </c>
       <c r="E922">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="F922">
-        <v>-12.58</v>
+        <v>2.14</v>
       </c>
       <c r="G922" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="923">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -28633,13 +28633,13 @@
         </is>
       </c>
       <c r="E923">
-        <v>5.816666666666667</v>
+        <v>10.65333333333333</v>
       </c>
       <c r="F923">
-        <v>-45.4</v>
+        <v>3.23</v>
       </c>
       <c r="G923" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="924">
@@ -28655,7 +28655,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -28664,13 +28664,13 @@
         </is>
       </c>
       <c r="E924">
-        <v>7.043333333333333</v>
+        <v>7.993333333333333</v>
       </c>
       <c r="F924">
-        <v>-11.88</v>
+        <v>2</v>
       </c>
       <c r="G924" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="925">
@@ -28686,7 +28686,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -28695,13 +28695,13 @@
         </is>
       </c>
       <c r="E925">
-        <v>3.406666666666667</v>
+        <v>3.206666666666667</v>
       </c>
       <c r="F925">
-        <v>6.24</v>
+        <v>-5.41</v>
       </c>
       <c r="G925" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="926">
@@ -28717,7 +28717,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -28726,13 +28726,13 @@
         </is>
       </c>
       <c r="E926">
-        <v>3.643333333333333</v>
+        <v>3.663333333333334</v>
       </c>
       <c r="F926">
-        <v>-0.55</v>
+        <v>-17.55</v>
       </c>
       <c r="G926" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="927">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -28760,10 +28760,10 @@
         <v>5.49</v>
       </c>
       <c r="F927">
-        <v>0</v>
+        <v>-16.31</v>
       </c>
       <c r="G927" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="928">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -28788,13 +28788,13 @@
         </is>
       </c>
       <c r="E928">
-        <v>4.98</v>
+        <v>4.853333333333333</v>
       </c>
       <c r="F928">
-        <v>2.61</v>
+        <v>-2.54</v>
       </c>
       <c r="G928" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="929">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
@@ -28819,13 +28819,13 @@
         </is>
       </c>
       <c r="E929">
-        <v>22.64333333333333</v>
+        <v>23.21</v>
       </c>
       <c r="F929">
-        <v>-2.44</v>
+        <v>-16.97</v>
       </c>
       <c r="G929" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="930">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -28850,13 +28850,13 @@
         </is>
       </c>
       <c r="E930">
-        <v>47.77333333333333</v>
+        <v>49.02666666666666</v>
       </c>
       <c r="F930">
-        <v>-2.56</v>
+        <v>-11.39</v>
       </c>
       <c r="G930" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="931">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
@@ -28881,13 +28881,13 @@
         </is>
       </c>
       <c r="E931">
-        <v>3.583333333333333</v>
+        <v>3.61</v>
       </c>
       <c r="F931">
-        <v>-0.74</v>
+        <v>4.64</v>
       </c>
       <c r="G931" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="932">
@@ -28903,7 +28903,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -28912,13 +28912,13 @@
         </is>
       </c>
       <c r="E932">
-        <v>6.086666666666667</v>
+        <v>5.846666666666667</v>
       </c>
       <c r="F932">
-        <v>4.1</v>
+        <v>8.74</v>
       </c>
       <c r="G932" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="933">
@@ -28934,7 +28934,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -28943,13 +28943,13 @@
         </is>
       </c>
       <c r="E933">
-        <v>4.833333333333333</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="F933">
-        <v>-1.69</v>
+        <v>16.51</v>
       </c>
       <c r="G933" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="934">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -28974,13 +28974,13 @@
         </is>
       </c>
       <c r="E934">
-        <v>25.47</v>
+        <v>24.68666666666667</v>
       </c>
       <c r="F934">
-        <v>3.17</v>
+        <v>-12.16</v>
       </c>
       <c r="G934" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="935">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -29005,13 +29005,13 @@
         </is>
       </c>
       <c r="E935">
-        <v>14.23333333333333</v>
+        <v>13.9</v>
       </c>
       <c r="F935">
-        <v>2.4</v>
+        <v>-12.58</v>
       </c>
       <c r="G935" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="936">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -29036,13 +29036,13 @@
         </is>
       </c>
       <c r="E936">
-        <v>11.98</v>
+        <v>5.816666666666667</v>
       </c>
       <c r="F936">
-        <v>105.96</v>
+        <v>-45.4</v>
       </c>
       <c r="G936" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="937">
@@ -29058,7 +29058,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -29067,19 +29067,19 @@
         </is>
       </c>
       <c r="E937">
-        <v>7.123333333333333</v>
+        <v>7.043333333333333</v>
       </c>
       <c r="F937">
-        <v>1.14</v>
+        <v>-11.88</v>
       </c>
       <c r="G937" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -29098,16 +29098,19 @@
         </is>
       </c>
       <c r="E938">
-        <v>3.393333333333334</v>
+        <v>3.406666666666667</v>
+      </c>
+      <c r="F938">
+        <v>6.24</v>
       </c>
       <c r="G938" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -29117,7 +29120,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -29126,16 +29129,19 @@
         </is>
       </c>
       <c r="E939">
-        <v>3.69</v>
+        <v>3.643333333333333</v>
+      </c>
+      <c r="F939">
+        <v>-0.55</v>
       </c>
       <c r="G939" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -29145,7 +29151,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -29154,16 +29160,19 @@
         </is>
       </c>
       <c r="E940">
-        <v>6.066666666666666</v>
+        <v>5.49</v>
+      </c>
+      <c r="F940">
+        <v>0</v>
       </c>
       <c r="G940" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -29173,7 +29182,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -29182,16 +29191,19 @@
         </is>
       </c>
       <c r="E941">
-        <v>3.826666666666667</v>
+        <v>4.98</v>
+      </c>
+      <c r="F941">
+        <v>2.61</v>
       </c>
       <c r="G941" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -29201,7 +29213,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -29210,16 +29222,19 @@
         </is>
       </c>
       <c r="E942">
-        <v>28.97</v>
+        <v>22.64333333333333</v>
+      </c>
+      <c r="F942">
+        <v>-2.44</v>
       </c>
       <c r="G942" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -29229,7 +29244,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -29238,16 +29253,19 @@
         </is>
       </c>
       <c r="E943">
-        <v>43.38</v>
+        <v>47.77333333333333</v>
+      </c>
+      <c r="F943">
+        <v>-2.56</v>
       </c>
       <c r="G943" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -29257,7 +29275,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -29266,16 +29284,19 @@
         </is>
       </c>
       <c r="E944">
-        <v>3.7</v>
+        <v>3.583333333333333</v>
+      </c>
+      <c r="F944">
+        <v>-0.74</v>
       </c>
       <c r="G944" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -29285,7 +29306,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -29294,16 +29315,19 @@
         </is>
       </c>
       <c r="E945">
-        <v>4.903333333333333</v>
+        <v>6.086666666666667</v>
+      </c>
+      <c r="F945">
+        <v>4.1</v>
       </c>
       <c r="G945" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -29313,7 +29337,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -29322,16 +29346,19 @@
         </is>
       </c>
       <c r="E946">
-        <v>3.783333333333333</v>
+        <v>4.833333333333333</v>
+      </c>
+      <c r="F946">
+        <v>-1.69</v>
       </c>
       <c r="G946" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -29341,7 +29368,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -29350,16 +29377,19 @@
         </is>
       </c>
       <c r="E947">
-        <v>23.95333333333333</v>
+        <v>25.47</v>
+      </c>
+      <c r="F947">
+        <v>3.17</v>
       </c>
       <c r="G947" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -29369,7 +29399,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -29378,16 +29408,19 @@
         </is>
       </c>
       <c r="E948">
-        <v>14.2</v>
+        <v>14.23333333333333</v>
+      </c>
+      <c r="F948">
+        <v>2.4</v>
       </c>
       <c r="G948" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -29397,7 +29430,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -29406,16 +29439,19 @@
         </is>
       </c>
       <c r="E949">
-        <v>8.130000000000001</v>
+        <v>11.98</v>
+      </c>
+      <c r="F949">
+        <v>105.96</v>
       </c>
       <c r="G949" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Massaranduba</t>
+          <t>Jaraguá do Sul</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
@@ -29425,7 +29461,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -29434,10 +29470,13 @@
         </is>
       </c>
       <c r="E950">
-        <v>6.693333333333333</v>
+        <v>7.123333333333333</v>
+      </c>
+      <c r="F950">
+        <v>1.14</v>
       </c>
       <c r="G950" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="951">
@@ -29453,7 +29492,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -29462,13 +29501,10 @@
         </is>
       </c>
       <c r="E951">
-        <v>3.67</v>
-      </c>
-      <c r="F951">
-        <v>8.15</v>
+        <v>3.393333333333334</v>
       </c>
       <c r="G951" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="952">
@@ -29484,7 +29520,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
@@ -29493,13 +29529,10 @@
         </is>
       </c>
       <c r="E952">
-        <v>3.766666666666667</v>
-      </c>
-      <c r="F952">
-        <v>2.08</v>
+        <v>3.69</v>
       </c>
       <c r="G952" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="953">
@@ -29515,7 +29548,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -29524,13 +29557,10 @@
         </is>
       </c>
       <c r="E953">
-        <v>4.42</v>
-      </c>
-      <c r="F953">
-        <v>-27.14</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="G953" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="954">
@@ -29546,7 +29576,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -29555,13 +29585,10 @@
         </is>
       </c>
       <c r="E954">
-        <v>4.99</v>
-      </c>
-      <c r="F954">
-        <v>30.4</v>
+        <v>3.826666666666667</v>
       </c>
       <c r="G954" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="955">
@@ -29577,7 +29604,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -29586,13 +29613,10 @@
         </is>
       </c>
       <c r="E955">
-        <v>25.06</v>
-      </c>
-      <c r="F955">
-        <v>-13.5</v>
+        <v>28.97</v>
       </c>
       <c r="G955" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="956">
@@ -29608,7 +29632,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -29617,13 +29641,10 @@
         </is>
       </c>
       <c r="E956">
-        <v>50.46</v>
-      </c>
-      <c r="F956">
-        <v>16.32</v>
+        <v>43.38</v>
       </c>
       <c r="G956" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="957">
@@ -29639,7 +29660,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -29648,13 +29669,10 @@
         </is>
       </c>
       <c r="E957">
-        <v>4.413333333333334</v>
-      </c>
-      <c r="F957">
-        <v>19.28</v>
+        <v>3.7</v>
       </c>
       <c r="G957" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="958">
@@ -29670,7 +29688,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -29679,13 +29697,10 @@
         </is>
       </c>
       <c r="E958">
-        <v>6.783333333333333</v>
-      </c>
-      <c r="F958">
-        <v>38.34</v>
+        <v>4.903333333333333</v>
       </c>
       <c r="G958" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="959">
@@ -29701,7 +29716,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -29710,13 +29725,10 @@
         </is>
       </c>
       <c r="E959">
-        <v>5.33</v>
-      </c>
-      <c r="F959">
-        <v>40.88</v>
+        <v>3.783333333333333</v>
       </c>
       <c r="G959" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="960">
@@ -29732,7 +29744,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -29741,13 +29753,10 @@
         </is>
       </c>
       <c r="E960">
-        <v>23.74</v>
-      </c>
-      <c r="F960">
-        <v>-0.89</v>
+        <v>23.95333333333333</v>
       </c>
       <c r="G960" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="961">
@@ -29763,7 +29772,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -29772,13 +29781,10 @@
         </is>
       </c>
       <c r="E961">
-        <v>12.435</v>
-      </c>
-      <c r="F961">
-        <v>-12.43</v>
+        <v>14.2</v>
       </c>
       <c r="G961" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="962">
@@ -29794,7 +29800,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -29803,13 +29809,10 @@
         </is>
       </c>
       <c r="E962">
-        <v>7.976666666666667</v>
-      </c>
-      <c r="F962">
-        <v>-1.89</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G962" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="963">
@@ -29825,7 +29828,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -29834,13 +29837,10 @@
         </is>
       </c>
       <c r="E963">
-        <v>7.606666666666666</v>
-      </c>
-      <c r="F963">
-        <v>13.65</v>
+        <v>6.693333333333333</v>
       </c>
       <c r="G963" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="964">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -29865,13 +29865,13 @@
         </is>
       </c>
       <c r="E964">
-        <v>4.113333333333333</v>
+        <v>3.67</v>
       </c>
       <c r="F964">
-        <v>12.08</v>
+        <v>8.15</v>
       </c>
       <c r="G964" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="965">
@@ -29887,7 +29887,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -29896,13 +29896,13 @@
         </is>
       </c>
       <c r="E965">
-        <v>3.7</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="F965">
-        <v>-1.77</v>
+        <v>2.08</v>
       </c>
       <c r="G965" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="966">
@@ -29918,7 +29918,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -29930,10 +29930,10 @@
         <v>4.42</v>
       </c>
       <c r="F966">
-        <v>0</v>
+        <v>-27.14</v>
       </c>
       <c r="G966" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="967">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -29958,13 +29958,13 @@
         </is>
       </c>
       <c r="E967">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
       <c r="F967">
-        <v>40.08</v>
+        <v>30.4</v>
       </c>
       <c r="G967" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="968">
@@ -29980,7 +29980,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -29989,13 +29989,13 @@
         </is>
       </c>
       <c r="E968">
-        <v>25.49</v>
+        <v>25.06</v>
       </c>
       <c r="F968">
-        <v>1.72</v>
+        <v>-13.5</v>
       </c>
       <c r="G968" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="969">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -30020,13 +30020,13 @@
         </is>
       </c>
       <c r="E969">
-        <v>51</v>
+        <v>50.46</v>
       </c>
       <c r="F969">
-        <v>1.07</v>
+        <v>16.32</v>
       </c>
       <c r="G969" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="970">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -30051,13 +30051,13 @@
         </is>
       </c>
       <c r="E970">
-        <v>4.43</v>
+        <v>4.413333333333334</v>
       </c>
       <c r="F970">
-        <v>0.38</v>
+        <v>19.28</v>
       </c>
       <c r="G970" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="971">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -30082,13 +30082,13 @@
         </is>
       </c>
       <c r="E971">
-        <v>7.24</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="F971">
-        <v>6.73</v>
+        <v>38.34</v>
       </c>
       <c r="G971" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="972">
@@ -30104,7 +30104,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -30113,13 +30113,13 @@
         </is>
       </c>
       <c r="E972">
-        <v>5.68</v>
+        <v>5.33</v>
       </c>
       <c r="F972">
-        <v>6.57</v>
+        <v>40.88</v>
       </c>
       <c r="G972" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="973">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -30144,13 +30144,13 @@
         </is>
       </c>
       <c r="E973">
-        <v>27.63666666666667</v>
+        <v>23.74</v>
       </c>
       <c r="F973">
-        <v>16.41</v>
+        <v>-0.89</v>
       </c>
       <c r="G973" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="974">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
@@ -30178,10 +30178,10 @@
         <v>12.435</v>
       </c>
       <c r="F974">
-        <v>0</v>
+        <v>-12.43</v>
       </c>
       <c r="G974" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="975">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -30206,13 +30206,13 @@
         </is>
       </c>
       <c r="E975">
-        <v>9.776666666666667</v>
+        <v>7.976666666666667</v>
       </c>
       <c r="F975">
-        <v>22.57</v>
+        <v>-1.89</v>
       </c>
       <c r="G975" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="976">
@@ -30228,7 +30228,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -30237,19 +30237,19 @@
         </is>
       </c>
       <c r="E976">
-        <v>7.673333333333333</v>
+        <v>7.606666666666666</v>
       </c>
       <c r="F976">
-        <v>0.88</v>
+        <v>13.65</v>
       </c>
       <c r="G976" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -30268,16 +30268,19 @@
         </is>
       </c>
       <c r="E977">
-        <v>2.705</v>
+        <v>4.113333333333333</v>
+      </c>
+      <c r="F977">
+        <v>12.08</v>
       </c>
       <c r="G977" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -30287,7 +30290,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -30296,16 +30299,19 @@
         </is>
       </c>
       <c r="E978">
-        <v>3.72</v>
+        <v>3.7</v>
+      </c>
+      <c r="F978">
+        <v>-1.77</v>
       </c>
       <c r="G978" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -30315,7 +30321,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -30324,16 +30330,19 @@
         </is>
       </c>
       <c r="E979">
-        <v>5.140000000000001</v>
+        <v>4.42</v>
+      </c>
+      <c r="F979">
+        <v>0</v>
       </c>
       <c r="G979" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -30343,7 +30352,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -30352,16 +30361,19 @@
         </is>
       </c>
       <c r="E980">
-        <v>4.390000000000001</v>
+        <v>6.99</v>
+      </c>
+      <c r="F980">
+        <v>40.08</v>
       </c>
       <c r="G980" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -30371,7 +30383,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -30380,16 +30392,19 @@
         </is>
       </c>
       <c r="E981">
-        <v>48.94</v>
+        <v>25.49</v>
+      </c>
+      <c r="F981">
+        <v>1.72</v>
       </c>
       <c r="G981" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -30399,7 +30414,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -30408,16 +30423,19 @@
         </is>
       </c>
       <c r="E982">
-        <v>55.07</v>
+        <v>51</v>
+      </c>
+      <c r="F982">
+        <v>1.07</v>
       </c>
       <c r="G982" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -30427,7 +30445,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -30436,16 +30454,19 @@
         </is>
       </c>
       <c r="E983">
-        <v>3.12</v>
+        <v>4.43</v>
+      </c>
+      <c r="F983">
+        <v>0.38</v>
       </c>
       <c r="G983" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -30455,7 +30476,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -30464,16 +30485,19 @@
         </is>
       </c>
       <c r="E984">
-        <v>4.84</v>
+        <v>7.24</v>
+      </c>
+      <c r="F984">
+        <v>6.73</v>
       </c>
       <c r="G984" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -30483,7 +30507,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -30492,16 +30516,19 @@
         </is>
       </c>
       <c r="E985">
-        <v>4.234999999999999</v>
+        <v>5.68</v>
+      </c>
+      <c r="F985">
+        <v>6.57</v>
       </c>
       <c r="G985" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -30511,7 +30538,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -30520,16 +30547,19 @@
         </is>
       </c>
       <c r="E986">
-        <v>13.96</v>
+        <v>27.63666666666667</v>
+      </c>
+      <c r="F986">
+        <v>16.41</v>
       </c>
       <c r="G986" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -30539,7 +30569,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -30548,16 +30578,19 @@
         </is>
       </c>
       <c r="E987">
-        <v>14.94</v>
+        <v>12.435</v>
+      </c>
+      <c r="F987">
+        <v>0</v>
       </c>
       <c r="G987" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -30567,7 +30600,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -30576,16 +30609,19 @@
         </is>
       </c>
       <c r="E988">
-        <v>8.24</v>
+        <v>9.776666666666667</v>
+      </c>
+      <c r="F988">
+        <v>22.57</v>
       </c>
       <c r="G988" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>Navegantes</t>
+          <t>Massaranduba</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -30595,7 +30631,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -30604,16 +30640,19 @@
         </is>
       </c>
       <c r="E989">
-        <v>8.460000000000001</v>
+        <v>7.673333333333333</v>
+      </c>
+      <c r="F989">
+        <v>0.88</v>
       </c>
       <c r="G989" s="2">
-        <v>46113</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -30632,7 +30671,7 @@
         </is>
       </c>
       <c r="E990">
-        <v>2.633333333333333</v>
+        <v>2.705</v>
       </c>
       <c r="G990" s="2">
         <v>46113</v>
@@ -30641,7 +30680,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -30660,7 +30699,7 @@
         </is>
       </c>
       <c r="E991">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="G991" s="2">
         <v>46113</v>
@@ -30669,7 +30708,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -30688,7 +30727,7 @@
         </is>
       </c>
       <c r="E992">
-        <v>5.29</v>
+        <v>5.140000000000001</v>
       </c>
       <c r="G992" s="2">
         <v>46113</v>
@@ -30697,7 +30736,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -30716,7 +30755,7 @@
         </is>
       </c>
       <c r="E993">
-        <v>5.09</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="G993" s="2">
         <v>46113</v>
@@ -30725,7 +30764,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -30744,7 +30783,7 @@
         </is>
       </c>
       <c r="E994">
-        <v>52.37</v>
+        <v>48.94</v>
       </c>
       <c r="G994" s="2">
         <v>46113</v>
@@ -30753,7 +30792,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -30772,7 +30811,7 @@
         </is>
       </c>
       <c r="E995">
-        <v>60.96666666666667</v>
+        <v>55.07</v>
       </c>
       <c r="G995" s="2">
         <v>46113</v>
@@ -30781,7 +30820,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -30800,7 +30839,7 @@
         </is>
       </c>
       <c r="E996">
-        <v>3.836666666666666</v>
+        <v>3.12</v>
       </c>
       <c r="G996" s="2">
         <v>46113</v>
@@ -30809,7 +30848,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -30828,7 +30867,7 @@
         </is>
       </c>
       <c r="E997">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="G997" s="2">
         <v>46113</v>
@@ -30837,7 +30876,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -30856,7 +30895,7 @@
         </is>
       </c>
       <c r="E998">
-        <v>4.426666666666667</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="G998" s="2">
         <v>46113</v>
@@ -30865,7 +30904,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -30884,7 +30923,7 @@
         </is>
       </c>
       <c r="E999">
-        <v>16.92333333333333</v>
+        <v>13.96</v>
       </c>
       <c r="G999" s="2">
         <v>46113</v>
@@ -30893,7 +30932,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -30912,7 +30951,7 @@
         </is>
       </c>
       <c r="E1000">
-        <v>17.86</v>
+        <v>14.94</v>
       </c>
       <c r="G1000" s="2">
         <v>46113</v>
@@ -30921,7 +30960,7 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -30940,7 +30979,7 @@
         </is>
       </c>
       <c r="E1001">
-        <v>8.933333333333334</v>
+        <v>8.24</v>
       </c>
       <c r="G1001" s="2">
         <v>46113</v>
@@ -30949,7 +30988,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>Timbó</t>
+          <t>Navegantes</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -30968,7 +31007,7 @@
         </is>
       </c>
       <c r="E1002">
-        <v>8.673333333333334</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G1002" s="2">
         <v>46113</v>
@@ -30987,7 +31026,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
@@ -30996,13 +31035,10 @@
         </is>
       </c>
       <c r="E1003">
-        <v>3.256666666666667</v>
-      </c>
-      <c r="F1003">
-        <v>23.67</v>
+        <v>2.633333333333333</v>
       </c>
       <c r="G1003" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1004">
@@ -31018,7 +31054,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -31027,13 +31063,10 @@
         </is>
       </c>
       <c r="E1004">
-        <v>4.443333333333333</v>
-      </c>
-      <c r="F1004">
-        <v>6.55</v>
+        <v>4.17</v>
       </c>
       <c r="G1004" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1005">
@@ -31049,7 +31082,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -31058,13 +31091,10 @@
         </is>
       </c>
       <c r="E1005">
-        <v>4.99</v>
-      </c>
-      <c r="F1005">
-        <v>-5.67</v>
+        <v>5.29</v>
       </c>
       <c r="G1005" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1006">
@@ -31080,7 +31110,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -31089,13 +31119,10 @@
         </is>
       </c>
       <c r="E1006">
-        <v>6.293333333333334</v>
-      </c>
-      <c r="F1006">
-        <v>23.64</v>
+        <v>5.09</v>
       </c>
       <c r="G1006" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1007">
@@ -31111,7 +31138,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -31120,13 +31147,10 @@
         </is>
       </c>
       <c r="E1007">
-        <v>23.41333333333333</v>
-      </c>
-      <c r="F1007">
-        <v>-55.29</v>
+        <v>52.37</v>
       </c>
       <c r="G1007" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1008">
@@ -31142,7 +31166,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -31151,13 +31175,10 @@
         </is>
       </c>
       <c r="E1008">
-        <v>48.88</v>
-      </c>
-      <c r="F1008">
-        <v>-19.83</v>
+        <v>60.96666666666667</v>
       </c>
       <c r="G1008" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1009">
@@ -31173,7 +31194,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -31182,13 +31203,10 @@
         </is>
       </c>
       <c r="E1009">
-        <v>3.996666666666667</v>
-      </c>
-      <c r="F1009">
-        <v>4.17</v>
+        <v>3.836666666666666</v>
       </c>
       <c r="G1009" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1010">
@@ -31204,7 +31222,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
@@ -31213,13 +31231,10 @@
         </is>
       </c>
       <c r="E1010">
-        <v>6.433333333333334</v>
-      </c>
-      <c r="F1010">
-        <v>31.56</v>
+        <v>4.89</v>
       </c>
       <c r="G1010" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1011">
@@ -31235,7 +31250,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -31244,13 +31259,10 @@
         </is>
       </c>
       <c r="E1011">
-        <v>5.12</v>
-      </c>
-      <c r="F1011">
-        <v>15.66</v>
+        <v>4.426666666666667</v>
       </c>
       <c r="G1011" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1012">
@@ -31266,7 +31278,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -31275,13 +31287,10 @@
         </is>
       </c>
       <c r="E1012">
-        <v>31.21666666666667</v>
-      </c>
-      <c r="F1012">
-        <v>84.45999999999999</v>
+        <v>16.92333333333333</v>
       </c>
       <c r="G1012" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1013">
@@ -31297,7 +31306,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -31306,13 +31315,10 @@
         </is>
       </c>
       <c r="E1013">
-        <v>15.26</v>
-      </c>
-      <c r="F1013">
-        <v>-14.56</v>
+        <v>17.86</v>
       </c>
       <c r="G1013" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1014">
@@ -31328,7 +31334,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -31337,13 +31343,10 @@
         </is>
       </c>
       <c r="E1014">
-        <v>5.76</v>
-      </c>
-      <c r="F1014">
-        <v>-35.52</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="G1014" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1015">
@@ -31359,7 +31362,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -31368,13 +31371,10 @@
         </is>
       </c>
       <c r="E1015">
-        <v>7.956666666666667</v>
-      </c>
-      <c r="F1015">
-        <v>-8.26</v>
+        <v>8.673333333333334</v>
       </c>
       <c r="G1015" s="2">
-        <v>46235</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="1016">
@@ -31390,7 +31390,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -31402,10 +31402,10 @@
         <v>3.256666666666667</v>
       </c>
       <c r="F1016">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="G1016" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1017">
@@ -31421,7 +31421,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -31433,10 +31433,10 @@
         <v>4.443333333333333</v>
       </c>
       <c r="F1017">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="G1017" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1018">
@@ -31452,7 +31452,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -31464,10 +31464,10 @@
         <v>4.99</v>
       </c>
       <c r="F1018">
-        <v>0</v>
+        <v>-5.67</v>
       </c>
       <c r="G1018" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1019">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -31492,13 +31492,13 @@
         </is>
       </c>
       <c r="E1019">
-        <v>5.96</v>
+        <v>6.293333333333334</v>
       </c>
       <c r="F1019">
-        <v>-5.3</v>
+        <v>23.64</v>
       </c>
       <c r="G1019" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1020">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -31523,13 +31523,13 @@
         </is>
       </c>
       <c r="E1020">
-        <v>22.8</v>
+        <v>23.41333333333333</v>
       </c>
       <c r="F1020">
-        <v>-2.62</v>
+        <v>-55.29</v>
       </c>
       <c r="G1020" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1021">
@@ -31545,7 +31545,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -31554,13 +31554,13 @@
         </is>
       </c>
       <c r="E1021">
-        <v>48.27333333333333</v>
+        <v>48.88</v>
       </c>
       <c r="F1021">
-        <v>-1.24</v>
+        <v>-19.83</v>
       </c>
       <c r="G1021" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1022">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -31588,10 +31588,10 @@
         <v>3.996666666666667</v>
       </c>
       <c r="F1022">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="G1022" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1023">
@@ -31607,7 +31607,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -31619,10 +31619,10 @@
         <v>6.433333333333334</v>
       </c>
       <c r="F1023">
-        <v>0</v>
+        <v>31.56</v>
       </c>
       <c r="G1023" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1024">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -31647,13 +31647,13 @@
         </is>
       </c>
       <c r="E1024">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="F1024">
-        <v>-0.98</v>
+        <v>15.66</v>
       </c>
       <c r="G1024" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1025">
@@ -31669,7 +31669,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -31678,13 +31678,13 @@
         </is>
       </c>
       <c r="E1025">
-        <v>30.76333333333333</v>
+        <v>31.21666666666667</v>
       </c>
       <c r="F1025">
-        <v>-1.45</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="G1025" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1026">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
@@ -31712,10 +31712,10 @@
         <v>15.26</v>
       </c>
       <c r="F1026">
-        <v>0</v>
+        <v>-14.56</v>
       </c>
       <c r="G1026" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1027">
@@ -31731,7 +31731,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
@@ -31740,13 +31740,13 @@
         </is>
       </c>
       <c r="E1027">
-        <v>5.49</v>
+        <v>5.76</v>
       </c>
       <c r="F1027">
-        <v>-4.69</v>
+        <v>-35.52</v>
       </c>
       <c r="G1027" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1028">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -31771,19 +31771,19 @@
         </is>
       </c>
       <c r="E1028">
-        <v>7.906666666666667</v>
+        <v>7.956666666666667</v>
       </c>
       <c r="F1028">
-        <v>-0.63</v>
+        <v>-8.26</v>
       </c>
       <c r="G1028" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -31793,7 +31793,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -31802,16 +31802,19 @@
         </is>
       </c>
       <c r="E1029">
-        <v>3.49</v>
+        <v>3.256666666666667</v>
+      </c>
+      <c r="F1029">
+        <v>0</v>
       </c>
       <c r="G1029" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
@@ -31821,7 +31824,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -31830,16 +31833,19 @@
         </is>
       </c>
       <c r="E1030">
-        <v>3.75</v>
+        <v>4.443333333333333</v>
+      </c>
+      <c r="F1030">
+        <v>0</v>
       </c>
       <c r="G1030" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -31849,7 +31855,7 @@
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -31858,16 +31864,19 @@
         </is>
       </c>
       <c r="E1031">
-        <v>6.806666666666667</v>
+        <v>4.99</v>
+      </c>
+      <c r="F1031">
+        <v>0</v>
       </c>
       <c r="G1031" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
@@ -31877,7 +31886,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -31886,16 +31895,19 @@
         </is>
       </c>
       <c r="E1032">
-        <v>6.46</v>
+        <v>5.96</v>
+      </c>
+      <c r="F1032">
+        <v>-5.3</v>
       </c>
       <c r="G1032" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -31905,7 +31917,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -31914,16 +31926,19 @@
         </is>
       </c>
       <c r="E1033">
-        <v>23.12333333333333</v>
+        <v>22.8</v>
+      </c>
+      <c r="F1033">
+        <v>-2.62</v>
       </c>
       <c r="G1033" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
@@ -31933,7 +31948,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -31942,16 +31957,19 @@
         </is>
       </c>
       <c r="E1034">
-        <v>52.01666666666667</v>
+        <v>48.27333333333333</v>
+      </c>
+      <c r="F1034">
+        <v>-1.24</v>
       </c>
       <c r="G1034" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -31961,7 +31979,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -31970,16 +31988,19 @@
         </is>
       </c>
       <c r="E1035">
-        <v>3.386666666666667</v>
+        <v>3.996666666666667</v>
+      </c>
+      <c r="F1035">
+        <v>0</v>
       </c>
       <c r="G1035" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
@@ -31989,7 +32010,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -31998,16 +32019,19 @@
         </is>
       </c>
       <c r="E1036">
-        <v>5.926666666666667</v>
+        <v>6.433333333333334</v>
+      </c>
+      <c r="F1036">
+        <v>0</v>
       </c>
       <c r="G1036" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -32017,7 +32041,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -32026,16 +32050,19 @@
         </is>
       </c>
       <c r="E1037">
-        <v>4.91</v>
+        <v>5.07</v>
+      </c>
+      <c r="F1037">
+        <v>-0.98</v>
       </c>
       <c r="G1037" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
@@ -32045,7 +32072,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -32054,16 +32081,19 @@
         </is>
       </c>
       <c r="E1038">
-        <v>26.97</v>
+        <v>30.76333333333333</v>
+      </c>
+      <c r="F1038">
+        <v>-1.45</v>
       </c>
       <c r="G1038" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -32073,7 +32103,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -32082,16 +32112,19 @@
         </is>
       </c>
       <c r="E1039">
-        <v>15.68666666666667</v>
+        <v>15.26</v>
+      </c>
+      <c r="F1039">
+        <v>0</v>
       </c>
       <c r="G1039" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
@@ -32101,7 +32134,7 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -32110,16 +32143,19 @@
         </is>
       </c>
       <c r="E1040">
-        <v>8.286666666666667</v>
+        <v>5.49</v>
+      </c>
+      <c r="F1040">
+        <v>-4.69</v>
       </c>
       <c r="G1040" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>Balneário Camboriú</t>
+          <t>Timbó</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -32129,7 +32165,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -32138,10 +32174,13 @@
         </is>
       </c>
       <c r="E1041">
-        <v>7.036666666666667</v>
+        <v>7.906666666666667</v>
+      </c>
+      <c r="F1041">
+        <v>-0.63</v>
       </c>
       <c r="G1041" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1042">
@@ -32157,7 +32196,7 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -32166,13 +32205,10 @@
         </is>
       </c>
       <c r="E1042">
-        <v>3.866666666666667</v>
-      </c>
-      <c r="F1042">
-        <v>10.79</v>
+        <v>3.49</v>
       </c>
       <c r="G1042" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1043">
@@ -32188,7 +32224,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -32197,13 +32233,10 @@
         </is>
       </c>
       <c r="E1043">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="F1043">
-        <v>-0.44</v>
+        <v>3.75</v>
       </c>
       <c r="G1043" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1044">
@@ -32219,7 +32252,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -32228,13 +32261,10 @@
         </is>
       </c>
       <c r="E1044">
-        <v>6.6</v>
-      </c>
-      <c r="F1044">
-        <v>-3.04</v>
+        <v>6.806666666666667</v>
       </c>
       <c r="G1044" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1045">
@@ -32250,7 +32280,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -32259,13 +32289,10 @@
         </is>
       </c>
       <c r="E1045">
-        <v>6.75</v>
-      </c>
-      <c r="F1045">
-        <v>4.49</v>
+        <v>6.46</v>
       </c>
       <c r="G1045" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1046">
@@ -32281,7 +32308,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -32290,13 +32317,10 @@
         </is>
       </c>
       <c r="E1046">
-        <v>23.51</v>
-      </c>
-      <c r="F1046">
-        <v>1.67</v>
+        <v>23.12333333333333</v>
       </c>
       <c r="G1046" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1047">
@@ -32312,7 +32336,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
@@ -32321,13 +32345,10 @@
         </is>
       </c>
       <c r="E1047">
-        <v>51.06</v>
-      </c>
-      <c r="F1047">
-        <v>-1.84</v>
+        <v>52.01666666666667</v>
       </c>
       <c r="G1047" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1048">
@@ -32343,7 +32364,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
@@ -32352,13 +32373,10 @@
         </is>
       </c>
       <c r="E1048">
-        <v>3.673333333333333</v>
-      </c>
-      <c r="F1048">
-        <v>8.460000000000001</v>
+        <v>3.386666666666667</v>
       </c>
       <c r="G1048" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1049">
@@ -32374,7 +32392,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -32383,13 +32401,10 @@
         </is>
       </c>
       <c r="E1049">
-        <v>6.32</v>
-      </c>
-      <c r="F1049">
-        <v>6.64</v>
+        <v>5.926666666666667</v>
       </c>
       <c r="G1049" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1050">
@@ -32405,7 +32420,7 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -32414,13 +32429,10 @@
         </is>
       </c>
       <c r="E1050">
-        <v>4.853333333333333</v>
-      </c>
-      <c r="F1050">
-        <v>-1.15</v>
+        <v>4.91</v>
       </c>
       <c r="G1050" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1051">
@@ -32436,7 +32448,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -32445,13 +32457,10 @@
         </is>
       </c>
       <c r="E1051">
-        <v>26.59333333333333</v>
-      </c>
-      <c r="F1051">
-        <v>-1.4</v>
+        <v>26.97</v>
       </c>
       <c r="G1051" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1052">
@@ -32467,7 +32476,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -32476,13 +32485,10 @@
         </is>
       </c>
       <c r="E1052">
-        <v>16.85</v>
-      </c>
-      <c r="F1052">
-        <v>7.42</v>
+        <v>15.68666666666667</v>
       </c>
       <c r="G1052" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1053">
@@ -32498,7 +32504,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -32507,13 +32513,10 @@
         </is>
       </c>
       <c r="E1053">
-        <v>13.12</v>
-      </c>
-      <c r="F1053">
-        <v>58.33</v>
+        <v>8.286666666666667</v>
       </c>
       <c r="G1053" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1054">
@@ -32529,7 +32532,7 @@
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -32538,19 +32541,16 @@
         </is>
       </c>
       <c r="E1054">
-        <v>7.166666666666667</v>
-      </c>
-      <c r="F1054">
-        <v>1.85</v>
+        <v>7.036666666666667</v>
       </c>
       <c r="G1054" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -32560,7 +32560,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -32569,16 +32569,19 @@
         </is>
       </c>
       <c r="E1055">
-        <v>3.096666666666667</v>
+        <v>3.866666666666667</v>
+      </c>
+      <c r="F1055">
+        <v>10.79</v>
       </c>
       <c r="G1055" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
@@ -32588,7 +32591,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -32597,16 +32600,19 @@
         </is>
       </c>
       <c r="E1056">
-        <v>3.763333333333333</v>
+        <v>3.733333333333333</v>
+      </c>
+      <c r="F1056">
+        <v>-0.44</v>
       </c>
       <c r="G1056" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -32616,7 +32622,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -32625,16 +32631,19 @@
         </is>
       </c>
       <c r="E1057">
-        <v>5.626666666666667</v>
+        <v>6.6</v>
+      </c>
+      <c r="F1057">
+        <v>-3.04</v>
       </c>
       <c r="G1057" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
@@ -32644,7 +32653,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -32653,16 +32662,19 @@
         </is>
       </c>
       <c r="E1058">
-        <v>5.49</v>
+        <v>6.75</v>
+      </c>
+      <c r="F1058">
+        <v>4.49</v>
       </c>
       <c r="G1058" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -32672,7 +32684,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -32681,16 +32693,19 @@
         </is>
       </c>
       <c r="E1059">
-        <v>23.57333333333333</v>
+        <v>23.51</v>
+      </c>
+      <c r="F1059">
+        <v>1.67</v>
       </c>
       <c r="G1059" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
@@ -32700,7 +32715,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -32709,16 +32724,19 @@
         </is>
       </c>
       <c r="E1060">
-        <v>53.28666666666666</v>
+        <v>51.06</v>
+      </c>
+      <c r="F1060">
+        <v>-1.84</v>
       </c>
       <c r="G1060" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -32728,7 +32746,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -32737,16 +32755,19 @@
         </is>
       </c>
       <c r="E1061">
-        <v>4.1</v>
+        <v>3.673333333333333</v>
+      </c>
+      <c r="F1061">
+        <v>8.460000000000001</v>
       </c>
       <c r="G1061" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
@@ -32756,7 +32777,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -32765,16 +32786,19 @@
         </is>
       </c>
       <c r="E1062">
-        <v>6.54</v>
+        <v>6.32</v>
+      </c>
+      <c r="F1062">
+        <v>6.64</v>
       </c>
       <c r="G1062" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -32784,7 +32808,7 @@
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -32793,16 +32817,19 @@
         </is>
       </c>
       <c r="E1063">
-        <v>5.776666666666666</v>
+        <v>4.853333333333333</v>
+      </c>
+      <c r="F1063">
+        <v>-1.15</v>
       </c>
       <c r="G1063" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
@@ -32812,7 +32839,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -32821,16 +32848,19 @@
         </is>
       </c>
       <c r="E1064">
-        <v>28.01666666666667</v>
+        <v>26.59333333333333</v>
+      </c>
+      <c r="F1064">
+        <v>-1.4</v>
       </c>
       <c r="G1064" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -32840,7 +32870,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -32849,16 +32879,19 @@
         </is>
       </c>
       <c r="E1065">
-        <v>14.9</v>
+        <v>16.85</v>
+      </c>
+      <c r="F1065">
+        <v>7.42</v>
       </c>
       <c r="G1065" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
@@ -32868,7 +32901,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -32877,16 +32910,19 @@
         </is>
       </c>
       <c r="E1066">
-        <v>9.120000000000001</v>
+        <v>13.12</v>
+      </c>
+      <c r="F1066">
+        <v>58.33</v>
       </c>
       <c r="G1066" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>Pomerode</t>
+          <t>Balneário Camboriú</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -32896,7 +32932,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Setembro</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -32905,10 +32941,13 @@
         </is>
       </c>
       <c r="E1067">
-        <v>8.6</v>
+        <v>7.166666666666667</v>
+      </c>
+      <c r="F1067">
+        <v>1.85</v>
       </c>
       <c r="G1067" s="2">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="1068">
@@ -32924,7 +32963,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -32933,13 +32972,10 @@
         </is>
       </c>
       <c r="E1068">
-        <v>3.596666666666667</v>
-      </c>
-      <c r="F1068">
-        <v>16.15</v>
+        <v>3.096666666666667</v>
       </c>
       <c r="G1068" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1069">
@@ -32955,7 +32991,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -32964,13 +33000,10 @@
         </is>
       </c>
       <c r="E1069">
-        <v>3.693333333333333</v>
-      </c>
-      <c r="F1069">
-        <v>-1.86</v>
+        <v>3.763333333333333</v>
       </c>
       <c r="G1069" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1070">
@@ -32986,7 +33019,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -32997,11 +33030,8 @@
       <c r="E1070">
         <v>5.626666666666667</v>
       </c>
-      <c r="F1070">
-        <v>0</v>
-      </c>
       <c r="G1070" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1071">
@@ -33017,7 +33047,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -33026,13 +33056,10 @@
         </is>
       </c>
       <c r="E1071">
-        <v>7.926666666666667</v>
-      </c>
-      <c r="F1071">
-        <v>44.38</v>
+        <v>5.49</v>
       </c>
       <c r="G1071" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1072">
@@ -33048,7 +33075,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -33057,13 +33084,10 @@
         </is>
       </c>
       <c r="E1072">
-        <v>26.01333333333333</v>
-      </c>
-      <c r="F1072">
-        <v>10.35</v>
+        <v>23.57333333333333</v>
       </c>
       <c r="G1072" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1073">
@@ -33079,7 +33103,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -33088,13 +33112,10 @@
         </is>
       </c>
       <c r="E1073">
-        <v>52.74</v>
-      </c>
-      <c r="F1073">
-        <v>-1.03</v>
+        <v>53.28666666666666</v>
       </c>
       <c r="G1073" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1074">
@@ -33110,7 +33131,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -33119,13 +33140,10 @@
         </is>
       </c>
       <c r="E1074">
-        <v>3.88</v>
-      </c>
-      <c r="F1074">
-        <v>-5.37</v>
+        <v>4.1</v>
       </c>
       <c r="G1074" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1075">
@@ -33141,7 +33159,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
@@ -33150,13 +33168,10 @@
         </is>
       </c>
       <c r="E1075">
-        <v>7.143333333333334</v>
-      </c>
-      <c r="F1075">
-        <v>9.23</v>
+        <v>6.54</v>
       </c>
       <c r="G1075" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1076">
@@ -33172,7 +33187,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
@@ -33181,13 +33196,10 @@
         </is>
       </c>
       <c r="E1076">
-        <v>5.826666666666667</v>
-      </c>
-      <c r="F1076">
-        <v>0.87</v>
+        <v>5.776666666666666</v>
       </c>
       <c r="G1076" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1077">
@@ -33203,7 +33215,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -33212,13 +33224,10 @@
         </is>
       </c>
       <c r="E1077">
-        <v>29.14666666666666</v>
-      </c>
-      <c r="F1077">
-        <v>4.03</v>
+        <v>28.01666666666667</v>
       </c>
       <c r="G1077" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1078">
@@ -33234,7 +33243,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -33245,11 +33254,8 @@
       <c r="E1078">
         <v>14.9</v>
       </c>
-      <c r="F1078">
-        <v>0</v>
-      </c>
       <c r="G1078" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1079">
@@ -33265,7 +33271,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Setembro</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -33274,13 +33280,10 @@
         </is>
       </c>
       <c r="E1079">
-        <v>12.32</v>
-      </c>
-      <c r="F1079">
-        <v>35.09</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="G1079" s="2">
-        <v>46266</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="1080">
@@ -33296,21 +33299,421 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E1080">
+        <v>8.6</v>
+      </c>
+      <c r="G1080" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
           <t>Setembro</t>
         </is>
       </c>
-      <c r="D1080" t="inlineStr">
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E1081">
+        <v>3.596666666666667</v>
+      </c>
+      <c r="F1081">
+        <v>16.15</v>
+      </c>
+      <c r="G1081" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E1082">
+        <v>3.693333333333333</v>
+      </c>
+      <c r="F1082">
+        <v>-1.86</v>
+      </c>
+      <c r="G1082" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E1083">
+        <v>5.626666666666667</v>
+      </c>
+      <c r="F1083">
+        <v>0</v>
+      </c>
+      <c r="G1083" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E1084">
+        <v>7.926666666666667</v>
+      </c>
+      <c r="F1084">
+        <v>44.38</v>
+      </c>
+      <c r="G1084" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E1085">
+        <v>26.01333333333333</v>
+      </c>
+      <c r="F1085">
+        <v>10.35</v>
+      </c>
+      <c r="G1085" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E1086">
+        <v>52.74</v>
+      </c>
+      <c r="F1086">
+        <v>-1.03</v>
+      </c>
+      <c r="G1086" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E1087">
+        <v>3.88</v>
+      </c>
+      <c r="F1087">
+        <v>-5.37</v>
+      </c>
+      <c r="G1087" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E1088">
+        <v>7.143333333333334</v>
+      </c>
+      <c r="F1088">
+        <v>9.23</v>
+      </c>
+      <c r="G1088" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E1089">
+        <v>5.826666666666667</v>
+      </c>
+      <c r="F1089">
+        <v>0.87</v>
+      </c>
+      <c r="G1089" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E1090">
+        <v>29.14666666666666</v>
+      </c>
+      <c r="F1090">
+        <v>4.03</v>
+      </c>
+      <c r="G1090" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E1091">
+        <v>14.9</v>
+      </c>
+      <c r="F1091">
+        <v>0</v>
+      </c>
+      <c r="G1091" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E1092">
+        <v>12.32</v>
+      </c>
+      <c r="F1092">
+        <v>35.09</v>
+      </c>
+      <c r="G1092" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
         <is>
           <t>Óleo de Soja</t>
         </is>
       </c>
-      <c r="E1080">
+      <c r="E1093">
         <v>8.91</v>
       </c>
-      <c r="F1080">
+      <c r="F1093">
         <v>3.6</v>
       </c>
-      <c r="G1080" s="2">
+      <c r="G1093" s="2">
         <v>46266</v>
       </c>
     </row>
